--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E18D35-5905-4B92-9C07-DDECCCF39E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3956520E-7B46-4112-9F5B-CEDFDDAB89B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="741">
   <si>
     <t>Image</t>
   </si>
@@ -249,9 +249,6 @@
     <t>Palais royal d'Amsterdam (ancien hôtel de ville)</t>
   </si>
   <si>
-    <t>"Mercure (statue)"</t>
-  </si>
-  <si>
     <t>c.200 cm</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t>1684</t>
   </si>
   <si>
-    <t>"L'Air (statue du Parterre d'Eau)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Filippo_parodi%2C_san_giovanni_battista%2C_1667.JPG/1280px-Filippo_parodi%2C_san_giovanni_battista%2C_1667.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -405,9 +399,6 @@
     <t>"Saint Jean-Baptiste"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Francesco_mochi%2C_santa_veronica%2C_1632.JPG/960px-Francesco_mochi%2C_santa_veronica%2C_1632.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>Francesco</t>
   </si>
   <si>
@@ -579,9 +570,6 @@
     <t>Église de Loschwitz</t>
   </si>
   <si>
-    <t>"Autel Nosseni (Nosseni-Altar)"</t>
-  </si>
-  <si>
     <t>Marbre et albâtre</t>
   </si>
   <si>
@@ -969,9 +957,6 @@
     <t>Graben</t>
   </si>
   <si>
-    <t>"Colonne de la Peste (contributions)"</t>
-  </si>
-  <si>
     <t>Melchiorre</t>
   </si>
   <si>
@@ -1410,9 +1395,6 @@
     <t>49;5</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg/960px-Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>c,200</t>
   </si>
   <si>
@@ -1695,6 +1677,9 @@
     <t>Buste de Michel-Ange Buonarroti le Jeune</t>
   </si>
   <si>
+    <t>Christ de la Clémence</t>
+  </si>
+  <si>
     <t>Christ gisant</t>
   </si>
   <si>
@@ -1887,9 +1872,6 @@
     <t xml:space="preserve">Colonnade </t>
   </si>
   <si>
-    <t>Basilique Sant'Andrea delle Fratte</t>
-  </si>
-  <si>
     <t>Musée du Bargello</t>
   </si>
   <si>
@@ -1929,9 +1911,6 @@
     <t>Sainte Hélène de Constantinople</t>
   </si>
   <si>
-    <t>Melchiorre_Caffà.jpg (540×714)</t>
-  </si>
-  <si>
     <t>Cathédrale</t>
   </si>
   <si>
@@ -1944,9 +1923,6 @@
     <t>Basilique Sainte-Marie-Majeure</t>
   </si>
   <si>
-    <t>1280px-Versailles,_sala_della_guerra.JPG (1280×960)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Louis XIV à cheval </t>
   </si>
   <si>
@@ -1959,9 +1935,6 @@
     <t>Institut de France</t>
   </si>
   <si>
-    <t>960px-Grand_Conde_Louvre_MR3343.jpg (960×1171)</t>
-  </si>
-  <si>
     <t>Buste de Charles Le Brun</t>
   </si>
   <si>
@@ -1977,21 +1950,12 @@
     <t>La Nymphe à la coquille</t>
   </si>
   <si>
-    <t>960px-Le_Brun_Coysevox_Louvre_MR2156.jpg (960×1278)</t>
-  </si>
-  <si>
-    <t>Parc_de_Versailles,_parterre_de_Latone,_Nymphe_à_la_coquille,_Auguste_Suchetet_d'ap._Antoine_Coysevox_01.jpg (3375×2251)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Eglise Saint-Nicolas </t>
   </si>
   <si>
     <t>960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG (960×1278)</t>
   </si>
   <si>
-    <t>Francesco_Mochi_Santa_Verónica_1629-32_Vaticano.jpg (672×1083)</t>
-  </si>
-  <si>
     <t>"Décors de l'Oratoire du Rosaire"</t>
   </si>
   <si>
@@ -2007,9 +1971,6 @@
     <t>960px-Ecce_Homo,_Pedro_de_Mena.jpg (960×1278)</t>
   </si>
   <si>
-    <t>1280px-Malaga_Kathedrale_Der_Chor2.jpg (1280×942)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cathédrale </t>
   </si>
   <si>
@@ -2061,9 +2022,6 @@
     <t>Le Nil</t>
   </si>
   <si>
-    <t>960px-Ange_portant_le_voile_de_sainte_Véronique_de_Cosimo_Fancelli,_Pont_Saint-Ange,_Rome,_Italie.jpg (960×1443)</t>
-  </si>
-  <si>
     <t>Pont Saint Ange</t>
   </si>
   <si>
@@ -2112,18 +2070,12 @@
     <t>S.m. del carmine, int., cappella corsini, g.b. foggini, apparizione di maria a s.andrea corsini, 1683-91 ca. - Catégorie : Reliefs de Giovanni Battista Foggini dans la Cappella Corsini - Wikimedia Commons</t>
   </si>
   <si>
-    <t>1920px-St_Paul's_Cathedral_Choir_looking_east,_London,_UK_-_Diliff.jpg (1920×2115)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cathédrale Saint-Paul </t>
   </si>
   <si>
     <t>Décor sculpté des stalles</t>
   </si>
   <si>
-    <t>960px-Enlèvement_de_Proserpine_par_Pluton,_Girardon,_original_-_DSC_0872.JPG (960×1444)</t>
-  </si>
-  <si>
     <t>Orangerie</t>
   </si>
   <si>
@@ -2154,9 +2106,6 @@
     <t>Médailon à l'effigie de Louis XIV</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t xml:space="preserve">Porte Saint-Denis </t>
   </si>
   <si>
@@ -2184,9 +2133,6 @@
     <t>1280px-Apollon_et_ses_chevaux,_Bassin_du_char_d'Apollon,_Château_de_Versailles.jpg (1280×853)</t>
   </si>
   <si>
-    <t>https://en.wikipedia.org/wiki/Camillo_Mariani#/media/File:Interior_of_San_Bernardo_alle_Terme_(Rome)_(8).jpg</t>
-  </si>
-  <si>
     <t>Saint François d'Assise</t>
   </si>
   <si>
@@ -2260,6 +2206,57 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/00120_Vatican_City_-_panoramio_%2842%29.jpg/960px-00120_Vatican_City_-_panoramio_%2842%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Interior_of_San_Bernardo_alle_Terme_%28Rome%29_%288%29.jpg/960px-Interior_of_San_Bernardo_alle_Terme_%28Rome%29_%288%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/70/Melchiorre_Caff%C3%A0.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/Parc_de_Versailles%2C_parterre_de_Latone%2C_Nymphe_%C3%A0_la_coquille%2C_Auguste_Suchetet_d%27ap._Antoine_Coysevox_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/96/Grand_Conde_Louvre_MR3343.jpg/960px-Grand_Conde_Louvre_MR3343.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Malaga_Kathedrale_Der_Chor2.jpg/1280px-Malaga_Kathedrale_Der_Chor2.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Le_Brun_Coysevox_Louvre_MR2156.jpg/960px-Le_Brun_Coysevox_Louvre_MR2156.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Versailles%2C_sala_della_guerra.JPG/1280px-Versailles%2C_sala_della_guerra.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>"Colonne de la Peste "</t>
+  </si>
+  <si>
+    <t>"Mercure "</t>
+  </si>
+  <si>
+    <t>Basilique San Andrea delle Fratte</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>"L'Air"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/Francesco_Mochi_Santa_Ver%C3%B3nica_1629-32_Vaticano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4a/Annonciation_de_Francesco_Mochi.jpg/1280px-Annonciation_de_Francesco_Mochi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2401,7 +2398,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2525,6 +2522,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2949,11 +2947,11 @@
         <v>26</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -2961,7 +2959,7 @@
         <v>27</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="Q2" s="4">
         <v>490</v>
@@ -2975,7 +2973,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>21</v>
@@ -2992,22 +2990,22 @@
         <v>24</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K3" s="39"/>
       <c r="L3" s="43" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
       <c r="O3" s="29" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="P3" s="35"/>
       <c r="R3" s="19"/>
@@ -3021,7 +3019,7 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>21</v>
@@ -3038,17 +3036,17 @@
         <v>24</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="43" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
@@ -3074,7 +3072,7 @@
     </row>
     <row r="5" spans="1:21" ht="14.25" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>21</v>
@@ -3091,17 +3089,17 @@
         <v>24</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="I5" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="43" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
@@ -3122,7 +3120,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>21</v>
@@ -3139,17 +3137,17 @@
         <v>24</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="43" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
@@ -3170,34 +3168,34 @@
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="30" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G7" s="30" t="s">
         <v>59</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>48</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3219,24 +3217,24 @@
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="30" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I8" s="30" t="s">
         <v>48</v>
@@ -3246,7 +3244,7 @@
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -3274,39 +3272,39 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="29" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G9" s="29" t="s">
         <v>59</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P9" s="35"/>
       <c r="R9" s="19"/>
@@ -3320,24 +3318,24 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="29" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>48</v>
@@ -3347,7 +3345,7 @@
       </c>
       <c r="K10" s="39"/>
       <c r="L10" s="43" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
@@ -3373,36 +3371,36 @@
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="30" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -3424,36 +3422,36 @@
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -3461,7 +3459,7 @@
         <v>27</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>28</v>
@@ -3475,36 +3473,36 @@
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I13" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -3512,7 +3510,7 @@
         <v>27</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>28</v>
@@ -3526,36 +3524,36 @@
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I14" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -3563,7 +3561,7 @@
         <v>27</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="Q14" s="4">
         <v>109</v>
@@ -3580,36 +3578,36 @@
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I15" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -3617,7 +3615,7 @@
         <v>27</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="Q15" s="4">
         <v>279</v>
@@ -3637,36 +3635,36 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I16" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -3674,7 +3672,7 @@
         <v>40</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>28</v>
@@ -3688,23 +3686,23 @@
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H17" s="28" t="s">
         <v>60</v>
@@ -3713,19 +3711,19 @@
         <v>26</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="37" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>28</v>
@@ -3739,41 +3737,41 @@
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="43" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
       <c r="O18" s="29" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="P18" s="35">
         <v>470</v>
@@ -3789,36 +3787,36 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J19" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K19" s="39"/>
       <c r="L19" s="43" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -3844,43 +3842,43 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="43" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="19" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="P20" s="35">
         <v>900</v>
@@ -3896,41 +3894,41 @@
     </row>
     <row r="21" spans="1:21" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="43" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
       <c r="O21" s="29" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="P21" s="35">
         <v>700</v>
@@ -3946,23 +3944,23 @@
     </row>
     <row r="22" spans="1:21" ht="15" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H22" s="29" t="s">
         <v>33</v>
@@ -3971,16 +3969,16 @@
         <v>26</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K22" s="39"/>
       <c r="L22" s="43" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
       <c r="O22" s="29" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="P22" s="35">
         <v>1269</v>
@@ -3996,36 +3994,36 @@
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K23" s="39"/>
       <c r="L23" s="43" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
@@ -4046,36 +4044,36 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K24" s="39"/>
       <c r="L24" s="43" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="19"/>
@@ -4096,38 +4094,38 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J25" s="43" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="L25" s="43" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
@@ -4153,41 +4151,41 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K26" s="39"/>
       <c r="L26" s="43" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
       <c r="O26" s="29" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="P26" s="35">
         <v>1677</v>
@@ -4208,36 +4206,36 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>617</v>
+        <v>736</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="M27" s="19"/>
       <c r="N27" s="19"/>
@@ -4263,36 +4261,36 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>617</v>
+        <v>736</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4318,36 +4316,36 @@
     </row>
     <row r="29" spans="1:21" ht="15" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="K29" s="39"/>
       <c r="L29" s="43" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
@@ -4373,41 +4371,41 @@
     </row>
     <row r="30" spans="1:21" ht="15" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="K30" s="39"/>
       <c r="L30" s="43" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="29" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="P30" s="35">
         <v>200</v>
@@ -4426,36 +4424,36 @@
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="K31" s="39"/>
       <c r="L31" s="43" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
@@ -4476,26 +4474,26 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>48</v>
@@ -4505,7 +4503,7 @@
       </c>
       <c r="K32" s="39"/>
       <c r="L32" s="43" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4531,36 +4529,36 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E33" s="19"/>
       <c r="F33" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="K33" s="39"/>
       <c r="L33" s="43" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4586,36 +4584,36 @@
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E34" s="19"/>
       <c r="F34" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K34" s="39"/>
       <c r="L34" s="43" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
@@ -4636,36 +4634,36 @@
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E35" s="19"/>
       <c r="F35" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="K35" s="39"/>
       <c r="L35" s="43" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -4686,36 +4684,36 @@
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E36" s="19"/>
       <c r="F36" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="K36" s="39"/>
       <c r="L36" s="43" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="M36" s="19"/>
       <c r="N36" s="19"/>
@@ -4741,41 +4739,41 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="K37" s="39"/>
       <c r="L37" s="43" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
       <c r="O37" s="29" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="P37" s="35">
         <v>150</v>
@@ -4794,34 +4792,34 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
       <c r="F38" s="29" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G38" s="29" t="s">
         <v>34</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I38" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="43" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
@@ -4842,47 +4840,47 @@
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="30" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I39" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="T39" s="2">
         <v>3</v>
@@ -4893,18 +4891,18 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>631</v>
+        <v>727</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="30" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G40" s="30" t="s">
         <v>33</v>
@@ -4916,11 +4914,11 @@
         <v>26</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4928,12 +4926,12 @@
         <v>27</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="T40" s="4">
         <v>2</v>
@@ -4964,10 +4962,10 @@
         <v>34</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="3" t="s">
@@ -4995,39 +4993,39 @@
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1">
       <c r="A42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="C42" s="30" t="s">
         <v>77</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>78</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="H42" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="H42" s="30" t="s">
+      <c r="I42" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="I42" s="30" t="s">
+      <c r="J42" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P42" s="2">
         <v>85</v>
@@ -5039,7 +5037,7 @@
         <v>74</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T42" s="2">
         <v>3</v>
@@ -5050,36 +5048,36 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="29" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="M43" s="19"/>
       <c r="N43" s="19"/>
@@ -5100,24 +5098,24 @@
     </row>
     <row r="44" spans="1:21" ht="15" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G44" s="30" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H44" s="30" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I44" s="30" t="s">
         <v>48</v>
@@ -5127,7 +5125,7 @@
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -5155,7 +5153,7 @@
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>43</v>
@@ -5181,10 +5179,10 @@
         <v>49</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -5192,10 +5190,10 @@
         <v>27</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="R45" s="4">
         <v>128</v>
@@ -5233,10 +5231,10 @@
         <v>49</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -5244,10 +5242,10 @@
         <v>27</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="R46" s="4">
         <v>128</v>
@@ -5261,7 +5259,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5278,14 +5276,14 @@
         <v>46</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -5304,7 +5302,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>648</v>
+        <v>729</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5321,14 +5319,14 @@
         <v>46</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -5376,10 +5374,10 @@
         <v>53</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -5387,7 +5385,7 @@
         <v>27</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q49" s="4">
         <v>75</v>
@@ -5402,7 +5400,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>636</v>
+        <v>733</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5419,22 +5417,22 @@
         <v>46</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="I50" s="29"/>
       <c r="J50" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
       <c r="O50" s="29" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="P50" s="35">
         <v>390</v>
@@ -5455,7 +5453,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5472,22 +5470,22 @@
         <v>46</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>48</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="43" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
       <c r="O51" s="29" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="P51" s="35">
         <v>400</v>
@@ -5503,7 +5501,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>647</v>
+        <v>732</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5530,7 +5528,7 @@
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="43" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5556,7 +5554,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>641</v>
+        <v>730</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5573,7 +5571,7 @@
         <v>46</v>
       </c>
       <c r="H53" s="29" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="I53" s="29" t="s">
         <v>48</v>
@@ -5583,7 +5581,7 @@
       </c>
       <c r="K53" s="39"/>
       <c r="L53" s="43" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M53" s="19"/>
       <c r="N53" s="19"/>
@@ -5609,34 +5607,34 @@
     </row>
     <row r="54" spans="1:21" ht="15" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="G54" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="I54" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="J54" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="G54" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="H54" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="I54" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -5649,7 +5647,7 @@
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
       <c r="S54" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="T54" s="2">
         <v>3</v>
@@ -5660,32 +5658,32 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
       <c r="F55" s="31" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G55" s="31" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H55" s="31" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
       <c r="L55" s="44" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
@@ -5711,13 +5709,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5725,18 +5723,18 @@
         <v>58</v>
       </c>
       <c r="G56" s="31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="I56" s="31" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J56" s="44"/>
       <c r="K56" s="40"/>
       <c r="L56" s="44" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
@@ -5762,34 +5760,34 @@
     </row>
     <row r="57" spans="1:21" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G57" s="32" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I57" s="32" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J57" s="23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K57" s="20"/>
       <c r="L57" s="22" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
@@ -5797,7 +5795,7 @@
         <v>36</v>
       </c>
       <c r="P57" s="20" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="Q57" s="2">
         <v>55</v>
@@ -5817,34 +5815,34 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G58" s="31" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H58" s="31" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I58" s="32" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J58" s="23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K58" s="40"/>
       <c r="L58" s="44" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
@@ -5870,43 +5868,43 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>657</v>
+        <v>731</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
       <c r="F59" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G59" s="31" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H59" s="31" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="I59" s="31" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
       <c r="O59" s="31" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5919,34 +5917,34 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
       <c r="F60" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H60" s="31">
         <v>1663</v>
       </c>
       <c r="I60" s="31" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5967,34 +5965,34 @@
     </row>
     <row r="61" spans="1:21" ht="15" customHeight="1">
       <c r="A61" s="15" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G61" s="32" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H61" s="32" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I61" s="32" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -6005,7 +6003,7 @@
         <v>47</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="R61" s="20">
         <v>27.5</v>
@@ -6020,24 +6018,24 @@
     </row>
     <row r="62" spans="1:21" ht="15" customHeight="1">
       <c r="A62" s="15" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="32" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H62" s="32" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I62" s="32" t="s">
         <v>48</v>
@@ -6047,7 +6045,7 @@
       </c>
       <c r="K62" s="20"/>
       <c r="L62" s="22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M62" s="22"/>
       <c r="N62" s="22"/>
@@ -6073,21 +6071,21 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="31" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G63" s="31" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H63" s="31" t="s">
         <v>59</v>
@@ -6100,7 +6098,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6124,34 +6122,34 @@
     </row>
     <row r="64" spans="1:21" ht="15" customHeight="1">
       <c r="A64" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I64" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K64" s="20"/>
       <c r="L64" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="M64" s="22"/>
       <c r="N64" s="22"/>
@@ -6164,7 +6162,7 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="20"/>
       <c r="S64" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T64" s="2">
         <v>1</v>
@@ -6175,34 +6173,34 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>458</v>
+        <v>728</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G65" s="33" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="I65" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K65" s="23"/>
       <c r="L65" s="23" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="M65" s="21"/>
       <c r="N65" s="21"/>
@@ -6222,22 +6220,22 @@
       </c>
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
-      <c r="A66" s="46" t="s">
-        <v>666</v>
+      <c r="A66" s="51" t="s">
+        <v>653</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C66" s="47" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
       <c r="F66" s="31" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G66" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H66" s="31">
         <v>1629</v>
@@ -6246,11 +6244,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6274,32 +6272,32 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
       <c r="F67" s="31" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G67" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6320,34 +6318,34 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="29" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>601</v>
-      </c>
-      <c r="J68" s="51" t="s">
-        <v>671</v>
+        <v>596</v>
+      </c>
+      <c r="J68" s="52" t="s">
+        <v>658</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6368,21 +6366,21 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="31" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G69" s="31" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="H69" s="31" t="s">
         <v>60</v>
@@ -6391,18 +6389,18 @@
         <v>26</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
       <c r="O69" s="31" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="P69" s="36">
         <v>550</v>
@@ -6418,34 +6416,34 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>675</v>
+        <v>724</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="31" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I70" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6466,34 +6464,34 @@
     </row>
     <row r="71" spans="1:21" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B71" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="C71" s="32" t="s">
         <v>91</v>
-      </c>
-      <c r="C71" s="32" t="s">
-        <v>92</v>
       </c>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="G71" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="G71" s="32" t="s">
+      <c r="H71" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="H71" s="32" t="s">
+      <c r="I71" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="I71" s="32" t="s">
+      <c r="J71" s="23" t="s">
         <v>96</v>
-      </c>
-      <c r="J71" s="23" t="s">
-        <v>97</v>
       </c>
       <c r="K71" s="20"/>
       <c r="L71" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M71" s="22"/>
       <c r="N71" s="22"/>
@@ -6515,45 +6513,45 @@
     </row>
     <row r="72" spans="1:21" ht="15" customHeight="1">
       <c r="A72" s="17" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="H72" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="I72" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="J72" s="23" t="s">
         <v>281</v>
-      </c>
-      <c r="G72" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="H72" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="I72" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="J72" s="23" t="s">
-        <v>285</v>
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
       <c r="O72" s="32" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P72" s="20"/>
       <c r="Q72" s="2"/>
       <c r="R72" s="20"/>
       <c r="S72" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T72" s="2">
         <v>3</v>
@@ -6562,34 +6560,34 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="31" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H73" s="31">
-        <v>1995</v>
+        <v>1695</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6610,38 +6608,38 @@
     </row>
     <row r="74" spans="1:21" ht="15" customHeight="1">
       <c r="A74" s="17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G74" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H74" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="I74" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="J74" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="G74" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="H74" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="I74" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="J74" s="23" t="s">
-        <v>198</v>
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="7" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M74" s="22"/>
       <c r="N74" s="22" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O74" s="32" t="s">
         <v>36</v>
@@ -6667,34 +6665,34 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="31" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K75" s="40"/>
       <c r="L75" s="44" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="M75" s="11"/>
       <c r="N75" s="11"/>
@@ -6720,34 +6718,34 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="31" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="44" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="M76" s="11"/>
       <c r="N76" s="11"/>
@@ -6773,24 +6771,24 @@
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B77" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="47" t="s">
         <v>105</v>
-      </c>
-      <c r="C77" s="47" t="s">
-        <v>106</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G77" s="31" t="s">
         <v>59</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I77" s="31" t="s">
         <v>26</v>
@@ -6798,12 +6796,12 @@
       <c r="J77" s="44"/>
       <c r="K77" s="40"/>
       <c r="L77" s="44" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="M77" s="11"/>
       <c r="N77" s="11"/>
       <c r="O77" s="31" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="P77" s="36"/>
       <c r="R77" s="11"/>
@@ -6817,34 +6815,34 @@
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B78" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="47" t="s">
         <v>105</v>
-      </c>
-      <c r="C78" s="47" t="s">
-        <v>106</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G78" s="31" t="s">
         <v>59</v>
       </c>
       <c r="H78" s="31" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I78" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="M78" s="11"/>
       <c r="N78" s="11"/>
@@ -6865,24 +6863,24 @@
     </row>
     <row r="79" spans="1:21" ht="15" customHeight="1">
       <c r="A79" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="32" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G79" s="32" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I79" s="32" t="s">
         <v>48</v>
@@ -6892,7 +6890,7 @@
       </c>
       <c r="K79" s="20"/>
       <c r="L79" s="22" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M79" s="22"/>
       <c r="N79" s="22"/>
@@ -6900,7 +6898,7 @@
         <v>27</v>
       </c>
       <c r="P79" s="20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" s="20"/>
@@ -6914,13 +6912,13 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
@@ -6928,20 +6926,20 @@
         <v>32</v>
       </c>
       <c r="G80" s="31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="I80" s="31" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
@@ -6962,36 +6960,36 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
       <c r="F81" s="31" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G81" s="31" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="I81" s="31" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6999,7 +6997,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -7012,39 +7010,39 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>692</v>
+        <v>726</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
       <c r="F82" s="31" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G82" s="31" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="I82" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
       <c r="O82" s="31" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="P82" s="36"/>
       <c r="R82" s="11"/>
@@ -7058,24 +7056,24 @@
     </row>
     <row r="83" spans="1:21" ht="15" customHeight="1">
       <c r="A83" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G83" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H83" s="33" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I83" s="33" t="s">
         <v>48</v>
@@ -7083,7 +7081,7 @@
       <c r="J83" s="23"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M83" s="21"/>
       <c r="N83" s="21"/>
@@ -7091,7 +7089,7 @@
         <v>27</v>
       </c>
       <c r="P83" s="21" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="R83" s="21"/>
       <c r="S83" s="26"/>
@@ -7104,34 +7102,34 @@
     </row>
     <row r="84" spans="1:21" ht="15" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
       <c r="F84" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G84" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I84" s="31" t="s">
         <v>48</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K84" s="40"/>
       <c r="L84" s="44" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
@@ -7159,34 +7157,34 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>695</v>
+        <v>737</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
       <c r="F85" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G85" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="I85" s="31" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
@@ -7212,32 +7210,32 @@
     </row>
     <row r="86" spans="1:21" ht="15" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
       <c r="F86" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G86" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H86" s="31" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I86" s="31" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="J86" s="44"/>
       <c r="K86" s="40"/>
       <c r="L86" s="44" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="M86" s="11"/>
       <c r="N86" s="11"/>
@@ -7256,34 +7254,34 @@
     </row>
     <row r="87" spans="1:21" ht="15" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D87" s="11"/>
       <c r="E87" s="11"/>
       <c r="F87" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G87" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H87" s="31" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I87" s="31"/>
       <c r="J87" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7309,32 +7307,32 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="B88" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" s="32" t="s">
         <v>99</v>
-      </c>
-      <c r="C88" s="32" t="s">
-        <v>100</v>
       </c>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="G88" s="32" t="s">
         <v>101</v>
-      </c>
-      <c r="G88" s="32" t="s">
-        <v>102</v>
       </c>
       <c r="H88" s="32">
         <v>1677</v>
       </c>
       <c r="I88" s="32"/>
       <c r="J88" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M88" s="22"/>
       <c r="N88" s="22"/>
@@ -7360,21 +7358,21 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="B89" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="C89" s="47" t="s">
-        <v>100</v>
       </c>
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
       <c r="F89" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G89" s="31" t="s">
         <v>101</v>
-      </c>
-      <c r="G89" s="31" t="s">
-        <v>102</v>
       </c>
       <c r="H89" s="31">
         <v>1670</v>
@@ -7383,11 +7381,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7406,24 +7404,24 @@
     </row>
     <row r="90" spans="1:21" ht="15" customHeight="1">
       <c r="A90" s="17" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="32" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I90" s="32" t="s">
         <v>48</v>
@@ -7433,7 +7431,7 @@
       </c>
       <c r="K90" s="20"/>
       <c r="L90" s="22" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M90" s="22"/>
       <c r="N90" s="22"/>
@@ -7441,7 +7439,7 @@
         <v>40</v>
       </c>
       <c r="P90" s="20" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="20"/>
@@ -7457,40 +7455,40 @@
     </row>
     <row r="91" spans="1:21" ht="15" customHeight="1">
       <c r="A91" s="15" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="32" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G91" s="32" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H91" s="32" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I91" s="32"/>
       <c r="J91" s="23" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K91" s="20"/>
       <c r="L91" s="22" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="M91" s="22"/>
       <c r="N91" s="22"/>
       <c r="O91" s="32" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P91" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" s="20"/>
@@ -7504,34 +7502,34 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
       <c r="F92" s="31" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G92" s="31" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I92" s="31" t="s">
-        <v>595</v>
-      </c>
-      <c r="J92" s="52" t="s">
-        <v>725</v>
+        <v>590</v>
+      </c>
+      <c r="J92" s="53" t="s">
+        <v>707</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7550,24 +7548,24 @@
     </row>
     <row r="93" spans="1:21" ht="15" customHeight="1">
       <c r="A93" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B93" s="32" t="s">
+      <c r="C93" s="32" t="s">
         <v>110</v>
-      </c>
-      <c r="C93" s="32" t="s">
-        <v>111</v>
       </c>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="G93" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="G93" s="32" t="s">
+      <c r="H93" s="32" t="s">
         <v>113</v>
-      </c>
-      <c r="H93" s="32" t="s">
-        <v>114</v>
       </c>
       <c r="I93" s="32"/>
       <c r="J93" s="23" t="s">
@@ -7575,7 +7573,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>115</v>
+        <v>738</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7583,7 +7581,7 @@
         <v>40</v>
       </c>
       <c r="P93" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" s="20"/>
@@ -7597,34 +7595,34 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
       <c r="F94" s="31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G94" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="I94" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
@@ -7643,32 +7641,32 @@
     </row>
     <row r="95" spans="1:21" ht="15" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="32" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G95" s="32" t="s">
         <v>39</v>
       </c>
       <c r="H95" s="32" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="I95" s="32"/>
       <c r="J95" s="23" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="K95" s="20"/>
       <c r="L95" s="22" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="M95" s="22"/>
       <c r="N95" s="22"/>
@@ -7676,7 +7674,7 @@
         <v>27</v>
       </c>
       <c r="P95" s="20" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" s="20"/>
@@ -7690,34 +7688,34 @@
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
       <c r="A96" s="17" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="32" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G96" s="32" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H96" s="32" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I96" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="K96" s="20"/>
       <c r="L96" s="22" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="M96" s="22"/>
       <c r="N96" s="22"/>
@@ -7725,7 +7723,7 @@
         <v>27</v>
       </c>
       <c r="P96" s="20" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" s="20"/>
@@ -7739,34 +7737,34 @@
     </row>
     <row r="97" spans="1:21" ht="15" customHeight="1">
       <c r="A97" s="46" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D97" s="11"/>
       <c r="E97" s="11"/>
       <c r="F97" s="31" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G97" s="31" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H97" s="31" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I97" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J97" s="23" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="K97" s="40"/>
       <c r="L97" s="44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="M97" s="11"/>
       <c r="N97" s="11"/>
@@ -7785,34 +7783,34 @@
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="32" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G98" s="32" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I98" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J98" s="23" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K98" s="20"/>
       <c r="L98" s="22" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M98" s="22"/>
       <c r="N98" s="22"/>
@@ -7820,7 +7818,7 @@
         <v>27</v>
       </c>
       <c r="P98" s="20" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" s="20"/>
@@ -7836,39 +7834,39 @@
     </row>
     <row r="99" spans="1:21" ht="15" customHeight="1">
       <c r="A99" s="49" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
       <c r="F99" s="31" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="G99" s="31" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H99" s="31" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I99" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J99" s="44" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="K99" s="40"/>
       <c r="L99" s="44" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="M99" s="11"/>
       <c r="N99" s="11"/>
       <c r="O99" s="31" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="P99" s="36">
         <v>350</v>
@@ -7884,13 +7882,13 @@
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
@@ -7898,10 +7896,10 @@
         <v>58</v>
       </c>
       <c r="G100" s="32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H100" s="32" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I100" s="32"/>
       <c r="J100" s="23" t="s">
@@ -7909,12 +7907,12 @@
       </c>
       <c r="K100" s="20"/>
       <c r="L100" s="22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="M100" s="22"/>
       <c r="N100" s="22"/>
       <c r="O100" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P100" s="20">
         <v>204</v>
@@ -7931,13 +7929,13 @@
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1">
       <c r="A101" s="46" t="s">
-        <v>715</v>
+        <v>698</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C101" s="47" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
@@ -7945,10 +7943,10 @@
         <v>58</v>
       </c>
       <c r="G101" s="31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H101" s="31" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I101" s="31"/>
       <c r="J101" s="23" t="s">
@@ -7956,12 +7954,12 @@
       </c>
       <c r="K101" s="40"/>
       <c r="L101" s="44" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="M101" s="11"/>
       <c r="N101" s="11"/>
       <c r="O101" s="31" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P101" s="36">
         <v>300</v>
@@ -7977,40 +7975,42 @@
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="32" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G102" s="32" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H102" s="32" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I102" s="32"/>
       <c r="J102" s="23" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="K102" s="20"/>
-      <c r="L102" s="22" t="s">
-        <v>268</v>
+      <c r="L102" s="7" t="s">
+        <v>547</v>
       </c>
       <c r="M102" s="22"/>
-      <c r="N102" s="22"/>
+      <c r="N102" s="22" t="s">
+        <v>264</v>
+      </c>
       <c r="O102" s="32" t="s">
         <v>36</v>
       </c>
       <c r="P102" s="20" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" s="20"/>
@@ -8023,33 +8023,33 @@
       <c r="U102" s="14"/>
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
-      <c r="A103" s="15" t="s">
-        <v>123</v>
+      <c r="A103" s="17" t="s">
+        <v>740</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D103" s="21"/>
       <c r="E103" s="21"/>
       <c r="F103" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G103" s="33" t="s">
         <v>24</v>
       </c>
       <c r="H103" s="33" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="I103" s="33" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
       <c r="L103" s="23" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="M103" s="21"/>
       <c r="N103" s="21"/>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="P103" s="21" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="R103" s="21"/>
       <c r="S103" s="26"/>
@@ -8070,32 +8070,32 @@
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
       <c r="F104" s="31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G104" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="I104" s="31" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="J104" s="44"/>
       <c r="K104" s="40"/>
       <c r="L104" s="44" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="M104" s="11"/>
       <c r="N104" s="11"/>
@@ -8116,34 +8116,34 @@
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>651</v>
+        <v>739</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
       <c r="F105" s="31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G105" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H105" s="31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I105" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K105" s="40"/>
       <c r="L105" s="44" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="M105" s="11"/>
       <c r="N105" s="11"/>
@@ -8164,34 +8164,34 @@
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
       <c r="F106" s="31" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G106" s="31" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H106" s="31" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="I106" s="31" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
@@ -8199,7 +8199,7 @@
         <v>36</v>
       </c>
       <c r="P106" s="36" t="s">
-        <v>713</v>
+        <v>696</v>
       </c>
       <c r="R106" s="11"/>
       <c r="S106" s="12"/>
@@ -8212,34 +8212,34 @@
     </row>
     <row r="107" spans="1:21" ht="15" customHeight="1">
       <c r="A107" s="46" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
       <c r="F107" s="31" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G107" s="31" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I107" s="31" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J107" s="44" t="s">
-        <v>710</v>
+        <v>693</v>
       </c>
       <c r="K107" s="40"/>
       <c r="L107" s="44" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M107" s="11"/>
       <c r="N107" s="11"/>
@@ -8260,39 +8260,39 @@
     </row>
     <row r="108" spans="1:21" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C108" s="32" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
       <c r="F108" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G108" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H108" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I108" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="J108" s="23" t="s">
         <v>177</v>
-      </c>
-      <c r="G108" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="H108" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="I108" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="J108" s="23" t="s">
-        <v>180</v>
       </c>
       <c r="K108" s="20"/>
       <c r="L108" s="22" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="32" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="P108" s="20"/>
       <c r="Q108" s="2"/>
@@ -8307,34 +8307,34 @@
     </row>
     <row r="109" spans="1:21" ht="15" customHeight="1">
       <c r="A109" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C109" s="32" t="s">
         <v>116</v>
-      </c>
-      <c r="B109" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C109" s="32" t="s">
-        <v>118</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
       <c r="F109" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G109" s="32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H109" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I109" s="32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J109" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K109" s="20"/>
       <c r="L109" s="22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M109" s="22"/>
       <c r="N109" s="22"/>
@@ -8342,7 +8342,7 @@
         <v>27</v>
       </c>
       <c r="P109" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" s="20"/>
@@ -8356,39 +8356,39 @@
     </row>
     <row r="110" spans="1:21" ht="15" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C110" s="32" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D110" s="20"/>
       <c r="E110" s="20"/>
       <c r="F110" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="G110" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="H110" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I110" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="G110" s="32" t="s">
+      <c r="J110" s="23" t="s">
         <v>158</v>
-      </c>
-      <c r="H110" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I110" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="J110" s="23" t="s">
-        <v>161</v>
       </c>
       <c r="K110" s="20"/>
       <c r="L110" s="22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M110" s="22"/>
       <c r="N110" s="22"/>
       <c r="O110" s="32" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P110" s="20"/>
       <c r="Q110" s="2"/>
@@ -8403,34 +8403,34 @@
     </row>
     <row r="111" spans="1:21" ht="15" customHeight="1">
       <c r="A111" s="15" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B111" s="33" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
       <c r="F111" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G111" s="33" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H111" s="33" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J111" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K111" s="23"/>
       <c r="L111" s="23" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M111" s="21"/>
       <c r="N111" s="21"/>
@@ -8438,13 +8438,13 @@
         <v>27</v>
       </c>
       <c r="P111" s="21" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Q111" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="R111" s="21" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="S111" s="26"/>
       <c r="T111" s="4">
@@ -8456,34 +8456,34 @@
     </row>
     <row r="112" spans="1:21" ht="15" customHeight="1">
       <c r="A112" s="15" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
       <c r="F112" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G112" s="33" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H112" s="33" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="I112" s="33" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="J112" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K112" s="23"/>
       <c r="L112" s="23" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M112" s="21"/>
       <c r="N112" s="21"/>
@@ -8509,39 +8509,39 @@
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="11"/>
       <c r="F113" s="31" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="I113" s="31" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J113" s="44" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="K113" s="40"/>
       <c r="L113" s="44" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
       <c r="O113" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P113" s="36"/>
       <c r="R113" s="11"/>
@@ -8555,24 +8555,24 @@
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="11"/>
       <c r="F114" s="31" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G114" s="31" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="I114" s="31" t="s">
         <v>48</v>
@@ -8581,9 +8581,7 @@
         <v>49</v>
       </c>
       <c r="K114" s="40"/>
-      <c r="L114" s="50" t="s">
-        <v>706</v>
-      </c>
+      <c r="L114" s="50"/>
       <c r="M114" s="11"/>
       <c r="N114" s="11"/>
       <c r="O114" s="31" t="s">
@@ -8608,34 +8606,34 @@
     </row>
     <row r="115" spans="1:21" ht="15" customHeight="1">
       <c r="A115" s="46" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="11"/>
       <c r="F115" s="31" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G115" s="31" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H115" s="31" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I115" s="31" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="J115" s="44" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="K115" s="40"/>
       <c r="L115" s="44" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="M115" s="11"/>
       <c r="N115" s="11"/>
@@ -8681,7 +8679,7 @@
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>71</v>
+        <v>735</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
@@ -8689,12 +8687,12 @@
         <v>27</v>
       </c>
       <c r="P116" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" s="20"/>
       <c r="S116" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T116" s="2">
         <v>3</v>
@@ -8752,34 +8750,34 @@
     </row>
     <row r="118" spans="1:21" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
       <c r="F118" s="32" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G118" s="32" t="s">
         <v>59</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I118" s="32" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J118" s="23" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>311</v>
+        <v>734</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
@@ -8799,24 +8797,24 @@
     </row>
     <row r="119" spans="1:21" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="32" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G119" s="32" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I119" s="32"/>
       <c r="J119" s="23" t="s">
@@ -8824,12 +8822,12 @@
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="22" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P119" s="20"/>
       <c r="Q119" s="2"/>
@@ -8844,34 +8842,34 @@
     </row>
     <row r="120" spans="1:21" ht="15" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D120" s="20"/>
       <c r="E120" s="20"/>
       <c r="F120" s="32" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H120" s="32" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K120" s="20"/>
       <c r="L120" s="22" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="M120" s="22"/>
       <c r="N120" s="22"/>
@@ -8879,7 +8877,7 @@
         <v>40</v>
       </c>
       <c r="P120" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" s="20"/>
@@ -8893,38 +8891,38 @@
     </row>
     <row r="121" spans="1:21" ht="15" customHeight="1">
       <c r="A121" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B121" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C121" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="F121" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="B121" s="32" t="s">
+      <c r="G121" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="C121" s="32" t="s">
+      <c r="H121" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="D121" s="20" t="s">
+      <c r="I121" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="E121" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="F121" s="32" t="s">
+      <c r="J121" s="23" t="s">
         <v>290</v>
-      </c>
-      <c r="G121" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="H121" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="I121" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="J121" s="23" t="s">
-        <v>294</v>
       </c>
       <c r="K121" s="20"/>
       <c r="L121" s="22" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M121" s="22"/>
       <c r="N121" s="22"/>
@@ -8932,7 +8930,7 @@
         <v>36</v>
       </c>
       <c r="P121" s="20" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" s="20"/>
@@ -8946,13 +8944,13 @@
     </row>
     <row r="122" spans="1:21" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C122" s="32" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
@@ -8960,20 +8958,20 @@
         <v>58</v>
       </c>
       <c r="G122" s="32" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J122" s="23" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="K122" s="20"/>
       <c r="L122" s="22" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
@@ -8981,7 +8979,7 @@
         <v>36</v>
       </c>
       <c r="P122" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" s="20"/>
@@ -8995,39 +8993,39 @@
     </row>
     <row r="123" spans="1:21" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
       <c r="F123" s="32" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G123" s="32" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H123" s="32" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I123" s="32" t="s">
         <v>48</v>
       </c>
       <c r="J123" s="23" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="32" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P123" s="20"/>
       <c r="Q123" s="2"/>
@@ -9042,13 +9040,13 @@
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
       <c r="A124" s="15" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D124" s="20"/>
       <c r="E124" s="20"/>
@@ -9056,25 +9054,25 @@
         <v>34</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H124" s="32" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I124" s="32" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="J124" s="23" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="22" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="32" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="P124" s="20"/>
       <c r="Q124" s="2"/>
@@ -9091,34 +9089,34 @@
     </row>
     <row r="125" spans="1:21" ht="15" customHeight="1">
       <c r="A125" s="15" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C125" s="32" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D125" s="20"/>
       <c r="E125" s="20"/>
       <c r="F125" s="32" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="G125" s="32" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="H125" s="32" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I125" s="32" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="J125" s="23" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="K125" s="20"/>
       <c r="L125" s="22" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
@@ -9129,7 +9127,7 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="20"/>
       <c r="S125" s="25" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="T125" s="2">
         <v>3</v>
@@ -9138,34 +9136,34 @@
     </row>
     <row r="126" spans="1:21" ht="15" customHeight="1">
       <c r="A126" s="15" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B126" s="32" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C126" s="32" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D126" s="20"/>
       <c r="E126" s="20"/>
       <c r="F126" s="32" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H126" s="32" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I126" s="32"/>
       <c r="J126" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K126" s="20" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M126" s="22"/>
       <c r="N126" s="22"/>
@@ -9193,13 +9191,13 @@
     </row>
     <row r="127" spans="1:21" ht="15" customHeight="1">
       <c r="A127" s="15" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C127" s="32" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D127" s="20"/>
       <c r="E127" s="20"/>
@@ -9207,20 +9205,20 @@
         <v>58</v>
       </c>
       <c r="G127" s="32" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H127" s="32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I127" s="32" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="J127" s="23" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K127" s="20"/>
       <c r="L127" s="22" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M127" s="22"/>
       <c r="N127" s="22"/>
@@ -9231,7 +9229,7 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="20"/>
       <c r="S127" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T127" s="2">
         <v>3</v>
@@ -9242,24 +9240,24 @@
     </row>
     <row r="128" spans="1:21" ht="15" customHeight="1">
       <c r="A128" s="15" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C128" s="32" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D128" s="20"/>
       <c r="E128" s="20"/>
       <c r="F128" s="32" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G128" s="32" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H128" s="32" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I128" s="32"/>
       <c r="J128" s="23" t="s">
@@ -9289,39 +9287,39 @@
     </row>
     <row r="129" spans="1:21" ht="15" customHeight="1">
       <c r="A129" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B129" s="32" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C129" s="32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D129" s="20"/>
       <c r="E129" s="20"/>
       <c r="F129" s="32" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G129" s="32" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H129" s="32" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="J129" s="23" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="K129" s="20"/>
       <c r="L129" s="22" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M129" s="22"/>
       <c r="N129" s="22"/>
       <c r="O129" s="32" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="P129" s="20"/>
       <c r="Q129" s="2"/>
@@ -11047,87 +11045,87 @@
     <hyperlink ref="A49" r:id="rId10" display="https://upload.wikimedia.org/wikipedia/commons/thumb/4/40/Ch%C3%A2teau_de_Versailles%2C_chambre_du_roi%2C_buste_de_Louis_XIV%2C_Antoine_Coysevox%2C_ca_1679_01.jpg/1280px-Ch%C3%A2teau_de_Versailles%2C_chambre_du_roi%2C_buste_de_Louis_XIV%2C_Antoine_Coysevox%2C_ca_1679_01.jpg" xr:uid="{E1D44029-E5A4-4034-8FBB-4325F8B0AD67}"/>
     <hyperlink ref="A42" r:id="rId11" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Cajus_gabriel_cibber%2C_allegoria_della_pazzia%2C_londra_1675_ca.jpg/1280px-Cajus_gabriel_cibber%2C_allegoria_della_pazzia%2C_londra_1675_ca.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{66B6E26B-5AB1-4C67-A347-F19F853AEB77}"/>
     <hyperlink ref="A44" r:id="rId12" xr:uid="{4722238B-991F-40E5-BBB4-5BCB847E17AA}"/>
-    <hyperlink ref="A65" r:id="rId13" xr:uid="{A4B21B97-CCBA-4FAD-9AB3-CF99D8E03329}"/>
-    <hyperlink ref="A90" r:id="rId14" xr:uid="{95FE0D7B-5987-40DE-8467-D8A326E0259A}"/>
-    <hyperlink ref="A18" r:id="rId15" xr:uid="{52D806BE-583E-4756-93E6-AD74999C00AC}"/>
-    <hyperlink ref="A19" r:id="rId16" xr:uid="{EAE4EEF8-50C9-43BE-A67E-15D4D4BE34DA}"/>
-    <hyperlink ref="A21" r:id="rId17" xr:uid="{AFD0A4C0-8F7A-4178-82C3-AFD16D7FE5CC}"/>
-    <hyperlink ref="A22" r:id="rId18" xr:uid="{9A91DB92-A1B0-49C9-9BCC-27031EFA890F}"/>
-    <hyperlink ref="A23" r:id="rId19" xr:uid="{DFE353BC-56F7-4D42-8CD1-85EA4544B4CE}"/>
-    <hyperlink ref="A24" r:id="rId20" xr:uid="{9D890162-34F6-4975-AAD5-6CD12099DDDE}"/>
-    <hyperlink ref="A25" r:id="rId21" xr:uid="{0ED88EB4-BABF-49DB-AB5B-FCFAAED767ED}"/>
-    <hyperlink ref="A26" r:id="rId22" xr:uid="{F9656E4A-4EEA-442F-A2B7-2E5D2C4F5F22}"/>
-    <hyperlink ref="A27" r:id="rId23" xr:uid="{4BCFDCBD-CC9B-4D94-858B-56E99635E9C6}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{552FC9D9-D503-4CAE-95BD-0C1DAC2F4F79}"/>
-    <hyperlink ref="A29" r:id="rId25" xr:uid="{E8BB6FD5-348D-412D-95BE-D404EB88A673}"/>
-    <hyperlink ref="A30" r:id="rId26" xr:uid="{E2E167C5-FC46-4F31-A2BC-4EC7F6E7ECA5}"/>
-    <hyperlink ref="A31" r:id="rId27" xr:uid="{7C75B4CB-20E1-4905-8C14-2063E9B820F9}"/>
-    <hyperlink ref="A32" r:id="rId28" xr:uid="{9D8E6B76-7CC8-466C-89AA-502F66A34E3D}"/>
-    <hyperlink ref="A33" r:id="rId29" xr:uid="{DA167E93-42C9-46D9-85FC-837F9AD62D5F}"/>
-    <hyperlink ref="A34" r:id="rId30" xr:uid="{154341E7-D5CC-4270-B9CA-F65A443651D8}"/>
-    <hyperlink ref="A35" r:id="rId31" xr:uid="{B2E5CCEB-7D04-4870-AB3B-F8D6C72F1531}"/>
-    <hyperlink ref="A36" r:id="rId32" xr:uid="{00156A24-142C-4104-8DBB-283C3FA3092D}"/>
-    <hyperlink ref="A37" r:id="rId33" xr:uid="{727F34CB-527D-4DE9-8B7F-EF45B82026BE}"/>
-    <hyperlink ref="A3" r:id="rId34" xr:uid="{8CA3DECB-0705-4A9F-BEF1-C551CFE91E9B}"/>
-    <hyperlink ref="A4" r:id="rId35" xr:uid="{FBEF4C1B-17D1-4B4B-8B04-E515851CEF78}"/>
-    <hyperlink ref="A5" r:id="rId36" xr:uid="{EF8934FA-B822-4722-8B78-A558AE023196}"/>
-    <hyperlink ref="A6" r:id="rId37" xr:uid="{51CE317D-4CB7-4404-96ED-CCEFFA7B1104}"/>
-    <hyperlink ref="A84" r:id="rId38" xr:uid="{CBF93172-B1DD-4177-B523-2019EFC222F7}"/>
-    <hyperlink ref="A86" r:id="rId39" xr:uid="{A098C7D7-E966-4299-A05F-20B9B6DF1A82}"/>
-    <hyperlink ref="A87" r:id="rId40" xr:uid="{120C261F-E2E8-4EF3-854D-002040466357}"/>
-    <hyperlink ref="A77" r:id="rId41" xr:uid="{2A9F7667-9C72-415B-BDA0-7897AF200BC7}"/>
-    <hyperlink ref="A9" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{36A963F9-1859-4BB5-AF7B-1749A3316556}"/>
-    <hyperlink ref="A10" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{5D5A21F2-A411-44D1-BB9B-2C0C70D5524C}"/>
-    <hyperlink ref="A38" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1772B789-BFB5-4FDC-8337-89F821F64C32}"/>
-    <hyperlink ref="A40" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/7/70/Melchiorre_Caff%C3%A0.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{BBE013D8-6C99-4A68-9C58-485B1200302C}"/>
-    <hyperlink ref="A41" r:id="rId46" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
-    <hyperlink ref="A43" r:id="rId47" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
-    <hyperlink ref="A50" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Versailles%2C_sala_della_guerra.JPG/1280px-Versailles%2C_sala_della_guerra.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D449D19B-B1C2-400E-BD55-2614D5955C08}"/>
-    <hyperlink ref="A51" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg/960px-Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{52FF7A73-D4C9-49E4-9DA8-B4D571EE14DF}"/>
-    <hyperlink ref="A53" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/96/Grand_Conde_Louvre_MR3343.jpg/960px-Grand_Conde_Louvre_MR3343.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{753858EE-7014-4C19-962B-334F29852C17}"/>
-    <hyperlink ref="A47" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44F48270-0A28-4A76-9385-8855A77BD678}"/>
-    <hyperlink ref="A52" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/04/Le_Brun_Coysevox_Louvre_MR2156.jpg/960px-Le_Brun_Coysevox_Louvre_MR2156.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D9CA9CF-1153-4306-B07D-964A5665DA45}"/>
-    <hyperlink ref="A48" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/c/c7/Parc_de_Versailles%2C_parterre_de_Latone%2C_Nymphe_%C3%A0_la_coquille%2C_Auguste_Suchetet_d%27ap._Antoine_Coysevox_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{4F444DD7-66D7-4240-A90D-9160F097BD01}"/>
-    <hyperlink ref="A104" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
-    <hyperlink ref="A105" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/f/f8/Francesco_Mochi_Santa_Ver%C3%B3nica_1629-32_Vaticano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51585271-CD60-4E07-AF79-C53BF64AE7AA}"/>
-    <hyperlink ref="A55" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/b/bd/Rotterdam_standbeeld_Erasmus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{8D48BE19-49C1-4A59-9D87-2A838B718323}"/>
-    <hyperlink ref="A54" r:id="rId57" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A56" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{AB6F1DEE-2C0D-41BE-B003-BEFB7CAB6CC8}"/>
-    <hyperlink ref="A58" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Ecce_Homo%2C_Pedro_de_Mena.jpg/960px-Ecce_Homo%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FB6D3180-3C2E-4CBF-8013-D378E06E4034}"/>
-    <hyperlink ref="A59" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Malaga_Kathedrale_Der_Chor2.jpg/1280px-Malaga_Kathedrale_Der_Chor2.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CED5E9A6-7454-4078-8FB1-5584FFD1A281}"/>
-    <hyperlink ref="A60" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
-    <hyperlink ref="A63" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
-    <hyperlink ref="A66" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27AD6E4F-9048-4FB8-9892-514F003B2433}"/>
-    <hyperlink ref="A67" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21561D5A-F635-44FA-B9B8-22E9ADDC5BE9}"/>
-    <hyperlink ref="A68" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
-    <hyperlink ref="A69" r:id="rId66" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
-    <hyperlink ref="A70" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44E1C9A6-1000-4192-A274-9C346A8C2715}"/>
-    <hyperlink ref="A72" r:id="rId68" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId69" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId70" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId71" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A76" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg/1280px-Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D3EDC299-9112-42A3-AC1A-E1868B07456F}"/>
-    <hyperlink ref="A78" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
-    <hyperlink ref="A80" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A81" r:id="rId75" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
-    <hyperlink ref="A82" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E3EF5CEE-BA93-4E90-9F32-BB2AE6533916}"/>
-    <hyperlink ref="A83" r:id="rId77" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A85" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42716E0F-D168-43DB-A977-CA0E120A61B9}"/>
-    <hyperlink ref="A113" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
-    <hyperlink ref="A114" r:id="rId80" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
-    <hyperlink ref="A115" r:id="rId81" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
-    <hyperlink ref="A107" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
-    <hyperlink ref="A106" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A101" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
-    <hyperlink ref="A99" r:id="rId85" location="/media/File:Interior_of_San_Bernardo_alle_Terme_(Rome)_(8).jpg" xr:uid="{180C82DC-3EFB-4B76-81AA-1F5BD0CC67E2}"/>
-    <hyperlink ref="A95" r:id="rId86" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A96" r:id="rId87" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
-    <hyperlink ref="A97" r:id="rId88" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
-    <hyperlink ref="A88" r:id="rId89" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A89" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
-    <hyperlink ref="A92" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
-    <hyperlink ref="A94" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
-    <hyperlink ref="A20" r:id="rId93" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A90" r:id="rId13" xr:uid="{95FE0D7B-5987-40DE-8467-D8A326E0259A}"/>
+    <hyperlink ref="A18" r:id="rId14" xr:uid="{52D806BE-583E-4756-93E6-AD74999C00AC}"/>
+    <hyperlink ref="A19" r:id="rId15" xr:uid="{EAE4EEF8-50C9-43BE-A67E-15D4D4BE34DA}"/>
+    <hyperlink ref="A21" r:id="rId16" xr:uid="{AFD0A4C0-8F7A-4178-82C3-AFD16D7FE5CC}"/>
+    <hyperlink ref="A22" r:id="rId17" xr:uid="{9A91DB92-A1B0-49C9-9BCC-27031EFA890F}"/>
+    <hyperlink ref="A23" r:id="rId18" xr:uid="{DFE353BC-56F7-4D42-8CD1-85EA4544B4CE}"/>
+    <hyperlink ref="A24" r:id="rId19" xr:uid="{9D890162-34F6-4975-AAD5-6CD12099DDDE}"/>
+    <hyperlink ref="A25" r:id="rId20" xr:uid="{0ED88EB4-BABF-49DB-AB5B-FCFAAED767ED}"/>
+    <hyperlink ref="A26" r:id="rId21" xr:uid="{F9656E4A-4EEA-442F-A2B7-2E5D2C4F5F22}"/>
+    <hyperlink ref="A27" r:id="rId22" xr:uid="{4BCFDCBD-CC9B-4D94-858B-56E99635E9C6}"/>
+    <hyperlink ref="A28" r:id="rId23" xr:uid="{552FC9D9-D503-4CAE-95BD-0C1DAC2F4F79}"/>
+    <hyperlink ref="A29" r:id="rId24" xr:uid="{E8BB6FD5-348D-412D-95BE-D404EB88A673}"/>
+    <hyperlink ref="A30" r:id="rId25" xr:uid="{E2E167C5-FC46-4F31-A2BC-4EC7F6E7ECA5}"/>
+    <hyperlink ref="A31" r:id="rId26" xr:uid="{7C75B4CB-20E1-4905-8C14-2063E9B820F9}"/>
+    <hyperlink ref="A32" r:id="rId27" xr:uid="{9D8E6B76-7CC8-466C-89AA-502F66A34E3D}"/>
+    <hyperlink ref="A33" r:id="rId28" xr:uid="{DA167E93-42C9-46D9-85FC-837F9AD62D5F}"/>
+    <hyperlink ref="A34" r:id="rId29" xr:uid="{154341E7-D5CC-4270-B9CA-F65A443651D8}"/>
+    <hyperlink ref="A35" r:id="rId30" xr:uid="{B2E5CCEB-7D04-4870-AB3B-F8D6C72F1531}"/>
+    <hyperlink ref="A36" r:id="rId31" xr:uid="{00156A24-142C-4104-8DBB-283C3FA3092D}"/>
+    <hyperlink ref="A37" r:id="rId32" xr:uid="{727F34CB-527D-4DE9-8B7F-EF45B82026BE}"/>
+    <hyperlink ref="A3" r:id="rId33" xr:uid="{8CA3DECB-0705-4A9F-BEF1-C551CFE91E9B}"/>
+    <hyperlink ref="A4" r:id="rId34" xr:uid="{FBEF4C1B-17D1-4B4B-8B04-E515851CEF78}"/>
+    <hyperlink ref="A5" r:id="rId35" xr:uid="{EF8934FA-B822-4722-8B78-A558AE023196}"/>
+    <hyperlink ref="A6" r:id="rId36" xr:uid="{51CE317D-4CB7-4404-96ED-CCEFFA7B1104}"/>
+    <hyperlink ref="A84" r:id="rId37" xr:uid="{CBF93172-B1DD-4177-B523-2019EFC222F7}"/>
+    <hyperlink ref="A86" r:id="rId38" xr:uid="{A098C7D7-E966-4299-A05F-20B9B6DF1A82}"/>
+    <hyperlink ref="A87" r:id="rId39" xr:uid="{120C261F-E2E8-4EF3-854D-002040466357}"/>
+    <hyperlink ref="A77" r:id="rId40" xr:uid="{2A9F7667-9C72-415B-BDA0-7897AF200BC7}"/>
+    <hyperlink ref="A9" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{36A963F9-1859-4BB5-AF7B-1749A3316556}"/>
+    <hyperlink ref="A10" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{5D5A21F2-A411-44D1-BB9B-2C0C70D5524C}"/>
+    <hyperlink ref="A38" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1772B789-BFB5-4FDC-8337-89F821F64C32}"/>
+    <hyperlink ref="A41" r:id="rId44" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
+    <hyperlink ref="A43" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
+    <hyperlink ref="A51" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg/960px-Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{52FF7A73-D4C9-49E4-9DA8-B4D571EE14DF}"/>
+    <hyperlink ref="A47" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44F48270-0A28-4A76-9385-8855A77BD678}"/>
+    <hyperlink ref="A104" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
+    <hyperlink ref="A55" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/b/bd/Rotterdam_standbeeld_Erasmus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{8D48BE19-49C1-4A59-9D87-2A838B718323}"/>
+    <hyperlink ref="A54" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
+    <hyperlink ref="A56" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{AB6F1DEE-2C0D-41BE-B003-BEFB7CAB6CC8}"/>
+    <hyperlink ref="A58" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Ecce_Homo%2C_Pedro_de_Mena.jpg/960px-Ecce_Homo%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FB6D3180-3C2E-4CBF-8013-D378E06E4034}"/>
+    <hyperlink ref="A60" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
+    <hyperlink ref="A63" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
+    <hyperlink ref="A67" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21561D5A-F635-44FA-B9B8-22E9ADDC5BE9}"/>
+    <hyperlink ref="A68" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
+    <hyperlink ref="A69" r:id="rId57" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
+    <hyperlink ref="A72" r:id="rId58" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId59" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId60" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId61" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A76" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg/1280px-Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D3EDC299-9112-42A3-AC1A-E1868B07456F}"/>
+    <hyperlink ref="A78" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
+    <hyperlink ref="A80" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
+    <hyperlink ref="A81" r:id="rId65" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
+    <hyperlink ref="A83" r:id="rId66" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A113" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
+    <hyperlink ref="A114" r:id="rId68" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
+    <hyperlink ref="A115" r:id="rId69" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
+    <hyperlink ref="A107" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
+    <hyperlink ref="A106" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
+    <hyperlink ref="A101" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
+    <hyperlink ref="A95" r:id="rId73" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A96" r:id="rId74" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
+    <hyperlink ref="A97" r:id="rId75" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
+    <hyperlink ref="A88" r:id="rId76" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A89" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
+    <hyperlink ref="A92" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
+    <hyperlink ref="A94" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
+    <hyperlink ref="A20" r:id="rId80" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A99" r:id="rId82" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId84" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A65" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{85E997C9-0A16-4446-94B7-9D30CAA9F62C}"/>
+    <hyperlink ref="A48" r:id="rId86" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId87" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId88" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId89" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId90" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A105" r:id="rId92" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A103" r:id="rId93" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3956520E-7B46-4112-9F5B-CEDFDDAB89B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AE08DB-DEA2-48E3-85E5-69BDCCE9380A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="740">
   <si>
     <t>Image</t>
   </si>
@@ -987,12 +987,6 @@
     <t>Église Saint-Roch</t>
   </si>
   <si>
-    <t>"La Nativité (dite du Val-de-Grâce)"</t>
-  </si>
-  <si>
-    <t>https://commons.wikimedia.org/wiki/Category:Nicholas_Stone#/media/File:Tomb_of_Sir_Charles_Morrison_the_younger,_Watford_St_Mary.jpg</t>
-  </si>
-  <si>
     <t>Nicholas</t>
   </si>
   <si>
@@ -1500,9 +1494,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Angel_with_the_Superscription_by_Bernini.jpg/960px-Angel_with_the_Superscription_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Ange au cartouche (INRI)</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg/960px-Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1620,9 +1611,6 @@
     <t>Saint Philippe Neri et l'ange</t>
   </si>
   <si>
-    <t>1650s</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/Cenotaph_richelieu.jpg/1280px-Cenotaph_richelieu.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1833,9 +1821,6 @@
     <t>Bruxelles</t>
   </si>
   <si>
-    <t>Manneken-Pis (fonte définitive)</t>
-  </si>
-  <si>
     <t>Statue d'Érasme</t>
   </si>
   <si>
@@ -1965,12 +1950,6 @@
     <t>Rotterdam</t>
   </si>
   <si>
-    <t>Gaspard_Marsy,_Fontaine_de_l’Encelade,_Musée_national_des_châteaux_de_Versailles_et_de_Trianon,_Versailles,_France_(1675–1676)_-_20050429.jpg (900×1200)</t>
-  </si>
-  <si>
-    <t>960px-Ecce_Homo,_Pedro_de_Mena.jpg (960×1278)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cathédrale </t>
   </si>
   <si>
@@ -2040,9 +2019,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Gregorio_Fernandez-Piedad.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>1280px-Cristo_Yacente_(Segovia)._Gregorio_Fernández.jpg (1280×960)</t>
-  </si>
-  <si>
     <t>960px-Sant'agnese_in_agone,_interno_06.JPG (960×1280)</t>
   </si>
   <si>
@@ -2257,6 +2233,27 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4a/Annonciation_de_Francesco_Mochi.jpg/1280px-Annonciation_de_Francesco_Mochi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Ecce_Homo%2C_Pedro_de_Mena.jpg/960px-Ecce_Homo%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manneken-Pis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ange au cartouche </t>
+  </si>
+  <si>
+    <t>"La Nativité "</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg/1280px-Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2947,11 +2944,11 @@
         <v>26</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -2959,7 +2956,7 @@
         <v>27</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q2" s="4">
         <v>490</v>
@@ -2973,7 +2970,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>21</v>
@@ -2990,22 +2987,22 @@
         <v>24</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K3" s="39"/>
       <c r="L3" s="43" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
       <c r="O3" s="29" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P3" s="35"/>
       <c r="R3" s="19"/>
@@ -3019,7 +3016,7 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>21</v>
@@ -3036,17 +3033,17 @@
         <v>24</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="43" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
@@ -3072,7 +3069,7 @@
     </row>
     <row r="5" spans="1:21" ht="14.25" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>21</v>
@@ -3089,17 +3086,17 @@
         <v>24</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I5" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="43" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>21</v>
@@ -3137,17 +3134,17 @@
         <v>24</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="43" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
@@ -3195,7 +3192,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>317</v>
+        <v>737</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3272,7 +3269,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>313</v>
@@ -3288,18 +3285,18 @@
       <c r="G9" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="29" t="s">
-        <v>528</v>
+      <c r="H9" s="29">
+        <v>1650</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3318,7 +3315,7 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>125</v>
@@ -3335,7 +3332,7 @@
         <v>128</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>48</v>
@@ -3345,7 +3342,7 @@
       </c>
       <c r="K10" s="39"/>
       <c r="L10" s="43" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
@@ -3371,36 +3368,36 @@
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C11" s="30" t="s">
         <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="30" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>95</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -3431,7 +3428,7 @@
         <v>163</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="28" t="s">
@@ -3451,7 +3448,7 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -3459,7 +3456,7 @@
         <v>27</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>28</v>
@@ -3473,7 +3470,7 @@
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>162</v>
@@ -3482,7 +3479,7 @@
         <v>163</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="28" t="s">
@@ -3502,7 +3499,7 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -3510,7 +3507,7 @@
         <v>27</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>28</v>
@@ -3524,7 +3521,7 @@
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>162</v>
@@ -3533,7 +3530,7 @@
         <v>163</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="28" t="s">
@@ -3553,7 +3550,7 @@
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -3561,7 +3558,7 @@
         <v>27</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Q14" s="4">
         <v>109</v>
@@ -3587,7 +3584,7 @@
         <v>163</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="28" t="s">
@@ -3607,7 +3604,7 @@
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -3615,7 +3612,7 @@
         <v>27</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Q15" s="4">
         <v>279</v>
@@ -3635,7 +3632,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>162</v>
@@ -3644,7 +3641,7 @@
         <v>163</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="28" t="s">
@@ -3654,17 +3651,17 @@
         <v>164</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I16" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -3672,7 +3669,7 @@
         <v>40</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>28</v>
@@ -3686,7 +3683,7 @@
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>162</v>
@@ -3695,7 +3692,7 @@
         <v>163</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="28" t="s">
@@ -3711,19 +3708,19 @@
         <v>26</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="37" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>28</v>
@@ -3737,7 +3734,7 @@
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>162</v>
@@ -3746,7 +3743,7 @@
         <v>163</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="29" t="s">
@@ -3756,22 +3753,22 @@
         <v>164</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="43" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
       <c r="O18" s="29" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P18" s="35">
         <v>470</v>
@@ -3787,7 +3784,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>162</v>
@@ -3796,7 +3793,7 @@
         <v>163</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="29" t="s">
@@ -3809,14 +3806,14 @@
         <v>315</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J19" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K19" s="39"/>
       <c r="L19" s="43" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -3842,7 +3839,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -3851,7 +3848,7 @@
         <v>163</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="29" t="s">
@@ -3861,24 +3858,24 @@
         <v>164</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="43" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="19" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P20" s="35">
         <v>900</v>
@@ -3894,7 +3891,7 @@
     </row>
     <row r="21" spans="1:21" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>162</v>
@@ -3903,7 +3900,7 @@
         <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="29" t="s">
@@ -3913,22 +3910,22 @@
         <v>164</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="43" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
       <c r="O21" s="29" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P21" s="35">
         <v>700</v>
@@ -3944,7 +3941,7 @@
     </row>
     <row r="22" spans="1:21" ht="15" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>162</v>
@@ -3953,7 +3950,7 @@
         <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="29" t="s">
@@ -3969,16 +3966,16 @@
         <v>26</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="K22" s="39"/>
       <c r="L22" s="43" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
       <c r="O22" s="29" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P22" s="35">
         <v>1269</v>
@@ -3994,7 +3991,7 @@
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>162</v>
@@ -4003,7 +4000,7 @@
         <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="29" t="s">
@@ -4013,7 +4010,7 @@
         <v>164</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>26</v>
@@ -4023,7 +4020,7 @@
       </c>
       <c r="K23" s="39"/>
       <c r="L23" s="43" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
@@ -4044,7 +4041,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>162</v>
@@ -4053,7 +4050,7 @@
         <v>163</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="29" t="s">
@@ -4063,7 +4060,7 @@
         <v>164</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>26</v>
@@ -4073,7 +4070,7 @@
       </c>
       <c r="K24" s="39"/>
       <c r="L24" s="43" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="19"/>
@@ -4094,7 +4091,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B25" s="29" t="s">
         <v>162</v>
@@ -4103,7 +4100,7 @@
         <v>163</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="29" t="s">
@@ -4113,19 +4110,19 @@
         <v>164</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J25" s="43" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="L25" s="43" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
@@ -4151,7 +4148,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>162</v>
@@ -4160,7 +4157,7 @@
         <v>163</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="29" t="s">
@@ -4170,22 +4167,22 @@
         <v>164</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K26" s="39"/>
       <c r="L26" s="43" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
       <c r="O26" s="29" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P26" s="35">
         <v>1677</v>
@@ -4206,7 +4203,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>162</v>
@@ -4215,7 +4212,7 @@
         <v>163</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="29" t="s">
@@ -4225,17 +4222,17 @@
         <v>164</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M27" s="19"/>
       <c r="N27" s="19"/>
@@ -4261,7 +4258,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>162</v>
@@ -4270,7 +4267,7 @@
         <v>163</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="29" t="s">
@@ -4280,17 +4277,17 @@
         <v>164</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>488</v>
+        <v>736</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4316,7 +4313,7 @@
     </row>
     <row r="29" spans="1:21" ht="15" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>162</v>
@@ -4325,7 +4322,7 @@
         <v>163</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="29" t="s">
@@ -4335,17 +4332,17 @@
         <v>164</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="K29" s="39"/>
       <c r="L29" s="43" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
@@ -4371,7 +4368,7 @@
     </row>
     <row r="30" spans="1:21" ht="15" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B30" s="29" t="s">
         <v>162</v>
@@ -4380,7 +4377,7 @@
         <v>163</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="29" t="s">
@@ -4390,22 +4387,22 @@
         <v>164</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K30" s="39"/>
       <c r="L30" s="43" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="29" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P30" s="35">
         <v>200</v>
@@ -4424,7 +4421,7 @@
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>162</v>
@@ -4433,7 +4430,7 @@
         <v>163</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="29" t="s">
@@ -4443,17 +4440,17 @@
         <v>164</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>81</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K31" s="39"/>
       <c r="L31" s="43" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
@@ -4474,7 +4471,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>162</v>
@@ -4483,7 +4480,7 @@
         <v>163</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="29" t="s">
@@ -4493,7 +4490,7 @@
         <v>164</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>48</v>
@@ -4503,7 +4500,7 @@
       </c>
       <c r="K32" s="39"/>
       <c r="L32" s="43" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4529,7 +4526,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>162</v>
@@ -4538,7 +4535,7 @@
         <v>163</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E33" s="19"/>
       <c r="F33" s="29" t="s">
@@ -4548,17 +4545,17 @@
         <v>164</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="K33" s="39"/>
       <c r="L33" s="43" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4584,7 +4581,7 @@
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>162</v>
@@ -4593,7 +4590,7 @@
         <v>163</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E34" s="19"/>
       <c r="F34" s="29" t="s">
@@ -4603,17 +4600,17 @@
         <v>164</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K34" s="39"/>
       <c r="L34" s="43" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
@@ -4634,7 +4631,7 @@
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>162</v>
@@ -4643,7 +4640,7 @@
         <v>163</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E35" s="19"/>
       <c r="F35" s="29" t="s">
@@ -4653,17 +4650,17 @@
         <v>164</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="K35" s="39"/>
       <c r="L35" s="43" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -4684,7 +4681,7 @@
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>162</v>
@@ -4693,7 +4690,7 @@
         <v>163</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E36" s="19"/>
       <c r="F36" s="29" t="s">
@@ -4703,17 +4700,17 @@
         <v>164</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="K36" s="39"/>
       <c r="L36" s="43" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="M36" s="19"/>
       <c r="N36" s="19"/>
@@ -4739,7 +4736,7 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>162</v>
@@ -4748,7 +4745,7 @@
         <v>163</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="29" t="s">
@@ -4758,22 +4755,22 @@
         <v>164</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="K37" s="39"/>
       <c r="L37" s="43" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
       <c r="O37" s="29" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P37" s="35">
         <v>150</v>
@@ -4792,18 +4789,18 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
       <c r="F38" s="29" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G38" s="29" t="s">
         <v>34</v>
@@ -4815,11 +4812,11 @@
         <v>26</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="43" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
@@ -4875,7 +4872,7 @@
         <v>84</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
@@ -4891,7 +4888,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -4962,10 +4959,10 @@
         <v>34</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="3" t="s">
@@ -5048,36 +5045,36 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="29" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>314</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M43" s="19"/>
       <c r="N43" s="19"/>
@@ -5098,13 +5095,13 @@
     </row>
     <row r="44" spans="1:21" ht="15" customHeight="1">
       <c r="A44" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="C44" s="30" t="s">
         <v>327</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>329</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -5112,10 +5109,10 @@
         <v>87</v>
       </c>
       <c r="G44" s="30" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H44" s="30" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I44" s="30" t="s">
         <v>48</v>
@@ -5125,7 +5122,7 @@
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -5153,7 +5150,7 @@
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>43</v>
@@ -5179,10 +5176,10 @@
         <v>49</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -5190,10 +5187,10 @@
         <v>27</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R45" s="4">
         <v>128</v>
@@ -5231,10 +5228,10 @@
         <v>49</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -5242,10 +5239,10 @@
         <v>27</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R46" s="4">
         <v>128</v>
@@ -5259,7 +5256,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5276,14 +5273,14 @@
         <v>46</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -5302,7 +5299,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5319,14 +5316,14 @@
         <v>46</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -5374,10 +5371,10 @@
         <v>53</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -5385,7 +5382,7 @@
         <v>27</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q49" s="4">
         <v>75</v>
@@ -5400,7 +5397,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5417,22 +5414,22 @@
         <v>46</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="I50" s="29"/>
       <c r="J50" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
       <c r="O50" s="29" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P50" s="35">
         <v>390</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5470,22 +5467,22 @@
         <v>46</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>48</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="43" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
       <c r="O51" s="29" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P51" s="35">
         <v>400</v>
@@ -5501,7 +5498,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5528,7 +5525,7 @@
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="43" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5554,7 +5551,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5571,7 +5568,7 @@
         <v>46</v>
       </c>
       <c r="H53" s="29" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="I53" s="29" t="s">
         <v>48</v>
@@ -5581,7 +5578,7 @@
       </c>
       <c r="K53" s="39"/>
       <c r="L53" s="43" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="M53" s="19"/>
       <c r="N53" s="19"/>
@@ -5613,7 +5610,7 @@
         <v>218</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -5658,13 +5655,13 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>218</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
@@ -5675,15 +5672,15 @@
         <v>220</v>
       </c>
       <c r="H55" s="31" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
       <c r="L55" s="44" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
@@ -5709,13 +5706,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>643</v>
+        <v>738</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5726,15 +5723,15 @@
         <v>147</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I56" s="31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J56" s="44"/>
       <c r="K56" s="40"/>
       <c r="L56" s="44" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
@@ -5760,13 +5757,13 @@
     </row>
     <row r="57" spans="1:21" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
@@ -5774,10 +5771,10 @@
         <v>111</v>
       </c>
       <c r="G57" s="32" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I57" s="32" t="s">
         <v>193</v>
@@ -5787,7 +5784,7 @@
       </c>
       <c r="K57" s="20"/>
       <c r="L57" s="22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
@@ -5795,7 +5792,7 @@
         <v>36</v>
       </c>
       <c r="P57" s="20" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="Q57" s="2">
         <v>55</v>
@@ -5815,13 +5812,13 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>644</v>
+        <v>733</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
@@ -5829,10 +5826,10 @@
         <v>111</v>
       </c>
       <c r="G58" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H58" s="31" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="I58" s="32" t="s">
         <v>193</v>
@@ -5842,7 +5839,7 @@
       </c>
       <c r="K58" s="40"/>
       <c r="L58" s="44" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
@@ -5868,13 +5865,13 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
@@ -5882,29 +5879,29 @@
         <v>111</v>
       </c>
       <c r="G59" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H59" s="31" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="I59" s="31" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
       <c r="O59" s="31" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5917,13 +5914,13 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
@@ -5931,20 +5928,20 @@
         <v>111</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H60" s="31">
         <v>1663</v>
       </c>
       <c r="I60" s="31" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5971,7 +5968,7 @@
         <v>254</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
@@ -5992,7 +5989,7 @@
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -6003,7 +6000,7 @@
         <v>47</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="R61" s="20">
         <v>27.5</v>
@@ -6071,7 +6068,7 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>294</v>
@@ -6098,7 +6095,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6173,7 +6170,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6190,17 +6187,17 @@
         <v>134</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I65" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K65" s="23"/>
       <c r="L65" s="23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M65" s="21"/>
       <c r="N65" s="21"/>
@@ -6221,7 +6218,7 @@
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
       <c r="A66" s="51" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>125</v>
@@ -6244,11 +6241,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6272,13 +6269,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6289,15 +6286,15 @@
         <v>24</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>599</v>
+        <v>735</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6318,13 +6315,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6335,17 +6332,17 @@
         <v>288</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="J68" s="52" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6366,18 +6363,18 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="31" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G69" s="31" t="s">
         <v>298</v>
@@ -6389,18 +6386,18 @@
         <v>26</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
       <c r="O69" s="31" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P69" s="36">
         <v>550</v>
@@ -6416,13 +6413,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6430,20 +6427,20 @@
         <v>175</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="I70" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6540,7 +6537,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6560,7 +6557,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6583,11 +6580,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6635,7 +6632,7 @@
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="7" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="M74" s="22"/>
       <c r="N74" s="22" t="s">
@@ -6665,7 +6662,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6676,13 +6673,13 @@
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="31" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G75" s="31" t="s">
         <v>191</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I75" s="31" t="s">
         <v>193</v>
@@ -6692,7 +6689,7 @@
       </c>
       <c r="K75" s="40"/>
       <c r="L75" s="44" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="M75" s="11"/>
       <c r="N75" s="11"/>
@@ -6718,7 +6715,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>668</v>
+        <v>739</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6729,23 +6726,23 @@
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="31" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G76" s="31" t="s">
         <v>191</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="44" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="M76" s="11"/>
       <c r="N76" s="11"/>
@@ -6771,7 +6768,7 @@
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B77" s="31" t="s">
         <v>104</v>
@@ -6796,12 +6793,12 @@
       <c r="J77" s="44"/>
       <c r="K77" s="40"/>
       <c r="L77" s="44" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="M77" s="11"/>
       <c r="N77" s="11"/>
       <c r="O77" s="31" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="P77" s="36"/>
       <c r="R77" s="11"/>
@@ -6815,7 +6812,7 @@
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="B78" s="31" t="s">
         <v>104</v>
@@ -6838,11 +6835,11 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M78" s="11"/>
       <c r="N78" s="11"/>
@@ -6912,7 +6909,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6929,17 +6926,17 @@
         <v>183</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I80" s="31" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
@@ -6960,13 +6957,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6974,22 +6971,22 @@
         <v>286</v>
       </c>
       <c r="G81" s="31" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I81" s="31" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6997,7 +6994,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -7010,7 +7007,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7027,22 +7024,22 @@
         <v>200</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I82" s="31" t="s">
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
       <c r="O82" s="31" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="P82" s="36"/>
       <c r="R82" s="11"/>
@@ -7081,7 +7078,7 @@
       <c r="J83" s="23"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M83" s="21"/>
       <c r="N83" s="21"/>
@@ -7089,7 +7086,7 @@
         <v>27</v>
       </c>
       <c r="P83" s="21" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="R83" s="21"/>
       <c r="S83" s="26"/>
@@ -7102,7 +7099,7 @@
     </row>
     <row r="84" spans="1:21" ht="15" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B84" s="31" t="s">
         <v>125</v>
@@ -7129,7 +7126,7 @@
       </c>
       <c r="K84" s="40"/>
       <c r="L84" s="44" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
@@ -7157,7 +7154,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7174,17 +7171,17 @@
         <v>88</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I85" s="31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
@@ -7210,7 +7207,7 @@
     </row>
     <row r="86" spans="1:21" ht="15" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B86" s="31" t="s">
         <v>125</v>
@@ -7230,12 +7227,12 @@
         <v>148</v>
       </c>
       <c r="I86" s="31" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J86" s="44"/>
       <c r="K86" s="40"/>
       <c r="L86" s="44" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="M86" s="11"/>
       <c r="N86" s="11"/>
@@ -7254,7 +7251,7 @@
     </row>
     <row r="87" spans="1:21" ht="15" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B87" s="31" t="s">
         <v>125</v>
@@ -7271,17 +7268,17 @@
         <v>88</v>
       </c>
       <c r="H87" s="31" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I87" s="31"/>
       <c r="J87" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7307,7 +7304,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7358,7 +7355,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7381,11 +7378,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7404,24 +7401,24 @@
     </row>
     <row r="90" spans="1:21" ht="15" customHeight="1">
       <c r="A90" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="C90" s="32" t="s">
         <v>375</v>
-      </c>
-      <c r="B90" s="32" t="s">
-        <v>376</v>
-      </c>
-      <c r="C90" s="32" t="s">
-        <v>377</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="32" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G90" s="32" t="s">
         <v>87</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I90" s="32" t="s">
         <v>48</v>
@@ -7431,7 +7428,7 @@
       </c>
       <c r="K90" s="20"/>
       <c r="L90" s="22" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M90" s="22"/>
       <c r="N90" s="22"/>
@@ -7439,7 +7436,7 @@
         <v>40</v>
       </c>
       <c r="P90" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="20"/>
@@ -7502,13 +7499,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7516,20 +7513,20 @@
         <v>156</v>
       </c>
       <c r="G92" s="31" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="I92" s="31" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="J92" s="53" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7573,7 +7570,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7595,13 +7592,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7612,17 +7609,17 @@
         <v>87</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I94" s="31" t="s">
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
@@ -7641,32 +7638,32 @@
     </row>
     <row r="95" spans="1:21" ht="15" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B95" s="32" t="s">
         <v>234</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="32" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G95" s="32" t="s">
         <v>39</v>
       </c>
       <c r="H95" s="32" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I95" s="32"/>
       <c r="J95" s="23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K95" s="20"/>
       <c r="L95" s="22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M95" s="22"/>
       <c r="N95" s="22"/>
@@ -7688,34 +7685,34 @@
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
       <c r="A96" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B96" s="32" t="s">
         <v>234</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="G96" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="H96" s="32" t="s">
         <v>353</v>
-      </c>
-      <c r="G96" s="32" t="s">
-        <v>354</v>
-      </c>
-      <c r="H96" s="32" t="s">
-        <v>355</v>
       </c>
       <c r="I96" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K96" s="20"/>
       <c r="L96" s="22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M96" s="22"/>
       <c r="N96" s="22"/>
@@ -7723,7 +7720,7 @@
         <v>27</v>
       </c>
       <c r="P96" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" s="20"/>
@@ -7737,34 +7734,34 @@
     </row>
     <row r="97" spans="1:21" ht="15" customHeight="1">
       <c r="A97" s="46" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B97" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D97" s="11"/>
       <c r="E97" s="11"/>
       <c r="F97" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="G97" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="H97" s="31" t="s">
         <v>353</v>
-      </c>
-      <c r="G97" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="H97" s="31" t="s">
-        <v>355</v>
       </c>
       <c r="I97" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J97" s="23" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K97" s="40"/>
       <c r="L97" s="44" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M97" s="11"/>
       <c r="N97" s="11"/>
@@ -7783,13 +7780,13 @@
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1">
       <c r="A98" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="B98" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="32" t="s">
         <v>380</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="C98" s="32" t="s">
-        <v>382</v>
       </c>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
@@ -7800,17 +7797,17 @@
         <v>191</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I98" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J98" s="23" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K98" s="20"/>
       <c r="L98" s="22" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M98" s="22"/>
       <c r="N98" s="22"/>
@@ -7818,7 +7815,7 @@
         <v>27</v>
       </c>
       <c r="P98" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" s="20"/>
@@ -7834,39 +7831,39 @@
     </row>
     <row r="99" spans="1:21" ht="15" customHeight="1">
       <c r="A99" s="49" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B99" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
       <c r="F99" s="31" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G99" s="31" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="H99" s="31" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I99" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J99" s="44" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="K99" s="40"/>
       <c r="L99" s="44" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="M99" s="11"/>
       <c r="N99" s="11"/>
       <c r="O99" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P99" s="36">
         <v>350</v>
@@ -7929,7 +7926,7 @@
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1">
       <c r="A101" s="46" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B101" s="31" t="s">
         <v>145</v>
@@ -7954,7 +7951,7 @@
       </c>
       <c r="K101" s="40"/>
       <c r="L101" s="44" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="M101" s="11"/>
       <c r="N101" s="11"/>
@@ -8000,7 +7997,7 @@
       </c>
       <c r="K102" s="20"/>
       <c r="L102" s="7" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="M102" s="22"/>
       <c r="N102" s="22" t="s">
@@ -8024,7 +8021,7 @@
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
       <c r="A103" s="17" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="B103" s="33" t="s">
         <v>121</v>
@@ -8041,15 +8038,15 @@
         <v>24</v>
       </c>
       <c r="H103" s="33" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I103" s="33" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
       <c r="L103" s="23" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M103" s="21"/>
       <c r="N103" s="21"/>
@@ -8057,7 +8054,7 @@
         <v>27</v>
       </c>
       <c r="P103" s="21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R103" s="21"/>
       <c r="S103" s="26"/>
@@ -8070,7 +8067,7 @@
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B104" s="31" t="s">
         <v>121</v>
@@ -8087,15 +8084,15 @@
         <v>24</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I104" s="31" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="J104" s="44"/>
       <c r="K104" s="40"/>
       <c r="L104" s="44" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M104" s="11"/>
       <c r="N104" s="11"/>
@@ -8116,7 +8113,7 @@
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="B105" s="31" t="s">
         <v>121</v>
@@ -8139,11 +8136,11 @@
         <v>26</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K105" s="40"/>
       <c r="L105" s="44" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="M105" s="11"/>
       <c r="N105" s="11"/>
@@ -8164,13 +8161,13 @@
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -8181,17 +8178,17 @@
         <v>255</v>
       </c>
       <c r="H106" s="31" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="I106" s="31" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
@@ -8199,7 +8196,7 @@
         <v>36</v>
       </c>
       <c r="P106" s="36" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="R106" s="11"/>
       <c r="S106" s="12"/>
@@ -8212,13 +8209,13 @@
     </row>
     <row r="107" spans="1:21" ht="15" customHeight="1">
       <c r="A107" s="46" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
@@ -8229,17 +8226,17 @@
         <v>255</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="I107" s="31" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J107" s="44" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="K107" s="40"/>
       <c r="L107" s="44" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="M107" s="11"/>
       <c r="N107" s="11"/>
@@ -8403,13 +8400,13 @@
     </row>
     <row r="111" spans="1:21" ht="15" customHeight="1">
       <c r="A111" s="15" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B111" s="33" t="s">
         <v>234</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
@@ -8420,17 +8417,17 @@
         <v>297</v>
       </c>
       <c r="H111" s="33" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J111" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K111" s="23"/>
       <c r="L111" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M111" s="21"/>
       <c r="N111" s="21"/>
@@ -8438,13 +8435,13 @@
         <v>27</v>
       </c>
       <c r="P111" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q111" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="R111" s="21" t="s">
         <v>417</v>
-      </c>
-      <c r="Q111" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="R111" s="21" t="s">
-        <v>419</v>
       </c>
       <c r="S111" s="26"/>
       <c r="T111" s="4">
@@ -8456,13 +8453,13 @@
     </row>
     <row r="112" spans="1:21" ht="15" customHeight="1">
       <c r="A112" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B112" s="33" t="s">
         <v>234</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D112" s="21"/>
       <c r="E112" s="21"/>
@@ -8473,17 +8470,17 @@
         <v>297</v>
       </c>
       <c r="H112" s="33" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I112" s="33" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J112" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K112" s="23"/>
       <c r="L112" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M112" s="21"/>
       <c r="N112" s="21"/>
@@ -8509,13 +8506,13 @@
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="B113" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="11"/>
@@ -8526,17 +8523,17 @@
         <v>297</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="I113" s="31" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J113" s="44" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="K113" s="40"/>
       <c r="L113" s="44" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
@@ -8555,13 +8552,13 @@
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="B114" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="11"/>
@@ -8572,7 +8569,7 @@
         <v>297</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="I114" s="31" t="s">
         <v>48</v>
@@ -8606,13 +8603,13 @@
     </row>
     <row r="115" spans="1:21" ht="15" customHeight="1">
       <c r="A115" s="46" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B115" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="11"/>
@@ -8623,17 +8620,17 @@
         <v>297</v>
       </c>
       <c r="H115" s="31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I115" s="31" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="J115" s="44" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="K115" s="40"/>
       <c r="L115" s="44" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="M115" s="11"/>
       <c r="N115" s="11"/>
@@ -8679,7 +8676,7 @@
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
@@ -8777,7 +8774,7 @@
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
@@ -8797,24 +8794,24 @@
     </row>
     <row r="119" spans="1:21" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="B119" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="C119" s="32" t="s">
         <v>387</v>
-      </c>
-      <c r="B119" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="C119" s="32" t="s">
-        <v>389</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="32" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G119" s="32" t="s">
         <v>287</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I119" s="32"/>
       <c r="J119" s="23" t="s">
@@ -8822,7 +8819,7 @@
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
@@ -8944,10 +8941,10 @@
     </row>
     <row r="122" spans="1:21" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C122" s="32" t="s">
         <v>284</v>
@@ -8958,20 +8955,20 @@
         <v>58</v>
       </c>
       <c r="G122" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="H122" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="I122" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="H122" s="32" t="s">
+      <c r="J122" s="23" t="s">
         <v>341</v>
-      </c>
-      <c r="I122" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="J122" s="23" t="s">
-        <v>343</v>
       </c>
       <c r="K122" s="20"/>
       <c r="L122" s="22" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
@@ -9040,13 +9037,13 @@
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
       <c r="A124" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="C124" s="32" t="s">
         <v>394</v>
-      </c>
-      <c r="B124" s="32" t="s">
-        <v>395</v>
-      </c>
-      <c r="C124" s="32" t="s">
-        <v>396</v>
       </c>
       <c r="D124" s="20"/>
       <c r="E124" s="20"/>
@@ -9057,22 +9054,22 @@
         <v>73</v>
       </c>
       <c r="H124" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="I124" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="J124" s="23" t="s">
         <v>397</v>
-      </c>
-      <c r="I124" s="32" t="s">
-        <v>398</v>
-      </c>
-      <c r="J124" s="23" t="s">
-        <v>399</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="22" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="32" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P124" s="20"/>
       <c r="Q124" s="2"/>
@@ -9088,35 +9085,35 @@
       </c>
     </row>
     <row r="125" spans="1:21" ht="15" customHeight="1">
-      <c r="A125" s="15" t="s">
+      <c r="A125" s="17" t="s">
+        <v>734</v>
+      </c>
+      <c r="B125" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C125" s="32" t="s">
         <v>318</v>
-      </c>
-      <c r="B125" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="C125" s="32" t="s">
-        <v>320</v>
       </c>
       <c r="D125" s="20"/>
       <c r="E125" s="20"/>
       <c r="F125" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="G125" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="H125" s="32" t="s">
         <v>321</v>
       </c>
-      <c r="G125" s="32" t="s">
+      <c r="I125" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="H125" s="32" t="s">
+      <c r="J125" s="23" t="s">
         <v>323</v>
-      </c>
-      <c r="I125" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="J125" s="23" t="s">
-        <v>325</v>
       </c>
       <c r="K125" s="20"/>
       <c r="L125" s="22" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
@@ -9160,10 +9157,10 @@
         <v>53</v>
       </c>
       <c r="K126" s="20" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M126" s="22"/>
       <c r="N126" s="22"/>
@@ -9191,13 +9188,13 @@
     </row>
     <row r="127" spans="1:21" ht="15" customHeight="1">
       <c r="A127" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="B127" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="C127" s="32" t="s">
         <v>369</v>
-      </c>
-      <c r="B127" s="32" t="s">
-        <v>370</v>
-      </c>
-      <c r="C127" s="32" t="s">
-        <v>371</v>
       </c>
       <c r="D127" s="20"/>
       <c r="E127" s="20"/>
@@ -9205,20 +9202,20 @@
         <v>58</v>
       </c>
       <c r="G127" s="32" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H127" s="32" t="s">
         <v>147</v>
       </c>
       <c r="I127" s="32" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J127" s="23" t="s">
         <v>223</v>
       </c>
       <c r="K127" s="20"/>
       <c r="L127" s="22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M127" s="22"/>
       <c r="N127" s="22"/>
@@ -9307,10 +9304,10 @@
         <v>271</v>
       </c>
       <c r="I129" s="31" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="J129" s="23" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="K129" s="20"/>
       <c r="L129" s="22" t="s">
@@ -11083,49 +11080,50 @@
     <hyperlink ref="A104" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
     <hyperlink ref="A55" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/b/bd/Rotterdam_standbeeld_Erasmus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{8D48BE19-49C1-4A59-9D87-2A838B718323}"/>
     <hyperlink ref="A54" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A56" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{AB6F1DEE-2C0D-41BE-B003-BEFB7CAB6CC8}"/>
-    <hyperlink ref="A58" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Ecce_Homo%2C_Pedro_de_Mena.jpg/960px-Ecce_Homo%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FB6D3180-3C2E-4CBF-8013-D378E06E4034}"/>
-    <hyperlink ref="A60" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
-    <hyperlink ref="A63" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
-    <hyperlink ref="A67" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21561D5A-F635-44FA-B9B8-22E9ADDC5BE9}"/>
-    <hyperlink ref="A68" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
-    <hyperlink ref="A69" r:id="rId57" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
-    <hyperlink ref="A72" r:id="rId58" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId59" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId60" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId61" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A76" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg/1280px-Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D3EDC299-9112-42A3-AC1A-E1868B07456F}"/>
-    <hyperlink ref="A78" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
-    <hyperlink ref="A80" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A81" r:id="rId65" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
-    <hyperlink ref="A83" r:id="rId66" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A113" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
-    <hyperlink ref="A114" r:id="rId68" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
-    <hyperlink ref="A115" r:id="rId69" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
-    <hyperlink ref="A107" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
-    <hyperlink ref="A106" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A101" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
-    <hyperlink ref="A95" r:id="rId73" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A96" r:id="rId74" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
-    <hyperlink ref="A97" r:id="rId75" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
-    <hyperlink ref="A88" r:id="rId76" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A89" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
-    <hyperlink ref="A92" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
-    <hyperlink ref="A94" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
-    <hyperlink ref="A20" r:id="rId80" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A99" r:id="rId82" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId84" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A65" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{85E997C9-0A16-4446-94B7-9D30CAA9F62C}"/>
-    <hyperlink ref="A48" r:id="rId86" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId87" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId88" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId89" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId90" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A105" r:id="rId92" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A103" r:id="rId93" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A60" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
+    <hyperlink ref="A63" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
+    <hyperlink ref="A67" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21561D5A-F635-44FA-B9B8-22E9ADDC5BE9}"/>
+    <hyperlink ref="A68" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
+    <hyperlink ref="A69" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
+    <hyperlink ref="A72" r:id="rId56" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId57" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId58" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A78" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
+    <hyperlink ref="A80" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
+    <hyperlink ref="A81" r:id="rId62" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
+    <hyperlink ref="A83" r:id="rId63" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A113" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
+    <hyperlink ref="A114" r:id="rId65" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
+    <hyperlink ref="A115" r:id="rId66" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
+    <hyperlink ref="A107" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
+    <hyperlink ref="A106" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
+    <hyperlink ref="A101" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
+    <hyperlink ref="A95" r:id="rId70" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A96" r:id="rId71" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
+    <hyperlink ref="A97" r:id="rId72" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
+    <hyperlink ref="A88" r:id="rId73" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A89" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
+    <hyperlink ref="A92" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
+    <hyperlink ref="A94" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
+    <hyperlink ref="A20" r:id="rId77" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A99" r:id="rId79" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId81" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A65" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{85E997C9-0A16-4446-94B7-9D30CAA9F62C}"/>
+    <hyperlink ref="A48" r:id="rId83" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId84" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId85" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId86" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId87" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A105" r:id="rId89" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A103" r:id="rId90" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId91" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A125" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId93" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId94" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AE08DB-DEA2-48E3-85E5-69BDCCE9380A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8E3B8D-FA86-4AE3-9DD8-ED8294CFEC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1983,9 +1983,6 @@
     <t>Santa Maria dell'Anima</t>
   </si>
   <si>
-    <t>960px-Bruxelles_Manneken_Pis.jpg (960×1450)</t>
-  </si>
-  <si>
     <t>960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg (960×1218)</t>
   </si>
   <si>
@@ -2196,9 +2193,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/7/70/Melchiorre_Caff%C3%A0.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/Parc_de_Versailles%2C_parterre_de_Latone%2C_Nymphe_%C3%A0_la_coquille%2C_Auguste_Suchetet_d%27ap._Antoine_Coysevox_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -2254,6 +2248,12 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg/1280px-Cristo_Yacente_%28Segovia%29._Gregorio_Fern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg/1920px-Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3292,11 +3292,11 @@
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -4228,7 +4228,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
@@ -4283,11 +4283,11 @@
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4795,7 +4795,7 @@
         <v>574</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -4888,7 +4888,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -5051,7 +5051,7 @@
         <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5706,13 +5706,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B58" s="31" t="s">
         <v>332</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>332</v>
@@ -5961,7 +5961,7 @@
       </c>
     </row>
     <row r="61" spans="1:21" ht="15" customHeight="1">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="17" t="s">
         <v>253</v>
       </c>
       <c r="B61" s="32" t="s">
@@ -6118,7 +6118,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="15" customHeight="1">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="17" t="s">
         <v>131</v>
       </c>
       <c r="B64" s="32" t="s">
@@ -6170,7 +6170,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>720</v>
+        <v>739</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6269,13 +6269,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>649</v>
+        <v>738</v>
       </c>
       <c r="B67" s="31" t="s">
         <v>593</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6294,7 +6294,7 @@
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6315,13 +6315,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B68" s="29" t="s">
         <v>596</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6338,11 +6338,11 @@
         <v>592</v>
       </c>
       <c r="J68" s="52" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6363,13 +6363,13 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B69" s="31" t="s">
         <v>575</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
@@ -6392,7 +6392,7 @@
         <v>409</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
@@ -6413,13 +6413,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6436,11 +6436,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6580,11 +6580,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6812,7 +6812,7 @@
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B78" s="31" t="s">
         <v>104</v>
@@ -6835,7 +6835,7 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
@@ -6909,7 +6909,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6932,7 +6932,7 @@
         <v>534</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
@@ -6957,13 +6957,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B81" s="31" t="s">
         <v>577</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6980,13 +6980,13 @@
         <v>534</v>
       </c>
       <c r="J81" s="44" t="s">
+        <v>665</v>
+      </c>
+      <c r="K81" s="40" t="s">
+        <v>664</v>
+      </c>
+      <c r="L81" s="44" t="s">
         <v>666</v>
-      </c>
-      <c r="K81" s="40" t="s">
-        <v>665</v>
-      </c>
-      <c r="L81" s="44" t="s">
-        <v>667</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6994,7 +6994,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7030,11 +7030,11 @@
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7177,7 +7177,7 @@
         <v>461</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
@@ -7275,10 +7275,10 @@
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="L87" s="44" t="s">
         <v>702</v>
-      </c>
-      <c r="L87" s="44" t="s">
-        <v>703</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7355,7 +7355,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7378,11 +7378,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7499,13 +7499,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B92" s="31" t="s">
         <v>587</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7522,11 +7522,11 @@
         <v>586</v>
       </c>
       <c r="J92" s="53" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7592,13 +7592,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B94" s="31" t="s">
         <v>590</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7615,7 +7615,7 @@
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
@@ -7734,7 +7734,7 @@
     </row>
     <row r="97" spans="1:21" ht="15" customHeight="1">
       <c r="A97" s="46" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B97" s="31" t="s">
         <v>234</v>
@@ -7831,13 +7831,13 @@
     </row>
     <row r="99" spans="1:21" ht="15" customHeight="1">
       <c r="A99" s="49" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B99" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
@@ -7854,11 +7854,11 @@
         <v>26</v>
       </c>
       <c r="J99" s="44" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K99" s="40"/>
       <c r="L99" s="44" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M99" s="11"/>
       <c r="N99" s="11"/>
@@ -7926,7 +7926,7 @@
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1">
       <c r="A101" s="46" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B101" s="31" t="s">
         <v>145</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K101" s="40"/>
       <c r="L101" s="44" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="M101" s="11"/>
       <c r="N101" s="11"/>
@@ -8021,7 +8021,7 @@
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
       <c r="A103" s="17" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B103" s="33" t="s">
         <v>121</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B105" s="31" t="s">
         <v>121</v>
@@ -8161,13 +8161,13 @@
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B106" s="31" t="s">
         <v>583</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -8184,7 +8184,7 @@
         <v>550</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
@@ -8196,7 +8196,7 @@
         <v>36</v>
       </c>
       <c r="P106" s="36" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="R106" s="11"/>
       <c r="S106" s="12"/>
@@ -8209,13 +8209,13 @@
     </row>
     <row r="107" spans="1:21" ht="15" customHeight="1">
       <c r="A107" s="46" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
@@ -8232,7 +8232,7 @@
         <v>550</v>
       </c>
       <c r="J107" s="44" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K107" s="40"/>
       <c r="L107" s="44" t="s">
@@ -8506,7 +8506,7 @@
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B113" s="31" t="s">
         <v>234</v>
@@ -8529,11 +8529,11 @@
         <v>413</v>
       </c>
       <c r="J113" s="44" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="K113" s="40"/>
       <c r="L113" s="44" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B114" s="31" t="s">
         <v>234</v>
@@ -8603,7 +8603,7 @@
     </row>
     <row r="115" spans="1:21" ht="15" customHeight="1">
       <c r="A115" s="46" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B115" s="31" t="s">
         <v>234</v>
@@ -8623,14 +8623,14 @@
         <v>395</v>
       </c>
       <c r="I115" s="31" t="s">
+        <v>678</v>
+      </c>
+      <c r="J115" s="44" t="s">
         <v>679</v>
-      </c>
-      <c r="J115" s="44" t="s">
-        <v>680</v>
       </c>
       <c r="K115" s="40"/>
       <c r="L115" s="44" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="M115" s="11"/>
       <c r="N115" s="11"/>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="125" spans="1:21" ht="15" customHeight="1">
       <c r="A125" s="17" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B125" s="32" t="s">
         <v>317</v>
@@ -11082,48 +11082,50 @@
     <hyperlink ref="A54" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
     <hyperlink ref="A60" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
     <hyperlink ref="A63" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
-    <hyperlink ref="A67" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Bruxelles_Manneken_Pis.jpg/960px-Bruxelles_Manneken_Pis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{21561D5A-F635-44FA-B9B8-22E9ADDC5BE9}"/>
-    <hyperlink ref="A68" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
-    <hyperlink ref="A69" r:id="rId55" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
-    <hyperlink ref="A72" r:id="rId56" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId57" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId58" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A78" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
-    <hyperlink ref="A80" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A81" r:id="rId62" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
-    <hyperlink ref="A83" r:id="rId63" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A113" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
-    <hyperlink ref="A114" r:id="rId65" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
-    <hyperlink ref="A115" r:id="rId66" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
-    <hyperlink ref="A107" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
-    <hyperlink ref="A106" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A101" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
-    <hyperlink ref="A95" r:id="rId70" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A96" r:id="rId71" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
-    <hyperlink ref="A97" r:id="rId72" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
-    <hyperlink ref="A88" r:id="rId73" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A89" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
-    <hyperlink ref="A92" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
-    <hyperlink ref="A94" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
-    <hyperlink ref="A20" r:id="rId77" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A99" r:id="rId79" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId81" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A65" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg/960px-Fran%C3%A7ois_duquesnoy%2C_tomba_di_adriano_vryburch%2C_m._1638%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{85E997C9-0A16-4446-94B7-9D30CAA9F62C}"/>
-    <hyperlink ref="A48" r:id="rId83" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId84" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId85" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId86" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId87" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A105" r:id="rId89" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A103" r:id="rId90" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
-    <hyperlink ref="A58" r:id="rId91" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
-    <hyperlink ref="A125" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
-    <hyperlink ref="A56" r:id="rId93" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
-    <hyperlink ref="A76" r:id="rId94" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A68" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
+    <hyperlink ref="A69" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
+    <hyperlink ref="A72" r:id="rId55" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId56" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId57" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A78" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
+    <hyperlink ref="A80" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
+    <hyperlink ref="A81" r:id="rId61" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
+    <hyperlink ref="A83" r:id="rId62" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A113" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
+    <hyperlink ref="A114" r:id="rId64" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
+    <hyperlink ref="A115" r:id="rId65" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
+    <hyperlink ref="A107" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
+    <hyperlink ref="A106" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
+    <hyperlink ref="A101" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
+    <hyperlink ref="A95" r:id="rId69" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A96" r:id="rId70" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
+    <hyperlink ref="A97" r:id="rId71" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
+    <hyperlink ref="A88" r:id="rId72" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A89" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
+    <hyperlink ref="A92" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
+    <hyperlink ref="A94" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
+    <hyperlink ref="A20" r:id="rId76" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A99" r:id="rId78" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId80" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A48" r:id="rId81" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId82" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId83" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId84" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId85" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A105" r:id="rId87" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A103" r:id="rId88" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId89" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A125" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId91" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId92" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A61" r:id="rId93" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{146FD4EB-CB96-47AE-B9BA-B7CFC3A2E4C7}"/>
+    <hyperlink ref="A67" r:id="rId94" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
+    <hyperlink ref="A64" r:id="rId95" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
+    <hyperlink ref="A65" r:id="rId96" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8E3B8D-FA86-4AE3-9DD8-ED8294CFEC05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C14C386-E731-4B03-8BEA-ADA1FC9FCBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="737">
   <si>
     <t>Image</t>
   </si>
@@ -1083,9 +1083,6 @@
     <t>"Pandore"</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1d/S._Ignatius_Le_Gros_Gesu_Rome.jpg/1280px-S._Ignatius_Le_Gros_Gesu_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>LEGROS LE JEUNE</t>
   </si>
   <si>
@@ -1101,12 +1098,6 @@
     <t>Église du Gesù</t>
   </si>
   <si>
-    <t>"Statue de saint Ignace de Loyola (autel Saint-Ignace)"</t>
-  </si>
-  <si>
-    <t>c.300 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Louvre_statue_DSC00917.jpg/960px-Louvre_statue_DSC00917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1656,6 +1647,9 @@
     <t>Saint Emerenziana</t>
   </si>
   <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>1670s</t>
   </si>
   <si>
@@ -1776,9 +1770,6 @@
     <t>1691-1693</t>
   </si>
   <si>
-    <t>1600s</t>
-  </si>
-  <si>
     <t>Überlingen</t>
   </si>
   <si>
@@ -1944,9 +1935,6 @@
     <t>"Décors de l'Oratoire du Rosaire"</t>
   </si>
   <si>
-    <t>Rotterdam_standbeeld_Erasmus.jpg (900×1200)</t>
-  </si>
-  <si>
     <t>Rotterdam</t>
   </si>
   <si>
@@ -1974,18 +1962,12 @@
     <t>Statues des Nations vaincues</t>
   </si>
   <si>
-    <t>960px-François_duquesnoy,_tomba_di_adriano_vryburch,_m._1638,_01.jpg (960×1782)</t>
-  </si>
-  <si>
     <t>L'Epitaphe d'Adrien Vryburch</t>
   </si>
   <si>
     <t>Santa Maria dell'Anima</t>
   </si>
   <si>
-    <t>960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg (960×1218)</t>
-  </si>
-  <si>
     <t>Église Saint-Jacques</t>
   </si>
   <si>
@@ -2016,9 +1998,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d7/Gregorio_Fernandez-Piedad.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>960px-Sant'agnese_in_agone,_interno_06.JPG (960×1280)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sant'Agnese in Agone </t>
   </si>
   <si>
@@ -2061,12 +2040,6 @@
     <t xml:space="preserve">Atlantes </t>
   </si>
   <si>
-    <t>960px-Toulon_caryatides_p1040271.jpg (960×1280)</t>
-  </si>
-  <si>
-    <t>Puget_-_Diogenes_Alexander_Louvre.jpg (701×767)</t>
-  </si>
-  <si>
     <t>Pierre_Puget_-_Louis_XIV.jpg (1828×1732)</t>
   </si>
   <si>
@@ -2103,9 +2076,6 @@
     <t xml:space="preserve">Le Char d'Apollon </t>
   </si>
   <si>
-    <t>1280px-Apollon_et_ses_chevaux,_Bassin_du_char_d'Apollon,_Château_de_Versailles.jpg (1280×853)</t>
-  </si>
-  <si>
     <t>Saint François d'Assise</t>
   </si>
   <si>
@@ -2124,18 +2094,9 @@
     <t>Pont Saint-Ange</t>
   </si>
   <si>
-    <t>960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg (960×1280)</t>
-  </si>
-  <si>
-    <t>1280px-Santa_Maria_della_Salute_(Venice)_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg (1280×854)</t>
-  </si>
-  <si>
     <t> Basilique Santa Maria della Salute</t>
   </si>
   <si>
-    <t>960px-Charles_I,_Trafalgar_Square.jpg (960×1441)</t>
-  </si>
-  <si>
     <t>Trafalgar square</t>
   </si>
   <si>
@@ -2254,13 +2215,43 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg/1920px-Saint_Andrew_by_Fran%C3%A7ois_Duquesnoy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>La Rencontre d'Alexandre et de Diogène</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bd/Rotterdam_standbeeld_Erasmus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Epitaph_of_Adriaen_Vryburch.jpg/500px-Epitaph_of_Adriaen_Vryburch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2301,12 +2292,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF202122"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2395,7 +2380,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2516,16 +2501,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{6AA84E56-6885-4D6A-8954-39C99888AB8D}"/>
@@ -2830,7 +2812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V651"/>
+  <dimension ref="A1:V650"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -2944,11 +2926,11 @@
         <v>26</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -2956,7 +2938,7 @@
         <v>27</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Q2" s="4">
         <v>490</v>
@@ -2970,7 +2952,7 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>21</v>
@@ -2987,22 +2969,22 @@
         <v>24</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K3" s="39"/>
       <c r="L3" s="43" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
       <c r="O3" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P3" s="35"/>
       <c r="R3" s="19"/>
@@ -3016,7 +2998,7 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>21</v>
@@ -3033,17 +3015,17 @@
         <v>24</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="43" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
@@ -3069,7 +3051,7 @@
     </row>
     <row r="5" spans="1:21" ht="14.25" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>21</v>
@@ -3086,17 +3068,17 @@
         <v>24</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="I5" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="43" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
@@ -3117,7 +3099,7 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>21</v>
@@ -3134,17 +3116,17 @@
         <v>24</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="43" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
@@ -3192,7 +3174,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3269,7 +3251,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>313</v>
@@ -3292,11 +3274,11 @@
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3315,7 +3297,7 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>125</v>
@@ -3332,7 +3314,7 @@
         <v>128</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>48</v>
@@ -3342,7 +3324,7 @@
       </c>
       <c r="K10" s="39"/>
       <c r="L10" s="43" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
@@ -3368,36 +3350,36 @@
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C11" s="30" t="s">
         <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="30" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G11" s="30" t="s">
         <v>345</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>95</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -3428,7 +3410,7 @@
         <v>163</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="28" t="s">
@@ -3448,7 +3430,7 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -3456,7 +3438,7 @@
         <v>27</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>28</v>
@@ -3470,7 +3452,7 @@
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>162</v>
@@ -3479,7 +3461,7 @@
         <v>163</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="28" t="s">
@@ -3499,7 +3481,7 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -3507,7 +3489,7 @@
         <v>27</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>28</v>
@@ -3521,7 +3503,7 @@
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>162</v>
@@ -3530,7 +3512,7 @@
         <v>163</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="28" t="s">
@@ -3550,7 +3532,7 @@
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -3558,7 +3540,7 @@
         <v>27</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="Q14" s="4">
         <v>109</v>
@@ -3584,7 +3566,7 @@
         <v>163</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="28" t="s">
@@ -3604,7 +3586,7 @@
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -3612,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="Q15" s="4">
         <v>279</v>
@@ -3632,7 +3614,7 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>162</v>
@@ -3641,7 +3623,7 @@
         <v>163</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="28" t="s">
@@ -3651,17 +3633,17 @@
         <v>164</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I16" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
@@ -3669,7 +3651,7 @@
         <v>40</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>28</v>
@@ -3683,7 +3665,7 @@
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>162</v>
@@ -3692,7 +3674,7 @@
         <v>163</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="28" t="s">
@@ -3708,19 +3690,19 @@
         <v>26</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="37" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>28</v>
@@ -3734,7 +3716,7 @@
     </row>
     <row r="18" spans="1:21" ht="15" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>162</v>
@@ -3743,7 +3725,7 @@
         <v>163</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="29" t="s">
@@ -3753,22 +3735,22 @@
         <v>164</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="43" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
       <c r="O18" s="29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P18" s="35">
         <v>470</v>
@@ -3784,7 +3766,7 @@
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>162</v>
@@ -3793,7 +3775,7 @@
         <v>163</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="29" t="s">
@@ -3806,14 +3788,14 @@
         <v>315</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J19" s="23" t="s">
         <v>53</v>
       </c>
       <c r="K19" s="39"/>
       <c r="L19" s="43" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
@@ -3839,7 +3821,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -3848,7 +3830,7 @@
         <v>163</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="29" t="s">
@@ -3858,24 +3840,24 @@
         <v>164</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="43" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="19" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="P20" s="35">
         <v>900</v>
@@ -3891,7 +3873,7 @@
     </row>
     <row r="21" spans="1:21" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>162</v>
@@ -3900,7 +3882,7 @@
         <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="29" t="s">
@@ -3910,22 +3892,22 @@
         <v>164</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="43" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
       <c r="O21" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P21" s="35">
         <v>700</v>
@@ -3941,7 +3923,7 @@
     </row>
     <row r="22" spans="1:21" ht="15" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>162</v>
@@ -3950,7 +3932,7 @@
         <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="29" t="s">
@@ -3966,16 +3948,16 @@
         <v>26</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="K22" s="39"/>
       <c r="L22" s="43" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
       <c r="O22" s="29" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="P22" s="35">
         <v>1269</v>
@@ -3991,7 +3973,7 @@
     </row>
     <row r="23" spans="1:21" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>162</v>
@@ -4000,7 +3982,7 @@
         <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="29" t="s">
@@ -4010,7 +3992,7 @@
         <v>164</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>26</v>
@@ -4020,7 +4002,7 @@
       </c>
       <c r="K23" s="39"/>
       <c r="L23" s="43" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
@@ -4041,7 +4023,7 @@
     </row>
     <row r="24" spans="1:21" ht="15" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>162</v>
@@ -4050,7 +4032,7 @@
         <v>163</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="29" t="s">
@@ -4060,7 +4042,7 @@
         <v>164</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>26</v>
@@ -4070,7 +4052,7 @@
       </c>
       <c r="K24" s="39"/>
       <c r="L24" s="43" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="19"/>
@@ -4091,7 +4073,7 @@
     </row>
     <row r="25" spans="1:21" ht="15" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B25" s="29" t="s">
         <v>162</v>
@@ -4100,7 +4082,7 @@
         <v>163</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="29" t="s">
@@ -4110,19 +4092,19 @@
         <v>164</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J25" s="43" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="L25" s="43" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
@@ -4148,7 +4130,7 @@
     </row>
     <row r="26" spans="1:21" ht="15" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>162</v>
@@ -4157,7 +4139,7 @@
         <v>163</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="29" t="s">
@@ -4167,22 +4149,22 @@
         <v>164</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K26" s="39"/>
       <c r="L26" s="43" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
       <c r="O26" s="29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P26" s="35">
         <v>1677</v>
@@ -4203,7 +4185,7 @@
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>162</v>
@@ -4212,7 +4194,7 @@
         <v>163</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="29" t="s">
@@ -4222,17 +4204,17 @@
         <v>164</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="M27" s="19"/>
       <c r="N27" s="19"/>
@@ -4258,7 +4240,7 @@
     </row>
     <row r="28" spans="1:21" ht="15" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>162</v>
@@ -4267,7 +4249,7 @@
         <v>163</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="29" t="s">
@@ -4277,17 +4259,17 @@
         <v>164</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4313,7 +4295,7 @@
     </row>
     <row r="29" spans="1:21" ht="15" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>162</v>
@@ -4322,7 +4304,7 @@
         <v>163</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="29" t="s">
@@ -4332,17 +4314,17 @@
         <v>164</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K29" s="39"/>
       <c r="L29" s="43" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
@@ -4368,7 +4350,7 @@
     </row>
     <row r="30" spans="1:21" ht="15" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B30" s="29" t="s">
         <v>162</v>
@@ -4377,7 +4359,7 @@
         <v>163</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="29" t="s">
@@ -4387,22 +4369,22 @@
         <v>164</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K30" s="39"/>
       <c r="L30" s="43" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="M30" s="19"/>
       <c r="N30" s="19"/>
       <c r="O30" s="29" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="P30" s="35">
         <v>200</v>
@@ -4421,7 +4403,7 @@
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>162</v>
@@ -4430,7 +4412,7 @@
         <v>163</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="29" t="s">
@@ -4440,17 +4422,17 @@
         <v>164</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>81</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="K31" s="39"/>
       <c r="L31" s="43" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
@@ -4471,7 +4453,7 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>162</v>
@@ -4480,7 +4462,7 @@
         <v>163</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="29" t="s">
@@ -4490,7 +4472,7 @@
         <v>164</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>48</v>
@@ -4500,7 +4482,7 @@
       </c>
       <c r="K32" s="39"/>
       <c r="L32" s="43" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="19"/>
@@ -4526,7 +4508,7 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>162</v>
@@ -4535,7 +4517,7 @@
         <v>163</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E33" s="19"/>
       <c r="F33" s="29" t="s">
@@ -4545,17 +4527,17 @@
         <v>164</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="K33" s="39"/>
       <c r="L33" s="43" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
@@ -4581,7 +4563,7 @@
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>162</v>
@@ -4590,7 +4572,7 @@
         <v>163</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E34" s="19"/>
       <c r="F34" s="29" t="s">
@@ -4600,17 +4582,17 @@
         <v>164</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K34" s="39"/>
       <c r="L34" s="43" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
@@ -4631,7 +4613,7 @@
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>162</v>
@@ -4640,7 +4622,7 @@
         <v>163</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E35" s="19"/>
       <c r="F35" s="29" t="s">
@@ -4650,17 +4632,17 @@
         <v>164</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="K35" s="39"/>
       <c r="L35" s="43" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
@@ -4681,7 +4663,7 @@
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>162</v>
@@ -4690,7 +4672,7 @@
         <v>163</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E36" s="19"/>
       <c r="F36" s="29" t="s">
@@ -4700,17 +4682,17 @@
         <v>164</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="K36" s="39"/>
       <c r="L36" s="43" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="M36" s="19"/>
       <c r="N36" s="19"/>
@@ -4736,7 +4718,7 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>162</v>
@@ -4745,7 +4727,7 @@
         <v>163</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="29" t="s">
@@ -4755,22 +4737,22 @@
         <v>164</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="K37" s="39"/>
       <c r="L37" s="43" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
       <c r="O37" s="29" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P37" s="35">
         <v>150</v>
@@ -4789,18 +4771,18 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
       <c r="F38" s="29" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G38" s="29" t="s">
         <v>34</v>
@@ -4812,11 +4794,11 @@
         <v>26</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="43" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
@@ -4872,7 +4854,7 @@
         <v>84</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
@@ -4888,7 +4870,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -4959,10 +4941,10 @@
         <v>34</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="3" t="s">
@@ -5045,36 +5027,36 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="29" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G43" s="29" t="s">
         <v>314</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L43" s="43" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="M43" s="19"/>
       <c r="N43" s="19"/>
@@ -5150,7 +5132,7 @@
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>43</v>
@@ -5176,10 +5158,10 @@
         <v>49</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -5187,10 +5169,10 @@
         <v>27</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="R45" s="4">
         <v>128</v>
@@ -5228,10 +5210,10 @@
         <v>49</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
@@ -5239,10 +5221,10 @@
         <v>27</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="R46" s="4">
         <v>128</v>
@@ -5256,7 +5238,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5273,14 +5255,14 @@
         <v>46</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -5299,7 +5281,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5316,14 +5298,14 @@
         <v>46</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -5371,10 +5353,10 @@
         <v>53</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -5382,7 +5364,7 @@
         <v>27</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q49" s="4">
         <v>75</v>
@@ -5397,7 +5379,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5414,22 +5396,22 @@
         <v>46</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I50" s="29"/>
       <c r="J50" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
       <c r="O50" s="29" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="P50" s="35">
         <v>390</v>
@@ -5450,7 +5432,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5467,22 +5449,22 @@
         <v>46</v>
       </c>
       <c r="H51" s="29" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>48</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="43" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
       <c r="O51" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P51" s="35">
         <v>400</v>
@@ -5498,7 +5480,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5525,7 +5507,7 @@
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="43" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5551,7 +5533,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5568,7 +5550,7 @@
         <v>46</v>
       </c>
       <c r="H53" s="29" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I53" s="29" t="s">
         <v>48</v>
@@ -5578,7 +5560,7 @@
       </c>
       <c r="K53" s="39"/>
       <c r="L53" s="43" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M53" s="19"/>
       <c r="N53" s="19"/>
@@ -5610,7 +5592,7 @@
         <v>218</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -5655,13 +5637,13 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>636</v>
+        <v>731</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>218</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
@@ -5671,16 +5653,16 @@
       <c r="G55" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="H55" s="31" t="s">
-        <v>580</v>
+      <c r="H55" s="31">
+        <v>1600</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
       <c r="L55" s="44" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
@@ -5706,13 +5688,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5723,15 +5705,15 @@
         <v>147</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I56" s="31" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J56" s="44"/>
       <c r="K56" s="40"/>
       <c r="L56" s="44" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
@@ -5763,7 +5745,7 @@
         <v>332</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
@@ -5812,13 +5794,13 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="B58" s="31" t="s">
         <v>332</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
@@ -5829,7 +5811,7 @@
         <v>333</v>
       </c>
       <c r="H58" s="31" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I58" s="32" t="s">
         <v>193</v>
@@ -5839,7 +5821,7 @@
       </c>
       <c r="K58" s="40"/>
       <c r="L58" s="44" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
@@ -5865,13 +5847,13 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>332</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
@@ -5882,26 +5864,26 @@
         <v>333</v>
       </c>
       <c r="H59" s="31" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I59" s="31" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
       <c r="O59" s="31" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5914,13 +5896,13 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B60" s="31" t="s">
         <v>332</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
@@ -5934,14 +5916,14 @@
         <v>1663</v>
       </c>
       <c r="I60" s="31" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5968,7 +5950,7 @@
         <v>254</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
@@ -5989,7 +5971,7 @@
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -6000,7 +5982,7 @@
         <v>47</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="R61" s="20">
         <v>27.5</v>
@@ -6068,7 +6050,7 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>294</v>
@@ -6095,7 +6077,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6170,7 +6152,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6187,17 +6169,17 @@
         <v>134</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="I65" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K65" s="23"/>
       <c r="L65" s="23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M65" s="21"/>
       <c r="N65" s="21"/>
@@ -6217,8 +6199,8 @@
       </c>
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
-      <c r="A66" s="51" t="s">
-        <v>646</v>
+      <c r="A66" s="52" t="s">
+        <v>736</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>125</v>
@@ -6241,11 +6223,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6269,13 +6251,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6286,15 +6268,15 @@
         <v>24</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6315,13 +6297,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>649</v>
+        <v>735</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6332,17 +6314,17 @@
         <v>288</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>592</v>
-      </c>
-      <c r="J68" s="52" t="s">
-        <v>650</v>
+        <v>589</v>
+      </c>
+      <c r="J68" s="50" t="s">
+        <v>644</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6363,18 +6345,18 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="31" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G69" s="31" t="s">
         <v>298</v>
@@ -6386,18 +6368,18 @@
         <v>26</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
       <c r="O69" s="31" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="P69" s="36">
         <v>550</v>
@@ -6413,13 +6395,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6430,17 +6412,17 @@
         <v>333</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="I70" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6537,7 +6519,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6557,7 +6539,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6580,11 +6562,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6632,7 +6614,7 @@
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M74" s="22"/>
       <c r="N74" s="22" t="s">
@@ -6662,7 +6644,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6673,13 +6655,13 @@
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="31" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G75" s="31" t="s">
         <v>191</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I75" s="31" t="s">
         <v>193</v>
@@ -6689,7 +6671,7 @@
       </c>
       <c r="K75" s="40"/>
       <c r="L75" s="44" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="M75" s="11"/>
       <c r="N75" s="11"/>
@@ -6715,7 +6697,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6726,23 +6708,23 @@
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="31" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G76" s="31" t="s">
         <v>191</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="44" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M76" s="11"/>
       <c r="N76" s="11"/>
@@ -6768,7 +6750,7 @@
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B77" s="31" t="s">
         <v>104</v>
@@ -6793,12 +6775,12 @@
       <c r="J77" s="44"/>
       <c r="K77" s="40"/>
       <c r="L77" s="44" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="M77" s="11"/>
       <c r="N77" s="11"/>
       <c r="O77" s="31" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="P77" s="36"/>
       <c r="R77" s="11"/>
@@ -6812,7 +6794,7 @@
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>660</v>
+        <v>537</v>
       </c>
       <c r="B78" s="31" t="s">
         <v>104</v>
@@ -6835,11 +6817,11 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="M78" s="11"/>
       <c r="N78" s="11"/>
@@ -6909,7 +6891,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6926,17 +6908,17 @@
         <v>183</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I80" s="31" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
@@ -6957,13 +6939,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6971,22 +6953,22 @@
         <v>286</v>
       </c>
       <c r="G81" s="31" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="I81" s="31" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6994,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -7007,7 +6989,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7024,22 +7006,22 @@
         <v>200</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I82" s="31" t="s">
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
       <c r="O82" s="31" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P82" s="36"/>
       <c r="R82" s="11"/>
@@ -7078,7 +7060,7 @@
       <c r="J83" s="23"/>
       <c r="K83" s="23"/>
       <c r="L83" s="23" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="M83" s="21"/>
       <c r="N83" s="21"/>
@@ -7086,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="P83" s="21" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="R83" s="21"/>
       <c r="S83" s="26"/>
@@ -7099,7 +7081,7 @@
     </row>
     <row r="84" spans="1:21" ht="15" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B84" s="31" t="s">
         <v>125</v>
@@ -7126,7 +7108,7 @@
       </c>
       <c r="K84" s="40"/>
       <c r="L84" s="44" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
@@ -7154,7 +7136,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7171,17 +7153,17 @@
         <v>88</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I85" s="31" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
@@ -7207,7 +7189,7 @@
     </row>
     <row r="86" spans="1:21" ht="15" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B86" s="31" t="s">
         <v>125</v>
@@ -7227,12 +7209,12 @@
         <v>148</v>
       </c>
       <c r="I86" s="31" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J86" s="44"/>
       <c r="K86" s="40"/>
       <c r="L86" s="44" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="M86" s="11"/>
       <c r="N86" s="11"/>
@@ -7251,7 +7233,7 @@
     </row>
     <row r="87" spans="1:21" ht="15" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B87" s="31" t="s">
         <v>125</v>
@@ -7275,10 +7257,10 @@
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7304,7 +7286,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7355,7 +7337,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>696</v>
+        <v>728</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7378,11 +7360,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7401,18 +7383,18 @@
     </row>
     <row r="90" spans="1:21" ht="15" customHeight="1">
       <c r="A90" s="17" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="32" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G90" s="32" t="s">
         <v>87</v>
@@ -7428,7 +7410,7 @@
       </c>
       <c r="K90" s="20"/>
       <c r="L90" s="22" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M90" s="22"/>
       <c r="N90" s="22"/>
@@ -7436,7 +7418,7 @@
         <v>40</v>
       </c>
       <c r="P90" s="20" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" s="20"/>
@@ -7499,13 +7481,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
+        <v>732</v>
+      </c>
+      <c r="B92" s="31" t="s">
+        <v>584</v>
+      </c>
+      <c r="C92" s="47" t="s">
         <v>697</v>
-      </c>
-      <c r="B92" s="31" t="s">
-        <v>587</v>
-      </c>
-      <c r="C92" s="47" t="s">
-        <v>710</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7513,20 +7495,20 @@
         <v>156</v>
       </c>
       <c r="G92" s="31" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="I92" s="31" t="s">
-        <v>586</v>
-      </c>
-      <c r="J92" s="53" t="s">
-        <v>698</v>
+        <v>583</v>
+      </c>
+      <c r="J92" s="51" t="s">
+        <v>686</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7570,7 +7552,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7592,13 +7574,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>699</v>
+        <v>733</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7609,17 +7591,17 @@
         <v>87</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I94" s="31" t="s">
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
@@ -7684,390 +7666,387 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
-      <c r="A96" s="17" t="s">
+      <c r="A96" s="46" t="s">
+        <v>682</v>
+      </c>
+      <c r="B96" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="C96" s="47" t="s">
         <v>349</v>
       </c>
-      <c r="B96" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="C96" s="32" t="s">
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="D96" s="20"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="32" t="s">
+      <c r="G96" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="G96" s="32" t="s">
+      <c r="H96" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="H96" s="32" t="s">
+      <c r="I96" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="I96" s="32" t="s">
+      <c r="K96" s="40"/>
+      <c r="L96" s="44" t="s">
+        <v>564</v>
+      </c>
+      <c r="M96" s="11"/>
+      <c r="N96" s="11"/>
+      <c r="O96" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P96" s="36"/>
+      <c r="R96" s="11"/>
+      <c r="S96" s="12"/>
+      <c r="T96" s="4">
+        <v>2</v>
+      </c>
+      <c r="U96" s="5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="15" customHeight="1">
+      <c r="A97" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="D97" s="20"/>
+      <c r="E97" s="20"/>
+      <c r="F97" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G97" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H97" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="I97" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="J96" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="K96" s="20"/>
-      <c r="L96" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="M96" s="22"/>
-      <c r="N96" s="22"/>
-      <c r="O96" s="32" t="s">
+      <c r="J97" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="K97" s="20"/>
+      <c r="L97" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="M97" s="22"/>
+      <c r="N97" s="22"/>
+      <c r="O97" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="P96" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" s="20"/>
-      <c r="S96" s="25" t="s">
+      <c r="P97" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" s="20"/>
+      <c r="S97" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="T97" s="2">
+        <v>2</v>
+      </c>
+      <c r="U97" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="15" customHeight="1">
+      <c r="A98" s="49" t="s">
+        <v>703</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C98" s="47" t="s">
+        <v>699</v>
+      </c>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="31" t="s">
+        <v>565</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>567</v>
+      </c>
+      <c r="H98" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="I98" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J98" s="44" t="s">
+        <v>681</v>
+      </c>
+      <c r="K98" s="40"/>
+      <c r="L98" s="44" t="s">
+        <v>680</v>
+      </c>
+      <c r="M98" s="11"/>
+      <c r="N98" s="11"/>
+      <c r="O98" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="P98" s="36">
+        <v>350</v>
+      </c>
+      <c r="R98" s="11"/>
+      <c r="S98" s="12"/>
+      <c r="T98" s="4">
+        <v>3</v>
+      </c>
+      <c r="U98" s="5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="15" customHeight="1">
+      <c r="A99" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="D99" s="20"/>
+      <c r="E99" s="20"/>
+      <c r="F99" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G99" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="H99" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="I99" s="32"/>
+      <c r="J99" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K99" s="20"/>
+      <c r="L99" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="M99" s="22"/>
+      <c r="N99" s="22"/>
+      <c r="O99" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="P99" s="20">
+        <v>204</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" s="20"/>
+      <c r="S99" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="T96" s="2">
-        <v>3</v>
-      </c>
-      <c r="U96" s="14"/>
-    </row>
-    <row r="97" spans="1:21" ht="15" customHeight="1">
-      <c r="A97" s="46" t="s">
-        <v>692</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="C97" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="G97" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="H97" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="I97" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J97" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="K97" s="40"/>
-      <c r="L97" s="44" t="s">
-        <v>566</v>
-      </c>
-      <c r="M97" s="11"/>
-      <c r="N97" s="11"/>
-      <c r="O97" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P97" s="36"/>
-      <c r="R97" s="11"/>
-      <c r="S97" s="12"/>
-      <c r="T97" s="4">
-        <v>2</v>
-      </c>
-      <c r="U97" s="5">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" ht="15" customHeight="1">
-      <c r="A98" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="D98" s="20"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="G98" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="H98" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="I98" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J98" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="K98" s="20"/>
-      <c r="L98" s="22" t="s">
-        <v>383</v>
-      </c>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P98" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" s="20"/>
-      <c r="S98" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="T98" s="2">
-        <v>2</v>
-      </c>
-      <c r="U98" s="5">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" ht="15" customHeight="1">
-      <c r="A99" s="49" t="s">
-        <v>716</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C99" s="47" t="s">
-        <v>712</v>
-      </c>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="G99" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="H99" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="I99" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="44" t="s">
-        <v>691</v>
-      </c>
-      <c r="K99" s="40"/>
-      <c r="L99" s="44" t="s">
-        <v>690</v>
-      </c>
-      <c r="M99" s="11"/>
-      <c r="N99" s="11"/>
-      <c r="O99" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="P99" s="36">
-        <v>350</v>
-      </c>
-      <c r="R99" s="11"/>
-      <c r="S99" s="12"/>
-      <c r="T99" s="4">
-        <v>3</v>
-      </c>
-      <c r="U99" s="5">
-        <v>106</v>
-      </c>
+      <c r="T99" s="2">
+        <v>1</v>
+      </c>
+      <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1">
-      <c r="A100" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="B100" s="32" t="s">
+      <c r="A100" s="46" t="s">
+        <v>734</v>
+      </c>
+      <c r="B100" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C100" s="32" t="s">
+      <c r="C100" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="32" t="s">
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="G100" s="32" t="s">
+      <c r="G100" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="H100" s="32" t="s">
+      <c r="H100" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="I100" s="32"/>
+      <c r="I100" s="31"/>
       <c r="J100" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="K100" s="20"/>
-      <c r="L100" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="M100" s="22"/>
-      <c r="N100" s="22"/>
-      <c r="O100" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="P100" s="20">
-        <v>204</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" s="20"/>
-      <c r="S100" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T100" s="2">
+      <c r="K100" s="40"/>
+      <c r="L100" s="44" t="s">
+        <v>679</v>
+      </c>
+      <c r="M100" s="11"/>
+      <c r="N100" s="11"/>
+      <c r="O100" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="P100" s="36">
+        <v>300</v>
+      </c>
+      <c r="R100" s="11"/>
+      <c r="S100" s="12"/>
+      <c r="T100" s="4">
         <v>1</v>
       </c>
-      <c r="U100" s="14"/>
+      <c r="U100" s="5">
+        <v>130</v>
+      </c>
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1">
-      <c r="A101" s="46" t="s">
-        <v>689</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G101" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="H101" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="I101" s="31"/>
+      <c r="A101" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C101" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G101" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="H101" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="I101" s="32"/>
       <c r="J101" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="K101" s="40"/>
-      <c r="L101" s="44" t="s">
-        <v>688</v>
-      </c>
-      <c r="M101" s="11"/>
-      <c r="N101" s="11"/>
-      <c r="O101" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="P101" s="36">
-        <v>300</v>
-      </c>
-      <c r="R101" s="11"/>
-      <c r="S101" s="12"/>
-      <c r="T101" s="4">
-        <v>1</v>
-      </c>
-      <c r="U101" s="5">
-        <v>130</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="K101" s="20"/>
+      <c r="L101" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="M101" s="22"/>
+      <c r="N101" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="O101" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P101" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="20"/>
+      <c r="S101" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="T101" s="2">
+        <v>3</v>
+      </c>
+      <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1">
-      <c r="A102" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="B102" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="C102" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="G102" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="H102" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="I102" s="32"/>
-      <c r="J102" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="K102" s="20"/>
-      <c r="L102" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="M102" s="22"/>
-      <c r="N102" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="O102" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="P102" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" s="20"/>
-      <c r="S102" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T102" s="2">
+      <c r="A102" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="B102" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G102" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="I102" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="M102" s="21"/>
+      <c r="N102" s="21"/>
+      <c r="O102" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P102" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="R102" s="21"/>
+      <c r="S102" s="26"/>
+      <c r="T102" s="4">
         <v>3</v>
       </c>
-      <c r="U102" s="14"/>
+      <c r="U102" s="5">
+        <v>107</v>
+      </c>
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
-      <c r="A103" s="17" t="s">
-        <v>730</v>
-      </c>
-      <c r="B103" s="33" t="s">
+      <c r="A103" s="46" t="s">
+        <v>631</v>
+      </c>
+      <c r="B103" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C103" s="38" t="s">
+      <c r="C103" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="33" t="s">
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="G103" s="33" t="s">
+      <c r="G103" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="H103" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="I103" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="J103" s="23"/>
-      <c r="K103" s="23"/>
-      <c r="L103" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="M103" s="21"/>
-      <c r="N103" s="21"/>
-      <c r="O103" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="P103" s="21" t="s">
-        <v>432</v>
-      </c>
-      <c r="R103" s="21"/>
-      <c r="S103" s="26"/>
+      <c r="H103" s="31" t="s">
+        <v>568</v>
+      </c>
+      <c r="I103" s="31" t="s">
+        <v>569</v>
+      </c>
+      <c r="J103" s="44"/>
+      <c r="K103" s="40"/>
+      <c r="L103" s="44" t="s">
+        <v>570</v>
+      </c>
+      <c r="M103" s="11"/>
+      <c r="N103" s="11"/>
+      <c r="O103" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="P103" s="36">
+        <v>320</v>
+      </c>
+      <c r="R103" s="11"/>
+      <c r="S103" s="12"/>
       <c r="T103" s="4">
         <v>3</v>
       </c>
       <c r="U103" s="5">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>634</v>
+        <v>716</v>
       </c>
       <c r="B104" s="31" t="s">
         <v>121</v>
@@ -8084,23 +8063,25 @@
         <v>24</v>
       </c>
       <c r="H104" s="31" t="s">
-        <v>570</v>
+        <v>135</v>
       </c>
       <c r="I104" s="31" t="s">
-        <v>571</v>
-      </c>
-      <c r="J104" s="44"/>
+        <v>26</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>433</v>
+      </c>
       <c r="K104" s="40"/>
       <c r="L104" s="44" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M104" s="11"/>
       <c r="N104" s="11"/>
       <c r="O104" s="31" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="P104" s="36">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="R104" s="11"/>
       <c r="S104" s="12"/>
@@ -8108,47 +8089,47 @@
         <v>3</v>
       </c>
       <c r="U104" s="5">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>729</v>
+        <v>676</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>121</v>
+        <v>580</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>122</v>
+        <v>700</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
       <c r="F105" s="31" t="s">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="G105" s="31" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="H105" s="31" t="s">
-        <v>135</v>
+        <v>581</v>
       </c>
       <c r="I105" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>436</v>
+        <v>548</v>
+      </c>
+      <c r="J105" s="44" t="s">
+        <v>675</v>
       </c>
       <c r="K105" s="40"/>
       <c r="L105" s="44" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="M105" s="11"/>
       <c r="N105" s="11"/>
       <c r="O105" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P105" s="36">
-        <v>500</v>
+        <v>36</v>
+      </c>
+      <c r="P105" s="36" t="s">
+        <v>678</v>
       </c>
       <c r="R105" s="11"/>
       <c r="S105" s="12"/>
@@ -8156,18 +8137,18 @@
         <v>3</v>
       </c>
       <c r="U105" s="5">
-        <v>109</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>583</v>
+        <v>677</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -8178,25 +8159,25 @@
         <v>255</v>
       </c>
       <c r="H106" s="31" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="I106" s="31" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
       <c r="O106" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="P106" s="36" t="s">
-        <v>687</v>
+      <c r="P106" s="36">
+        <v>50</v>
       </c>
       <c r="R106" s="11"/>
       <c r="S106" s="12"/>
@@ -8204,94 +8185,95 @@
         <v>3</v>
       </c>
       <c r="U106" s="5">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:21" ht="15" customHeight="1">
-      <c r="A107" s="46" t="s">
-        <v>683</v>
-      </c>
-      <c r="B107" s="31" t="s">
-        <v>686</v>
-      </c>
-      <c r="C107" s="47" t="s">
-        <v>713</v>
-      </c>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="G107" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="H107" s="31" t="s">
-        <v>565</v>
-      </c>
-      <c r="I107" s="31" t="s">
-        <v>550</v>
-      </c>
-      <c r="J107" s="44" t="s">
-        <v>684</v>
-      </c>
-      <c r="K107" s="40"/>
-      <c r="L107" s="44" t="s">
-        <v>553</v>
-      </c>
-      <c r="M107" s="11"/>
-      <c r="N107" s="11"/>
-      <c r="O107" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="P107" s="36">
-        <v>50</v>
-      </c>
-      <c r="R107" s="11"/>
-      <c r="S107" s="12"/>
-      <c r="T107" s="4">
+      <c r="A107" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C107" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G107" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H107" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I107" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="J107" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="K107" s="20"/>
+      <c r="L107" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="M107" s="22"/>
+      <c r="N107" s="22"/>
+      <c r="O107" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="P107" s="20"/>
+      <c r="Q107" s="2"/>
+      <c r="R107" s="20"/>
+      <c r="S107" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="T107" s="2">
         <v>3</v>
       </c>
-      <c r="U107" s="5">
-        <v>152</v>
-      </c>
+      <c r="U107" s="14"/>
     </row>
     <row r="108" spans="1:21" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="C108" s="32" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="D108" s="20"/>
       <c r="E108" s="20"/>
       <c r="F108" s="32" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="G108" s="32" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="H108" s="32" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="I108" s="32" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="J108" s="23" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="K108" s="20"/>
       <c r="L108" s="22" t="s">
-        <v>272</v>
+        <v>120</v>
       </c>
       <c r="M108" s="22"/>
       <c r="N108" s="22"/>
       <c r="O108" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="P108" s="20"/>
+        <v>27</v>
+      </c>
+      <c r="P108" s="20" t="s">
+        <v>71</v>
+      </c>
       <c r="Q108" s="2"/>
       <c r="R108" s="20"/>
       <c r="S108" s="25" t="s">
@@ -8304,47 +8286,45 @@
     </row>
     <row r="109" spans="1:21" ht="15" customHeight="1">
       <c r="A109" s="15" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="B109" s="32" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C109" s="32" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="D109" s="20"/>
       <c r="E109" s="20"/>
       <c r="F109" s="32" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="G109" s="32" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="H109" s="32" t="s">
-        <v>33</v>
+        <v>156</v>
       </c>
       <c r="I109" s="32" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="J109" s="23" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="K109" s="20"/>
       <c r="L109" s="22" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="M109" s="22"/>
       <c r="N109" s="22"/>
       <c r="O109" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P109" s="20" t="s">
-        <v>71</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="P109" s="20"/>
       <c r="Q109" s="2"/>
       <c r="R109" s="20"/>
       <c r="S109" s="25" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="T109" s="2">
         <v>3</v>
@@ -8353,50 +8333,56 @@
     </row>
     <row r="110" spans="1:21" ht="15" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B110" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C110" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="D110" s="20"/>
-      <c r="E110" s="20"/>
-      <c r="F110" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="G110" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="H110" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="I110" s="32" t="s">
-        <v>157</v>
+        <v>354</v>
+      </c>
+      <c r="B110" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C110" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G110" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H110" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="I110" s="33" t="s">
+        <v>410</v>
       </c>
       <c r="J110" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="K110" s="20"/>
-      <c r="L110" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="M110" s="22"/>
-      <c r="N110" s="22"/>
-      <c r="O110" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="P110" s="20"/>
-      <c r="Q110" s="2"/>
-      <c r="R110" s="20"/>
-      <c r="S110" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T110" s="2">
-        <v>3</v>
-      </c>
-      <c r="U110" s="14"/>
+        <v>49</v>
+      </c>
+      <c r="K110" s="23"/>
+      <c r="L110" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="M110" s="21"/>
+      <c r="N110" s="21"/>
+      <c r="O110" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P110" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q110" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="R110" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="S110" s="26"/>
+      <c r="T110" s="4">
+        <v>1</v>
+      </c>
+      <c r="U110" s="5">
+        <v>40</v>
+      </c>
     </row>
     <row r="111" spans="1:21" ht="15" customHeight="1">
       <c r="A111" s="15" t="s">
@@ -8406,7 +8392,7 @@
         <v>234</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D111" s="21"/>
       <c r="E111" s="21"/>
@@ -8417,102 +8403,95 @@
         <v>297</v>
       </c>
       <c r="H111" s="33" t="s">
-        <v>359</v>
+        <v>415</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J111" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K111" s="23"/>
       <c r="L111" s="23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M111" s="21"/>
       <c r="N111" s="21"/>
       <c r="O111" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="P111" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q111" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="R111" s="21" t="s">
-        <v>417</v>
+      <c r="P111" s="21">
+        <v>320</v>
+      </c>
+      <c r="Q111" s="4">
+        <v>106</v>
+      </c>
+      <c r="R111" s="21">
+        <v>114</v>
       </c>
       <c r="S111" s="26"/>
       <c r="T111" s="4">
         <v>1</v>
       </c>
       <c r="U111" s="5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="15" customHeight="1">
-      <c r="A112" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="B112" s="33" t="s">
+      <c r="A112" s="46" t="s">
+        <v>727</v>
+      </c>
+      <c r="B112" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="C112" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="33" t="s">
+      <c r="C112" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="G112" s="33" t="s">
+      <c r="G112" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="H112" s="33" t="s">
-        <v>418</v>
-      </c>
-      <c r="I112" s="33" t="s">
-        <v>419</v>
-      </c>
-      <c r="J112" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="K112" s="23"/>
-      <c r="L112" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="M112" s="21"/>
-      <c r="N112" s="21"/>
-      <c r="O112" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="P112" s="21">
-        <v>320</v>
-      </c>
-      <c r="Q112" s="4">
-        <v>106</v>
-      </c>
-      <c r="R112" s="21">
-        <v>114</v>
-      </c>
-      <c r="S112" s="26"/>
+      <c r="H112" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="I112" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="J112" s="44" t="s">
+        <v>666</v>
+      </c>
+      <c r="K112" s="40"/>
+      <c r="L112" s="44" t="s">
+        <v>667</v>
+      </c>
+      <c r="M112" s="11"/>
+      <c r="N112" s="11"/>
+      <c r="O112" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="P112" s="36"/>
+      <c r="R112" s="11"/>
+      <c r="S112" s="12"/>
       <c r="T112" s="4">
         <v>1</v>
       </c>
       <c r="U112" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>675</v>
+        <v>729</v>
       </c>
       <c r="B113" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D113" s="11"/>
       <c r="E113" s="11"/>
@@ -8523,42 +8502,49 @@
         <v>297</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="I113" s="31" t="s">
-        <v>413</v>
-      </c>
-      <c r="J113" s="44" t="s">
-        <v>673</v>
+        <v>48</v>
+      </c>
+      <c r="J113" s="23" t="s">
+        <v>49</v>
       </c>
       <c r="K113" s="40"/>
-      <c r="L113" s="44" t="s">
-        <v>674</v>
+      <c r="L113" t="s">
+        <v>730</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
       <c r="O113" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="P113" s="36"/>
-      <c r="R113" s="11"/>
+        <v>27</v>
+      </c>
+      <c r="P113" s="36">
+        <v>332</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>296</v>
+      </c>
+      <c r="R113" s="11">
+        <v>44</v>
+      </c>
       <c r="S113" s="12"/>
       <c r="T113" s="4">
         <v>1</v>
       </c>
       <c r="U113" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B114" s="31" t="s">
         <v>234</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="11"/>
@@ -8569,114 +8555,112 @@
         <v>297</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>532</v>
+        <v>392</v>
       </c>
       <c r="I114" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="J114" s="23" t="s">
-        <v>49</v>
+        <v>669</v>
+      </c>
+      <c r="J114" s="44" t="s">
+        <v>670</v>
       </c>
       <c r="K114" s="40"/>
-      <c r="L114" s="50"/>
+      <c r="L114" s="44" t="s">
+        <v>671</v>
+      </c>
       <c r="M114" s="11"/>
       <c r="N114" s="11"/>
       <c r="O114" s="31" t="s">
         <v>27</v>
       </c>
       <c r="P114" s="36">
-        <v>332</v>
-      </c>
-      <c r="Q114" s="4">
-        <v>296</v>
-      </c>
-      <c r="R114" s="11">
-        <v>44</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="R114" s="11"/>
       <c r="S114" s="12"/>
       <c r="T114" s="4">
         <v>1</v>
       </c>
       <c r="U114" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:21" ht="15" customHeight="1">
-      <c r="A115" s="46" t="s">
-        <v>677</v>
-      </c>
-      <c r="B115" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="C115" s="47" t="s">
-        <v>358</v>
-      </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="G115" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="H115" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="I115" s="31" t="s">
-        <v>678</v>
-      </c>
-      <c r="J115" s="44" t="s">
-        <v>679</v>
-      </c>
-      <c r="K115" s="40"/>
-      <c r="L115" s="44" t="s">
-        <v>680</v>
-      </c>
-      <c r="M115" s="11"/>
-      <c r="N115" s="11"/>
-      <c r="O115" s="31" t="s">
+      <c r="A115" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G115" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="H115" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I115" s="32"/>
+      <c r="J115" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K115" s="20"/>
+      <c r="L115" s="22" t="s">
+        <v>712</v>
+      </c>
+      <c r="M115" s="22"/>
+      <c r="N115" s="22"/>
+      <c r="O115" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="P115" s="36">
-        <v>66</v>
-      </c>
-      <c r="R115" s="11"/>
-      <c r="S115" s="12"/>
-      <c r="T115" s="4">
-        <v>1</v>
-      </c>
-      <c r="U115" s="5">
-        <v>44</v>
-      </c>
+      <c r="P115" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" s="20"/>
+      <c r="S115" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="T115" s="2">
+        <v>3</v>
+      </c>
+      <c r="U115" s="14"/>
     </row>
     <row r="116" spans="1:21" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
       <c r="F116" s="32" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G116" s="32" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H116" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I116" s="32"/>
+        <v>60</v>
+      </c>
+      <c r="I116" s="32" t="s">
+        <v>26</v>
+      </c>
       <c r="J116" s="23" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>725</v>
+        <v>62</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
@@ -8684,12 +8668,12 @@
         <v>27</v>
       </c>
       <c r="P116" s="20" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" s="20"/>
       <c r="S116" s="25" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="T116" s="2">
         <v>3</v>
@@ -8698,47 +8682,45 @@
     </row>
     <row r="117" spans="1:21" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="B117" s="32" t="s">
-        <v>56</v>
+        <v>301</v>
       </c>
       <c r="C117" s="32" t="s">
-        <v>57</v>
+        <v>302</v>
       </c>
       <c r="D117" s="20"/>
       <c r="E117" s="20"/>
       <c r="F117" s="32" t="s">
-        <v>58</v>
+        <v>303</v>
       </c>
       <c r="G117" s="32" t="s">
         <v>59</v>
       </c>
       <c r="H117" s="32" t="s">
-        <v>60</v>
+        <v>304</v>
       </c>
       <c r="I117" s="32" t="s">
-        <v>26</v>
+        <v>305</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>61</v>
+        <v>306</v>
       </c>
       <c r="K117" s="20"/>
       <c r="L117" s="22" t="s">
-        <v>62</v>
+        <v>711</v>
       </c>
       <c r="M117" s="22"/>
       <c r="N117" s="22"/>
       <c r="O117" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="P117" s="20" t="s">
-        <v>63</v>
-      </c>
+      <c r="P117" s="20"/>
       <c r="Q117" s="2"/>
       <c r="R117" s="20"/>
       <c r="S117" s="25" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="T117" s="2">
         <v>3</v>
@@ -8747,45 +8729,43 @@
     </row>
     <row r="118" spans="1:21" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>301</v>
+        <v>383</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
       <c r="F118" s="32" t="s">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="G118" s="32" t="s">
-        <v>59</v>
+        <v>287</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="I118" s="32" t="s">
-        <v>305</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="I118" s="32"/>
       <c r="J118" s="23" t="s">
-        <v>306</v>
+        <v>53</v>
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>724</v>
+        <v>387</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
       <c r="O118" s="32" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="P118" s="20"/>
       <c r="Q118" s="2"/>
       <c r="R118" s="20"/>
       <c r="S118" s="25" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="T118" s="2">
         <v>3</v>
@@ -8794,92 +8774,100 @@
     </row>
     <row r="119" spans="1:21" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>385</v>
+        <v>210</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>386</v>
+        <v>203</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="32" t="s">
-        <v>388</v>
+        <v>205</v>
       </c>
       <c r="G119" s="32" t="s">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="I119" s="32"/>
+        <v>213</v>
+      </c>
+      <c r="I119" s="32" t="s">
+        <v>214</v>
+      </c>
       <c r="J119" s="23" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="22" t="s">
-        <v>390</v>
+        <v>216</v>
       </c>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="P119" s="20"/>
+        <v>40</v>
+      </c>
+      <c r="P119" s="20" t="s">
+        <v>71</v>
+      </c>
       <c r="Q119" s="2"/>
       <c r="R119" s="20"/>
       <c r="S119" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T119" s="2">
+        <v>41</v>
+      </c>
+      <c r="T119" s="4">
         <v>3</v>
       </c>
       <c r="U119" s="14"/>
     </row>
     <row r="120" spans="1:21" ht="15" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>203</v>
+        <v>283</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
+        <v>284</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>285</v>
+      </c>
       <c r="F120" s="32" t="s">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>212</v>
+        <v>287</v>
       </c>
       <c r="H120" s="32" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="K120" s="20"/>
       <c r="L120" s="22" t="s">
-        <v>216</v>
+        <v>291</v>
       </c>
       <c r="M120" s="22"/>
       <c r="N120" s="22"/>
       <c r="O120" s="32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P120" s="20" t="s">
-        <v>71</v>
+        <v>292</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" s="20"/>
       <c r="S120" s="25" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="T120" s="4">
         <v>3</v>
@@ -8888,38 +8876,34 @@
     </row>
     <row r="121" spans="1:21" ht="15" customHeight="1">
       <c r="A121" s="15" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>283</v>
+        <v>332</v>
       </c>
       <c r="C121" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="D121" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E121" s="20" t="s">
-        <v>285</v>
-      </c>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
       <c r="F121" s="32" t="s">
-        <v>286</v>
+        <v>58</v>
       </c>
       <c r="G121" s="32" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="H121" s="32" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="J121" s="23" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="K121" s="20"/>
       <c r="L121" s="22" t="s">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="M121" s="22"/>
       <c r="N121" s="22"/>
@@ -8927,7 +8911,7 @@
         <v>36</v>
       </c>
       <c r="P121" s="20" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" s="20"/>
@@ -8941,395 +8925,367 @@
     </row>
     <row r="122" spans="1:21" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="C122" s="32" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
       <c r="F122" s="32" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="G122" s="32" t="s">
-        <v>338</v>
+        <v>230</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>339</v>
+        <v>231</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>340</v>
+        <v>48</v>
       </c>
       <c r="J122" s="23" t="s">
-        <v>341</v>
+        <v>232</v>
       </c>
       <c r="K122" s="20"/>
       <c r="L122" s="22" t="s">
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
       <c r="O122" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="P122" s="20" t="s">
-        <v>196</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="P122" s="20"/>
       <c r="Q122" s="2"/>
       <c r="R122" s="20"/>
       <c r="S122" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T122" s="4">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="T122" s="2">
+        <v>2</v>
       </c>
       <c r="U122" s="14"/>
     </row>
     <row r="123" spans="1:21" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>226</v>
+        <v>389</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>227</v>
+        <v>390</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>228</v>
+        <v>391</v>
       </c>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
       <c r="F123" s="32" t="s">
-        <v>229</v>
+        <v>34</v>
       </c>
       <c r="G123" s="32" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
       <c r="H123" s="32" t="s">
-        <v>231</v>
+        <v>392</v>
       </c>
       <c r="I123" s="32" t="s">
-        <v>48</v>
+        <v>393</v>
       </c>
       <c r="J123" s="23" t="s">
-        <v>232</v>
+        <v>394</v>
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>233</v>
+        <v>632</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="32" t="s">
-        <v>234</v>
+        <v>395</v>
       </c>
       <c r="P123" s="20"/>
       <c r="Q123" s="2"/>
       <c r="R123" s="20"/>
       <c r="S123" s="25" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="T123" s="2">
-        <v>2</v>
-      </c>
-      <c r="U123" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="U123" s="5">
+        <v>162</v>
+      </c>
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
-      <c r="A124" s="15" t="s">
-        <v>392</v>
+      <c r="A124" s="17" t="s">
+        <v>719</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>393</v>
+        <v>317</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>394</v>
+        <v>318</v>
       </c>
       <c r="D124" s="20"/>
       <c r="E124" s="20"/>
       <c r="F124" s="32" t="s">
-        <v>34</v>
+        <v>319</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>73</v>
+        <v>320</v>
       </c>
       <c r="H124" s="32" t="s">
-        <v>395</v>
+        <v>321</v>
       </c>
       <c r="I124" s="32" t="s">
-        <v>396</v>
+        <v>322</v>
       </c>
       <c r="J124" s="23" t="s">
-        <v>397</v>
+        <v>323</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="22" t="s">
-        <v>635</v>
+        <v>324</v>
       </c>
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="32" t="s">
-        <v>398</v>
+        <v>27</v>
       </c>
       <c r="P124" s="20"/>
       <c r="Q124" s="2"/>
       <c r="R124" s="20"/>
       <c r="S124" s="25" t="s">
-        <v>28</v>
+        <v>201</v>
       </c>
       <c r="T124" s="2">
         <v>3</v>
       </c>
-      <c r="U124" s="5">
-        <v>162</v>
-      </c>
+      <c r="U124" s="14"/>
     </row>
     <row r="125" spans="1:21" ht="15" customHeight="1">
-      <c r="A125" s="17" t="s">
-        <v>732</v>
+      <c r="A125" s="15" t="s">
+        <v>241</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="C125" s="32" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="D125" s="20"/>
       <c r="E125" s="20"/>
       <c r="F125" s="32" t="s">
-        <v>319</v>
+        <v>244</v>
       </c>
       <c r="G125" s="32" t="s">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="H125" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="I125" s="32" t="s">
-        <v>322</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I125" s="32"/>
       <c r="J125" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="K125" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="K125" s="20" t="s">
+        <v>449</v>
+      </c>
       <c r="L125" s="22" t="s">
-        <v>324</v>
+        <v>450</v>
       </c>
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
       <c r="O125" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P125" s="20"/>
-      <c r="Q125" s="2"/>
-      <c r="R125" s="20"/>
+        <v>50</v>
+      </c>
+      <c r="P125" s="20">
+        <v>240</v>
+      </c>
+      <c r="Q125" s="2">
+        <v>1350</v>
+      </c>
+      <c r="R125" s="20">
+        <v>1370</v>
+      </c>
       <c r="S125" s="25" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="T125" s="2">
         <v>3</v>
       </c>
-      <c r="U125" s="14"/>
+      <c r="U125" s="5">
+        <v>129</v>
+      </c>
     </row>
     <row r="126" spans="1:21" ht="15" customHeight="1">
       <c r="A126" s="15" t="s">
-        <v>241</v>
+        <v>364</v>
       </c>
       <c r="B126" s="32" t="s">
-        <v>242</v>
+        <v>365</v>
       </c>
       <c r="C126" s="32" t="s">
-        <v>243</v>
+        <v>366</v>
       </c>
       <c r="D126" s="20"/>
       <c r="E126" s="20"/>
       <c r="F126" s="32" t="s">
-        <v>244</v>
+        <v>58</v>
       </c>
       <c r="G126" s="32" t="s">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="H126" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="I126" s="32"/>
+        <v>147</v>
+      </c>
+      <c r="I126" s="32" t="s">
+        <v>368</v>
+      </c>
       <c r="J126" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="K126" s="20" t="s">
-        <v>452</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="K126" s="20"/>
       <c r="L126" s="22" t="s">
-        <v>453</v>
+        <v>369</v>
       </c>
       <c r="M126" s="22"/>
       <c r="N126" s="22"/>
       <c r="O126" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="P126" s="20">
-        <v>240</v>
-      </c>
-      <c r="Q126" s="2">
-        <v>1350</v>
-      </c>
-      <c r="R126" s="20">
-        <v>1370</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="P126" s="20"/>
+      <c r="Q126" s="2"/>
+      <c r="R126" s="20"/>
       <c r="S126" s="25" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="T126" s="2">
         <v>3</v>
       </c>
       <c r="U126" s="5">
-        <v>129</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:21" ht="15" customHeight="1">
       <c r="A127" s="15" t="s">
-        <v>367</v>
+        <v>235</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>368</v>
+        <v>236</v>
       </c>
       <c r="C127" s="32" t="s">
-        <v>369</v>
+        <v>237</v>
       </c>
       <c r="D127" s="20"/>
       <c r="E127" s="20"/>
       <c r="F127" s="32" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="G127" s="32" t="s">
-        <v>370</v>
+        <v>239</v>
       </c>
       <c r="H127" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="I127" s="32" t="s">
-        <v>371</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="I127" s="32"/>
       <c r="J127" s="23" t="s">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="K127" s="20"/>
       <c r="L127" s="22" t="s">
-        <v>372</v>
+        <v>54</v>
       </c>
       <c r="M127" s="22"/>
       <c r="N127" s="22"/>
       <c r="O127" s="32" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="P127" s="20"/>
       <c r="Q127" s="2"/>
       <c r="R127" s="20"/>
       <c r="S127" s="25" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="T127" s="2">
         <v>3</v>
       </c>
       <c r="U127" s="5">
-        <v>181</v>
+        <v>136</v>
       </c>
     </row>
     <row r="128" spans="1:21" ht="15" customHeight="1">
       <c r="A128" s="15" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="C128" s="32" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="D128" s="20"/>
       <c r="E128" s="20"/>
       <c r="F128" s="32" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="G128" s="32" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="H128" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="I128" s="32"/>
+        <v>271</v>
+      </c>
+      <c r="I128" s="31" t="s">
+        <v>578</v>
+      </c>
       <c r="J128" s="23" t="s">
-        <v>53</v>
+        <v>630</v>
       </c>
       <c r="K128" s="20"/>
       <c r="L128" s="22" t="s">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="M128" s="22"/>
       <c r="N128" s="22"/>
       <c r="O128" s="32" t="s">
-        <v>40</v>
+        <v>273</v>
       </c>
       <c r="P128" s="20"/>
       <c r="Q128" s="2"/>
       <c r="R128" s="20"/>
       <c r="S128" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T128" s="2">
+        <v>41</v>
+      </c>
+      <c r="T128" s="4">
         <v>3</v>
       </c>
       <c r="U128" s="5">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:21" ht="15" customHeight="1">
-      <c r="A129" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B129" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="C129" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="G129" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="H129" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="I129" s="31" t="s">
-        <v>581</v>
-      </c>
-      <c r="J129" s="23" t="s">
-        <v>633</v>
-      </c>
-      <c r="K129" s="20"/>
-      <c r="L129" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="M129" s="22"/>
-      <c r="N129" s="22"/>
-      <c r="O129" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="P129" s="20"/>
-      <c r="Q129" s="2"/>
-      <c r="R129" s="20"/>
-      <c r="S129" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T129" s="4">
-        <v>3</v>
-      </c>
-      <c r="U129" s="5">
-        <v>121</v>
-      </c>
+      <c r="A129" s="15"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="38"/>
+      <c r="D129" s="15"/>
+      <c r="E129" s="15"/>
+      <c r="F129" s="33"/>
+      <c r="G129" s="33"/>
+      <c r="H129" s="33"/>
+      <c r="I129" s="33"/>
+      <c r="J129" s="23"/>
+      <c r="K129" s="24"/>
+      <c r="L129" s="23"/>
+      <c r="M129" s="15"/>
+      <c r="N129" s="15"/>
+      <c r="O129" s="38"/>
+      <c r="P129" s="21"/>
+      <c r="R129" s="21"/>
+      <c r="S129" s="26"/>
+      <c r="U129" s="14"/>
     </row>
     <row r="130" spans="1:21" ht="15" customHeight="1">
       <c r="A130" s="15"/>
@@ -9356,43 +9312,43 @@
       <c r="A131" s="15"/>
       <c r="B131" s="33"/>
       <c r="C131" s="38"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="21"/>
       <c r="F131" s="33"/>
       <c r="G131" s="33"/>
       <c r="H131" s="33"/>
       <c r="I131" s="33"/>
       <c r="J131" s="23"/>
-      <c r="K131" s="24"/>
+      <c r="K131" s="23"/>
       <c r="L131" s="23"/>
-      <c r="M131" s="15"/>
-      <c r="N131" s="15"/>
+      <c r="M131" s="21"/>
+      <c r="N131" s="21"/>
       <c r="O131" s="38"/>
       <c r="P131" s="21"/>
       <c r="R131" s="21"/>
-      <c r="S131" s="26"/>
+      <c r="S131" s="25"/>
+      <c r="T131" s="2"/>
       <c r="U131" s="14"/>
     </row>
     <row r="132" spans="1:21" ht="15" customHeight="1">
       <c r="A132" s="15"/>
       <c r="B132" s="33"/>
       <c r="C132" s="38"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="21"/>
+      <c r="D132" s="15"/>
+      <c r="E132" s="15"/>
       <c r="F132" s="33"/>
       <c r="G132" s="33"/>
       <c r="H132" s="33"/>
       <c r="I132" s="33"/>
       <c r="J132" s="23"/>
-      <c r="K132" s="23"/>
+      <c r="K132" s="24"/>
       <c r="L132" s="23"/>
-      <c r="M132" s="21"/>
-      <c r="N132" s="21"/>
+      <c r="M132" s="15"/>
+      <c r="N132" s="15"/>
       <c r="O132" s="38"/>
       <c r="P132" s="21"/>
       <c r="R132" s="21"/>
-      <c r="S132" s="25"/>
-      <c r="T132" s="2"/>
+      <c r="S132" s="26"/>
       <c r="U132" s="14"/>
     </row>
     <row r="133" spans="1:21" ht="15" customHeight="1">
@@ -9459,24 +9415,6 @@
       <c r="U135" s="14"/>
     </row>
     <row r="136" spans="1:21" ht="15" customHeight="1">
-      <c r="A136" s="15"/>
-      <c r="B136" s="33"/>
-      <c r="C136" s="38"/>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="33"/>
-      <c r="G136" s="33"/>
-      <c r="H136" s="33"/>
-      <c r="I136" s="33"/>
-      <c r="J136" s="23"/>
-      <c r="K136" s="24"/>
-      <c r="L136" s="23"/>
-      <c r="M136" s="15"/>
-      <c r="N136" s="15"/>
-      <c r="O136" s="38"/>
-      <c r="P136" s="21"/>
-      <c r="R136" s="21"/>
-      <c r="S136" s="26"/>
       <c r="U136" s="14"/>
     </row>
     <row r="137" spans="1:21" ht="15" customHeight="1">
@@ -11021,12 +10959,9 @@
     <row r="650" spans="21:21" ht="15" customHeight="1">
       <c r="U650" s="14"/>
     </row>
-    <row r="651" spans="21:21" ht="15" customHeight="1">
-      <c r="U651" s="14"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U136">
-    <sortCondition ref="C2:C136"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U135">
+    <sortCondition ref="C2:C135"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -11077,55 +11012,55 @@
     <hyperlink ref="A43" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
     <hyperlink ref="A51" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg/960px-Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{52FF7A73-D4C9-49E4-9DA8-B4D571EE14DF}"/>
     <hyperlink ref="A47" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44F48270-0A28-4A76-9385-8855A77BD678}"/>
-    <hyperlink ref="A104" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
-    <hyperlink ref="A55" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/b/bd/Rotterdam_standbeeld_Erasmus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{8D48BE19-49C1-4A59-9D87-2A838B718323}"/>
-    <hyperlink ref="A54" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A60" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
-    <hyperlink ref="A63" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
-    <hyperlink ref="A68" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A7D7D432-2C44-4D93-9AD5-BCE850FF4010}"/>
-    <hyperlink ref="A69" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
-    <hyperlink ref="A72" r:id="rId55" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId56" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId57" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId58" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A78" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Sant%27agnese_in_agone%2C_interno_06.JPG/960px-Sant%27agnese_in_agone%2C_interno_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43F44C46-51CA-4A19-8F06-CEDF5D2AF317}"/>
-    <hyperlink ref="A80" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A81" r:id="rId61" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
-    <hyperlink ref="A83" r:id="rId62" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A113" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Toulon_caryatides_p1040271.jpg/960px-Toulon_caryatides_p1040271.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{72500094-C016-4577-BD72-A067C687B29D}"/>
-    <hyperlink ref="A114" r:id="rId64" display="https://upload.wikimedia.org/wikipedia/commons/4/4a/Puget_-_Diogenes_Alexander_Louvre.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{7304CB1E-C333-42F2-8267-9517DBDE8CC0}"/>
-    <hyperlink ref="A115" r:id="rId65" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
-    <hyperlink ref="A107" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
-    <hyperlink ref="A106" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A101" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D133D4F9-387C-41F9-B0C0-5378E60BF7CF}"/>
-    <hyperlink ref="A95" r:id="rId69" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A96" r:id="rId70" xr:uid="{F31CE0DA-AF1D-47AA-AF9C-4B7E4D8C86C1}"/>
-    <hyperlink ref="A97" r:id="rId71" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
-    <hyperlink ref="A88" r:id="rId72" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A89" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg/960px-Domenico_Guidi-Angel_bearing_a_lance-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D14F3A35-A0A6-443F-B83E-30FAABFF4B83}"/>
-    <hyperlink ref="A92" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CF7BA0BC-0AF1-43BC-B403-A08617016A90}"/>
-    <hyperlink ref="A94" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{01772568-8B55-4ED2-9BBD-D73E5C058AAF}"/>
-    <hyperlink ref="A20" r:id="rId76" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A99" r:id="rId78" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId80" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A48" r:id="rId81" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId82" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId83" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId84" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId85" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A105" r:id="rId87" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A103" r:id="rId88" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
-    <hyperlink ref="A58" r:id="rId89" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
-    <hyperlink ref="A125" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
-    <hyperlink ref="A56" r:id="rId91" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
-    <hyperlink ref="A76" r:id="rId92" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
-    <hyperlink ref="A61" r:id="rId93" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{146FD4EB-CB96-47AE-B9BA-B7CFC3A2E4C7}"/>
-    <hyperlink ref="A67" r:id="rId94" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
-    <hyperlink ref="A64" r:id="rId95" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
-    <hyperlink ref="A65" r:id="rId96" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
+    <hyperlink ref="A103" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
+    <hyperlink ref="A54" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
+    <hyperlink ref="A60" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
+    <hyperlink ref="A63" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
+    <hyperlink ref="A69" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
+    <hyperlink ref="A72" r:id="rId53" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId54" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId55" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A80" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
+    <hyperlink ref="A81" r:id="rId58" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
+    <hyperlink ref="A83" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A114" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
+    <hyperlink ref="A106" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
+    <hyperlink ref="A105" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
+    <hyperlink ref="A95" r:id="rId63" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A96" r:id="rId64" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
+    <hyperlink ref="A88" r:id="rId65" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A20" r:id="rId66" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A98" r:id="rId68" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId70" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A48" r:id="rId71" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId72" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId73" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId74" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId75" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A104" r:id="rId77" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A102" r:id="rId78" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId79" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A124" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId81" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId82" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A61" r:id="rId83" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{146FD4EB-CB96-47AE-B9BA-B7CFC3A2E4C7}"/>
+    <hyperlink ref="A67" r:id="rId84" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
+    <hyperlink ref="A64" r:id="rId85" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
+    <hyperlink ref="A65" r:id="rId86" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
+    <hyperlink ref="A112" r:id="rId87" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
+    <hyperlink ref="A89" r:id="rId88" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
+    <hyperlink ref="A113" r:id="rId89" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
+    <hyperlink ref="A55" r:id="rId90" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
+    <hyperlink ref="A92" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
+    <hyperlink ref="A94" r:id="rId92" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
+    <hyperlink ref="A100" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
+    <hyperlink ref="A78" r:id="rId94" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
+    <hyperlink ref="A68" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
+    <hyperlink ref="A66" r:id="rId96" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C14C386-E731-4B03-8BEA-ADA1FC9FCBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D3C8E6-4FB4-4FEA-968A-6E62B90E3CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1881,9 +1881,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
   </si>
   <si>
-    <t>960px-0_Statue_de_Sainte_Hélène_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG (960×1440)</t>
-  </si>
-  <si>
     <t>Sainte Hélène de Constantinople</t>
   </si>
   <si>
@@ -1905,18 +1902,12 @@
     <t>Salon de la Guerre</t>
   </si>
   <si>
-    <t>960px-Cenotaph_of_Mazarin,_Paris_6th_004.jpg (960×1445)</t>
-  </si>
-  <si>
     <t>Institut de France</t>
   </si>
   <si>
     <t>Buste de Charles Le Brun</t>
   </si>
   <si>
-    <t>960px-Vase_de_la_guerre_au_Château_de_Versailles_le_9_décembre_2014_-_01.jpg (960×1440)</t>
-  </si>
-  <si>
     <t>1684-1685</t>
   </si>
   <si>
@@ -1947,18 +1938,12 @@
     <t>88 stèles</t>
   </si>
   <si>
-    <t>960px-San_Francisco_sobre_el_sepulcro,_Pedro_de_Mena.jpg (960×1280)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saint François d'Assise </t>
   </si>
   <si>
     <t>"Vierge de douleur"</t>
   </si>
   <si>
-    <t>1280px-Four_Corners_4_of_4_(4067010861).jpg (1280×857)</t>
-  </si>
-  <si>
     <t>Statues des Nations vaincues</t>
   </si>
   <si>
@@ -1974,9 +1959,6 @@
     <t>Cénotaphe de Jacob van Wassenaer Obdam</t>
   </si>
   <si>
-    <t>Fontana_dei_fiumi_(Rome)_-_Nile.jpg (927×1280)</t>
-  </si>
-  <si>
     <t>Le Nil</t>
   </si>
   <si>
@@ -2019,9 +2001,6 @@
     <t>c,400</t>
   </si>
   <si>
-    <t>S.m. del carmine, int., cappella corsini, g.b. foggini, apparizione di maria a s.andrea corsini, 1683-91 ca. - Catégorie : Reliefs de Giovanni Battista Foggini dans la Cappella Corsini - Wikimedia Commons</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cathédrale Saint-Paul </t>
   </si>
   <si>
@@ -2040,27 +2019,18 @@
     <t xml:space="preserve">Atlantes </t>
   </si>
   <si>
-    <t>Pierre_Puget_-_Louis_XIV.jpg (1828×1732)</t>
-  </si>
-  <si>
     <t>Marseile</t>
   </si>
   <si>
     <t>Musée des Beaux-Arts</t>
   </si>
   <si>
-    <t>Médailon à l'effigie de Louis XIV</t>
-  </si>
-  <si>
     <t xml:space="preserve">Porte Saint-Denis </t>
   </si>
   <si>
     <t>Reliefs</t>
   </si>
   <si>
-    <t>960px-Ecce_Homo,_Capilla_Real_de_Granada.jpg (960×1280)</t>
-  </si>
-  <si>
     <t>Capilla real</t>
   </si>
   <si>
@@ -2082,9 +2052,6 @@
     <t xml:space="preserve"> Eglise de San Bernardo alle Terme</t>
   </si>
   <si>
-    <t>Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg (1800×2120)</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/d/dd/Guidi_Renomm%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -2245,6 +2212,39 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Epitaph_of_Adriaen_Vryburch.jpg/500px-Epitaph_of_Adriaen_Vryburch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Médaillon à l'effigie de Louis XIV</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg/960px-Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3274,11 +3274,11 @@
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -4210,7 +4210,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
@@ -4265,11 +4265,11 @@
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4771,13 +4771,13 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>615</v>
+        <v>729</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>572</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="43" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -4944,7 +4944,7 @@
         <v>548</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="3" t="s">
@@ -5027,13 +5027,13 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
@@ -5050,10 +5050,10 @@
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="L43" s="43" t="s">
         <v>398</v>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>626</v>
+        <v>728</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5255,14 +5255,14 @@
         <v>46</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -5379,7 +5379,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5403,10 +5403,10 @@
         <v>53</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>623</v>
+        <v>735</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5455,7 +5455,7 @@
         <v>48</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="43" t="s">
@@ -5480,7 +5480,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="43" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>218</v>
@@ -5657,7 +5657,7 @@
         <v>1600</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
@@ -5688,13 +5688,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="B58" s="31" t="s">
         <v>332</v>
@@ -5847,7 +5847,7 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>332</v>
@@ -5870,11 +5870,11 @@
         <v>553</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>637</v>
+        <v>734</v>
       </c>
       <c r="B60" s="31" t="s">
         <v>332</v>
@@ -5919,11 +5919,11 @@
         <v>550</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -5996,7 +5996,7 @@
       <c r="U61" s="14"/>
     </row>
     <row r="62" spans="1:21" ht="15" customHeight="1">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="17" t="s">
         <v>293</v>
       </c>
       <c r="B62" s="32" t="s">
@@ -6050,7 +6050,7 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>640</v>
+        <v>732</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>294</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
       <c r="A66" s="52" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>125</v>
@@ -6223,11 +6223,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="B67" s="31" t="s">
         <v>590</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6276,7 +6276,7 @@
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6297,13 +6297,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="B68" s="29" t="s">
         <v>593</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6320,11 +6320,11 @@
         <v>589</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6345,13 +6345,13 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>646</v>
+        <v>731</v>
       </c>
       <c r="B69" s="31" t="s">
         <v>573</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
@@ -6374,7 +6374,7 @@
         <v>406</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
@@ -6395,13 +6395,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6418,11 +6418,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6539,7 +6539,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6562,11 +6562,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6720,7 +6720,7 @@
         <v>546</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="44" t="s">
@@ -6817,7 +6817,7 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
@@ -6891,7 +6891,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6914,7 +6914,7 @@
         <v>531</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
@@ -6939,13 +6939,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>661</v>
+        <v>730</v>
       </c>
       <c r="B81" s="31" t="s">
         <v>575</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6962,13 +6962,13 @@
         <v>531</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7012,11 +7012,11 @@
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7159,7 +7159,7 @@
         <v>458</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
@@ -7257,10 +7257,10 @@
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7360,11 +7360,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7481,13 +7481,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="B92" s="31" t="s">
         <v>584</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7504,11 +7504,11 @@
         <v>583</v>
       </c>
       <c r="J92" s="51" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7574,13 +7574,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="B94" s="31" t="s">
         <v>587</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7597,7 +7597,7 @@
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>682</v>
+        <v>736</v>
       </c>
       <c r="B96" s="31" t="s">
         <v>234</v>
@@ -7764,13 +7764,13 @@
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1">
       <c r="A98" s="49" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B98" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
@@ -7787,11 +7787,11 @@
         <v>26</v>
       </c>
       <c r="J98" s="44" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="K98" s="40"/>
       <c r="L98" s="44" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="M98" s="11"/>
       <c r="N98" s="11"/>
@@ -7859,7 +7859,7 @@
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1">
       <c r="A100" s="46" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="B100" s="31" t="s">
         <v>145</v>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="K100" s="40"/>
       <c r="L100" s="44" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="M100" s="11"/>
       <c r="N100" s="11"/>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1">
       <c r="A102" s="17" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="B102" s="33" t="s">
         <v>121</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B103" s="31" t="s">
         <v>121</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="B104" s="31" t="s">
         <v>121</v>
@@ -8094,13 +8094,13 @@
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B105" s="31" t="s">
         <v>580</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
@@ -8117,7 +8117,7 @@
         <v>548</v>
       </c>
       <c r="J105" s="44" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="K105" s="40"/>
       <c r="L105" s="44" t="s">
@@ -8129,7 +8129,7 @@
         <v>36</v>
       </c>
       <c r="P105" s="36" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="R105" s="11"/>
       <c r="S105" s="12"/>
@@ -8142,13 +8142,13 @@
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>674</v>
+        <v>733</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -8165,7 +8165,7 @@
         <v>548</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
@@ -8439,7 +8439,7 @@
     </row>
     <row r="112" spans="1:21" ht="15" customHeight="1">
       <c r="A112" s="46" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="B112" s="31" t="s">
         <v>234</v>
@@ -8462,11 +8462,11 @@
         <v>410</v>
       </c>
       <c r="J112" s="44" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="K112" s="40"/>
       <c r="L112" s="44" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="M112" s="11"/>
       <c r="N112" s="11"/>
@@ -8485,7 +8485,7 @@
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="B113" s="31" t="s">
         <v>234</v>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="K113" s="40"/>
       <c r="L113" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
@@ -8538,7 +8538,7 @@
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
       <c r="B114" s="31" t="s">
         <v>234</v>
@@ -8558,14 +8558,14 @@
         <v>392</v>
       </c>
       <c r="I114" s="31" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="J114" s="44" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="K114" s="40"/>
       <c r="L114" s="44" t="s">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="M114" s="11"/>
       <c r="N114" s="11"/>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="22" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="K117" s="20"/>
       <c r="L117" s="22" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="M117" s="22"/>
       <c r="N117" s="22"/>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
@@ -9021,7 +9021,7 @@
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
       <c r="A124" s="17" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="B124" s="32" t="s">
         <v>317</v>
@@ -9242,7 +9242,7 @@
         <v>578</v>
       </c>
       <c r="J128" s="23" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K128" s="20"/>
       <c r="L128" s="22" t="s">
@@ -11007,60 +11007,61 @@
     <hyperlink ref="A77" r:id="rId40" xr:uid="{2A9F7667-9C72-415B-BDA0-7897AF200BC7}"/>
     <hyperlink ref="A9" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{36A963F9-1859-4BB5-AF7B-1749A3316556}"/>
     <hyperlink ref="A10" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{5D5A21F2-A411-44D1-BB9B-2C0C70D5524C}"/>
-    <hyperlink ref="A38" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1772B789-BFB5-4FDC-8337-89F821F64C32}"/>
-    <hyperlink ref="A41" r:id="rId44" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
-    <hyperlink ref="A43" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
-    <hyperlink ref="A51" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg/960px-Cenotaph_of_Mazarin%2C_Paris_6th_004.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{52FF7A73-D4C9-49E4-9DA8-B4D571EE14DF}"/>
-    <hyperlink ref="A47" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{44F48270-0A28-4A76-9385-8855A77BD678}"/>
-    <hyperlink ref="A103" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
-    <hyperlink ref="A54" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A60" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg/960px-San_Francisco_sobre_el_sepulcro%2C_Pedro_de_Mena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EDBD5279-653B-431D-86A4-BF8C3BE4670A}"/>
-    <hyperlink ref="A63" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Four_Corners_4_of_4_%284067010861%29.jpg/1280px-Four_Corners_4_of_4_%284067010861%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{E0B125E3-0608-48F9-A328-F1833CFDE1F6}"/>
-    <hyperlink ref="A69" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{4C0D2493-1798-443B-BD8E-B99A35DB2811}"/>
-    <hyperlink ref="A72" r:id="rId53" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId54" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId55" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A80" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A81" r:id="rId58" location="/media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" display="https://commons.wikimedia.org/wiki/Category:Reliefs_by_Giovanni_Battista_Foggini_in_the_Cappella_Corsini - /media/File:S.m._del_carmine,_int.,_cappella_corsini,_g.b._foggini,_apparizione_di_maria_a_s.andrea_corsini,_1683-91_ca..JPG" xr:uid="{985F2FD8-D172-466E-A331-AA41EDCEE450}"/>
-    <hyperlink ref="A83" r:id="rId59" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A114" r:id="rId60" display="https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{11A466AF-140C-4BD9-BAA3-92900137B2D8}"/>
-    <hyperlink ref="A106" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Ecce_Homo%2C_Capilla_Real_de_Granada.jpg/960px-Ecce_Homo%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{98CB4871-0E7E-4013-B71A-5C9D1845D356}"/>
-    <hyperlink ref="A105" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A95" r:id="rId63" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A96" r:id="rId64" display="https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{E58B31CC-7032-421C-94C6-F7F9AF575661}"/>
-    <hyperlink ref="A88" r:id="rId65" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A20" r:id="rId66" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A98" r:id="rId68" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId70" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A48" r:id="rId71" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId72" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId73" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId74" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId75" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A104" r:id="rId77" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A102" r:id="rId78" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
-    <hyperlink ref="A58" r:id="rId79" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
-    <hyperlink ref="A124" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
-    <hyperlink ref="A56" r:id="rId81" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
-    <hyperlink ref="A76" r:id="rId82" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
-    <hyperlink ref="A61" r:id="rId83" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{146FD4EB-CB96-47AE-B9BA-B7CFC3A2E4C7}"/>
-    <hyperlink ref="A67" r:id="rId84" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
-    <hyperlink ref="A64" r:id="rId85" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
-    <hyperlink ref="A65" r:id="rId86" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
-    <hyperlink ref="A112" r:id="rId87" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
-    <hyperlink ref="A89" r:id="rId88" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
-    <hyperlink ref="A113" r:id="rId89" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
-    <hyperlink ref="A55" r:id="rId90" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
-    <hyperlink ref="A92" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
-    <hyperlink ref="A94" r:id="rId92" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
-    <hyperlink ref="A100" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
-    <hyperlink ref="A78" r:id="rId94" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
-    <hyperlink ref="A68" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
-    <hyperlink ref="A66" r:id="rId96" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
+    <hyperlink ref="A41" r:id="rId43" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
+    <hyperlink ref="A43" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
+    <hyperlink ref="A103" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
+    <hyperlink ref="A54" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
+    <hyperlink ref="A72" r:id="rId47" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId48" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId49" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A80" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
+    <hyperlink ref="A83" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A105" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
+    <hyperlink ref="A95" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A88" r:id="rId55" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A20" r:id="rId56" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A98" r:id="rId58" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId60" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A48" r:id="rId61" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId62" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId63" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId64" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId65" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A104" r:id="rId67" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A102" r:id="rId68" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId69" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A124" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId71" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId72" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A67" r:id="rId73" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
+    <hyperlink ref="A64" r:id="rId74" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
+    <hyperlink ref="A65" r:id="rId75" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
+    <hyperlink ref="A112" r:id="rId76" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
+    <hyperlink ref="A89" r:id="rId77" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
+    <hyperlink ref="A113" r:id="rId78" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
+    <hyperlink ref="A55" r:id="rId79" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
+    <hyperlink ref="A92" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
+    <hyperlink ref="A94" r:id="rId81" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
+    <hyperlink ref="A100" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
+    <hyperlink ref="A78" r:id="rId83" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
+    <hyperlink ref="A68" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
+    <hyperlink ref="A66" r:id="rId85" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
+    <hyperlink ref="A61" r:id="rId86" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{7CC81E97-336C-4BE3-9FAB-830B94A1ED65}"/>
+    <hyperlink ref="A114" r:id="rId87" xr:uid="{4AB8AFAA-AC83-45E2-9518-E2D11E6D96B0}"/>
+    <hyperlink ref="A47" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{26C53F9C-E257-4CAE-A946-AC2781FD39DA}"/>
+    <hyperlink ref="A38" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F20C007B-8F5D-4991-B161-59964EC6A904}"/>
+    <hyperlink ref="A81" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E845835-848D-41BC-990F-0451F6EDC6B6}"/>
+    <hyperlink ref="A69" r:id="rId91" xr:uid="{100C0767-B909-4784-8140-124E31407B35}"/>
+    <hyperlink ref="A62" r:id="rId92" xr:uid="{EBB6B418-7671-46B4-8264-66B320EA6644}"/>
+    <hyperlink ref="A63" r:id="rId93" xr:uid="{4531BD62-CB46-48D7-A458-DCEED66905FA}"/>
+    <hyperlink ref="A106" r:id="rId94" xr:uid="{D187F26A-6548-4108-847B-E7C9C32C11E1}"/>
+    <hyperlink ref="A60" r:id="rId95" xr:uid="{0FA07B7D-6A05-40FA-BD8E-65ED21205D3E}"/>
+    <hyperlink ref="A51" r:id="rId96" xr:uid="{1572CB3F-0825-489E-930B-D185D839CFAB}"/>
+    <hyperlink ref="A96" r:id="rId97" xr:uid="{2C8E7F40-8076-41F1-8377-4886D132DE7E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D3C8E6-4FB4-4FEA-968A-6E62B90E3CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EDE9E2-2A23-4783-B983-B15AA2393C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="737">
   <si>
     <t>Image</t>
   </si>
@@ -1920,9 +1920,6 @@
     <t xml:space="preserve">Eglise Saint-Nicolas </t>
   </si>
   <si>
-    <t>960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG (960×1278)</t>
-  </si>
-  <si>
     <t>"Décors de l'Oratoire du Rosaire"</t>
   </si>
   <si>
@@ -1983,9 +1980,6 @@
     <t xml:space="preserve">Sant'Agnese in Agone </t>
   </si>
   <si>
-    <t>960px-Giuliano_finelli,_ritratto_di_michelangelo_il_giovane,_1630.JPG (960×1324)</t>
-  </si>
-  <si>
     <t>Casa Buonarroti</t>
   </si>
   <si>
@@ -2034,9 +2028,6 @@
     <t>Capilla real</t>
   </si>
   <si>
-    <t>960px-Dolorosa,_Capilla_Real_de_Granada.jpg (960×1280)</t>
-  </si>
-  <si>
     <t>Bernardo de</t>
   </si>
   <si>
@@ -2245,6 +2236,15 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3274,11 +3274,11 @@
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -4210,7 +4210,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
@@ -4265,11 +4265,11 @@
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4771,13 +4771,13 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>572</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -5033,7 +5033,7 @@
         <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5379,7 +5379,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>218</v>
@@ -5657,7 +5657,7 @@
         <v>1600</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
@@ -5688,13 +5688,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B58" s="31" t="s">
         <v>332</v>
@@ -5847,7 +5847,7 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>332</v>
@@ -5870,11 +5870,11 @@
         <v>553</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B60" s="31" t="s">
         <v>332</v>
@@ -5919,11 +5919,11 @@
         <v>550</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -6050,7 +6050,7 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>294</v>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
       <c r="A66" s="52" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>125</v>
@@ -6223,11 +6223,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B67" s="31" t="s">
         <v>590</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6276,7 +6276,7 @@
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6297,13 +6297,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B68" s="29" t="s">
         <v>593</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6320,11 +6320,11 @@
         <v>589</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6345,13 +6345,13 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B69" s="31" t="s">
         <v>573</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
@@ -6374,7 +6374,7 @@
         <v>406</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
@@ -6395,13 +6395,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6418,11 +6418,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6539,7 +6539,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6562,11 +6562,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6817,7 +6817,7 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
@@ -6891,7 +6891,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>649</v>
+        <v>735</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6907,14 +6907,14 @@
       <c r="G80" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="H80" s="31" t="s">
-        <v>539</v>
+      <c r="H80" s="31">
+        <v>1630</v>
       </c>
       <c r="I80" s="31" t="s">
         <v>531</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
@@ -6939,13 +6939,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B81" s="31" t="s">
         <v>575</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6962,13 +6962,13 @@
         <v>531</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K81" s="40" t="s">
+        <v>649</v>
+      </c>
+      <c r="L81" s="44" t="s">
         <v>651</v>
-      </c>
-      <c r="L81" s="44" t="s">
-        <v>653</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7012,11 +7012,11 @@
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7159,7 +7159,7 @@
         <v>458</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
@@ -7257,10 +7257,10 @@
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7360,11 +7360,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7481,13 +7481,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B92" s="31" t="s">
         <v>584</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7504,11 +7504,11 @@
         <v>583</v>
       </c>
       <c r="J92" s="51" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7574,13 +7574,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B94" s="31" t="s">
         <v>587</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7597,7 +7597,7 @@
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B96" s="31" t="s">
         <v>234</v>
@@ -7764,13 +7764,13 @@
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1">
       <c r="A98" s="49" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B98" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
@@ -7787,11 +7787,11 @@
         <v>26</v>
       </c>
       <c r="J98" s="44" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="K98" s="40"/>
       <c r="L98" s="44" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M98" s="11"/>
       <c r="N98" s="11"/>
@@ -7859,7 +7859,7 @@
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1">
       <c r="A100" s="46" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B100" s="31" t="s">
         <v>145</v>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="K100" s="40"/>
       <c r="L100" s="44" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M100" s="11"/>
       <c r="N100" s="11"/>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1">
       <c r="A102" s="17" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B102" s="33" t="s">
         <v>121</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>628</v>
+        <v>734</v>
       </c>
       <c r="B103" s="31" t="s">
         <v>121</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B104" s="31" t="s">
         <v>121</v>
@@ -8094,13 +8094,13 @@
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>666</v>
+        <v>736</v>
       </c>
       <c r="B105" s="31" t="s">
         <v>580</v>
       </c>
       <c r="C105" s="47" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
@@ -8117,7 +8117,7 @@
         <v>548</v>
       </c>
       <c r="J105" s="44" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K105" s="40"/>
       <c r="L105" s="44" t="s">
@@ -8129,7 +8129,7 @@
         <v>36</v>
       </c>
       <c r="P105" s="36" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="R105" s="11"/>
       <c r="S105" s="12"/>
@@ -8142,13 +8142,13 @@
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1">
       <c r="A106" s="46" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
@@ -8165,7 +8165,7 @@
         <v>548</v>
       </c>
       <c r="J106" s="44" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="44" t="s">
@@ -8439,7 +8439,7 @@
     </row>
     <row r="112" spans="1:21" ht="15" customHeight="1">
       <c r="A112" s="46" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B112" s="31" t="s">
         <v>234</v>
@@ -8462,11 +8462,11 @@
         <v>410</v>
       </c>
       <c r="J112" s="44" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="K112" s="40"/>
       <c r="L112" s="44" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="M112" s="11"/>
       <c r="N112" s="11"/>
@@ -8485,7 +8485,7 @@
     </row>
     <row r="113" spans="1:21" ht="15" customHeight="1">
       <c r="A113" s="46" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B113" s="31" t="s">
         <v>234</v>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="K113" s="40"/>
       <c r="L113" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="M113" s="11"/>
       <c r="N113" s="11"/>
@@ -8538,7 +8538,7 @@
     </row>
     <row r="114" spans="1:21" ht="15" customHeight="1">
       <c r="A114" s="46" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B114" s="31" t="s">
         <v>234</v>
@@ -8558,14 +8558,14 @@
         <v>392</v>
       </c>
       <c r="I114" s="31" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="J114" s="44" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K114" s="40"/>
       <c r="L114" s="44" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="M114" s="11"/>
       <c r="N114" s="11"/>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="22" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="K117" s="20"/>
       <c r="L117" s="22" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="M117" s="22"/>
       <c r="N117" s="22"/>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
@@ -9021,7 +9021,7 @@
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
       <c r="A124" s="17" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B124" s="32" t="s">
         <v>317</v>
@@ -11009,59 +11009,59 @@
     <hyperlink ref="A10" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{5D5A21F2-A411-44D1-BB9B-2C0C70D5524C}"/>
     <hyperlink ref="A41" r:id="rId43" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
     <hyperlink ref="A43" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
-    <hyperlink ref="A103" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88788CCD-3D7B-4A3D-85F8-1ACC42F48D67}"/>
-    <hyperlink ref="A54" r:id="rId46" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A72" r:id="rId47" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId48" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId49" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A80" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{57E689B1-9285-4A92-97DF-A022F00B5C3A}"/>
-    <hyperlink ref="A83" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A105" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{90680F02-1325-4FA5-A1F7-D97F4A469500}"/>
-    <hyperlink ref="A95" r:id="rId54" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A88" r:id="rId55" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A20" r:id="rId56" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A98" r:id="rId58" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId60" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A48" r:id="rId61" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId62" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId63" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId64" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId65" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A104" r:id="rId67" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A102" r:id="rId68" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
-    <hyperlink ref="A58" r:id="rId69" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
-    <hyperlink ref="A124" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
-    <hyperlink ref="A56" r:id="rId71" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
-    <hyperlink ref="A76" r:id="rId72" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
-    <hyperlink ref="A67" r:id="rId73" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
-    <hyperlink ref="A64" r:id="rId74" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
-    <hyperlink ref="A65" r:id="rId75" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
-    <hyperlink ref="A112" r:id="rId76" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
-    <hyperlink ref="A89" r:id="rId77" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
-    <hyperlink ref="A113" r:id="rId78" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
-    <hyperlink ref="A55" r:id="rId79" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
-    <hyperlink ref="A92" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
-    <hyperlink ref="A94" r:id="rId81" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
-    <hyperlink ref="A100" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
-    <hyperlink ref="A78" r:id="rId83" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
-    <hyperlink ref="A68" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
-    <hyperlink ref="A66" r:id="rId85" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
-    <hyperlink ref="A61" r:id="rId86" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{7CC81E97-336C-4BE3-9FAB-830B94A1ED65}"/>
-    <hyperlink ref="A114" r:id="rId87" xr:uid="{4AB8AFAA-AC83-45E2-9518-E2D11E6D96B0}"/>
-    <hyperlink ref="A47" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{26C53F9C-E257-4CAE-A946-AC2781FD39DA}"/>
-    <hyperlink ref="A38" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F20C007B-8F5D-4991-B161-59964EC6A904}"/>
-    <hyperlink ref="A81" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E845835-848D-41BC-990F-0451F6EDC6B6}"/>
-    <hyperlink ref="A69" r:id="rId91" xr:uid="{100C0767-B909-4784-8140-124E31407B35}"/>
-    <hyperlink ref="A62" r:id="rId92" xr:uid="{EBB6B418-7671-46B4-8264-66B320EA6644}"/>
-    <hyperlink ref="A63" r:id="rId93" xr:uid="{4531BD62-CB46-48D7-A458-DCEED66905FA}"/>
-    <hyperlink ref="A106" r:id="rId94" xr:uid="{D187F26A-6548-4108-847B-E7C9C32C11E1}"/>
-    <hyperlink ref="A60" r:id="rId95" xr:uid="{0FA07B7D-6A05-40FA-BD8E-65ED21205D3E}"/>
-    <hyperlink ref="A51" r:id="rId96" xr:uid="{1572CB3F-0825-489E-930B-D185D839CFAB}"/>
-    <hyperlink ref="A96" r:id="rId97" xr:uid="{2C8E7F40-8076-41F1-8377-4886D132DE7E}"/>
+    <hyperlink ref="A54" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
+    <hyperlink ref="A72" r:id="rId46" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId47" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId48" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A83" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A95" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A88" r:id="rId52" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A20" r:id="rId53" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A98" r:id="rId55" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId57" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A48" r:id="rId58" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId59" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId60" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId61" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId62" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A104" r:id="rId64" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A102" r:id="rId65" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId66" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A124" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId68" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId69" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A67" r:id="rId70" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
+    <hyperlink ref="A64" r:id="rId71" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
+    <hyperlink ref="A65" r:id="rId72" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
+    <hyperlink ref="A112" r:id="rId73" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
+    <hyperlink ref="A89" r:id="rId74" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
+    <hyperlink ref="A113" r:id="rId75" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
+    <hyperlink ref="A55" r:id="rId76" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
+    <hyperlink ref="A92" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
+    <hyperlink ref="A94" r:id="rId78" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
+    <hyperlink ref="A100" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
+    <hyperlink ref="A78" r:id="rId80" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
+    <hyperlink ref="A68" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
+    <hyperlink ref="A66" r:id="rId82" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
+    <hyperlink ref="A61" r:id="rId83" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{7CC81E97-336C-4BE3-9FAB-830B94A1ED65}"/>
+    <hyperlink ref="A114" r:id="rId84" xr:uid="{4AB8AFAA-AC83-45E2-9518-E2D11E6D96B0}"/>
+    <hyperlink ref="A47" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{26C53F9C-E257-4CAE-A946-AC2781FD39DA}"/>
+    <hyperlink ref="A38" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F20C007B-8F5D-4991-B161-59964EC6A904}"/>
+    <hyperlink ref="A81" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E845835-848D-41BC-990F-0451F6EDC6B6}"/>
+    <hyperlink ref="A69" r:id="rId88" xr:uid="{100C0767-B909-4784-8140-124E31407B35}"/>
+    <hyperlink ref="A62" r:id="rId89" xr:uid="{EBB6B418-7671-46B4-8264-66B320EA6644}"/>
+    <hyperlink ref="A63" r:id="rId90" xr:uid="{4531BD62-CB46-48D7-A458-DCEED66905FA}"/>
+    <hyperlink ref="A106" r:id="rId91" xr:uid="{D187F26A-6548-4108-847B-E7C9C32C11E1}"/>
+    <hyperlink ref="A60" r:id="rId92" xr:uid="{0FA07B7D-6A05-40FA-BD8E-65ED21205D3E}"/>
+    <hyperlink ref="A51" r:id="rId93" xr:uid="{1572CB3F-0825-489E-930B-D185D839CFAB}"/>
+    <hyperlink ref="A96" r:id="rId94" xr:uid="{2C8E7F40-8076-41F1-8377-4886D132DE7E}"/>
+    <hyperlink ref="A103" r:id="rId95" xr:uid="{8EB233D0-BBB2-4751-B077-47308791807E}"/>
+    <hyperlink ref="A80" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D67D790E-4D8C-4BD3-9449-D7EE995AFD7D}"/>
+    <hyperlink ref="A105" r:id="rId97" xr:uid="{74E6E34E-22EC-41F4-BAC4-E3036D82A01C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EDE9E2-2A23-4783-B983-B15AA2393C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7065BA7-68E9-488A-A3BB-ECAAC03BAE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="726">
   <si>
     <t>Image</t>
   </si>
@@ -1740,15 +1740,6 @@
     <t>1611</t>
   </si>
   <si>
-    <t>1620-1625</t>
-  </si>
-  <si>
-    <t>Plaisance</t>
-  </si>
-  <si>
-    <t>Statue équestre d'Alexandre Farnèse</t>
-  </si>
-  <si>
     <t>Sainte Véronique</t>
   </si>
   <si>
@@ -1776,15 +1767,6 @@
     <t>Encelade</t>
   </si>
   <si>
-    <t>José de</t>
-  </si>
-  <si>
-    <t>1671-1673</t>
-  </si>
-  <si>
-    <t>Vierge des Douleurs</t>
-  </si>
-  <si>
     <t>Venise</t>
   </si>
   <si>
@@ -1887,9 +1869,6 @@
     <t>Cathédrale</t>
   </si>
   <si>
-    <t>David_SM_Maggiore.jpg (850×1540)</t>
-  </si>
-  <si>
     <t>Chapelle Paolina</t>
   </si>
   <si>
@@ -2031,12 +2010,6 @@
     <t>Bernardo de</t>
   </si>
   <si>
-    <t>c,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Char d'Apollon </t>
-  </si>
-  <si>
     <t>Saint François d'Assise</t>
   </si>
   <si>
@@ -2196,9 +2169,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Charles_I%2C_Trafalgar_Square.jpg/960px-Charles_I%2C_Trafalgar_Square.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -2238,13 +2208,10 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Religion_Overthrowing_Heresy_and_Hatred_Legros.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG/960px-Monumento_Alessandro_Farnese_di_Francesco_Mochi.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/47/Dolorosa%2C_Capilla_Real_de_Granada.jpg/960px-Dolorosa%2C_Capilla_Real_de_Granada.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -2812,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V650"/>
+  <dimension ref="A1:V647"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3021,7 +2988,7 @@
         <v>514</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="43" t="s">
@@ -3074,7 +3041,7 @@
         <v>26</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="43" t="s">
@@ -3122,7 +3089,7 @@
         <v>26</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="43" t="s">
@@ -3174,7 +3141,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -3251,7 +3218,7 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>313</v>
@@ -3274,11 +3241,11 @@
         <v>48</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="43" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
@@ -3297,7 +3264,7 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>125</v>
@@ -3741,7 +3708,7 @@
         <v>26</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="43" t="s">
@@ -3821,7 +3788,7 @@
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>162</v>
@@ -3850,11 +3817,11 @@
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="43" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="19" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="O20" s="29" t="s">
         <v>460</v>
@@ -3948,7 +3915,7 @@
         <v>26</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="K22" s="39"/>
       <c r="L22" s="43" t="s">
@@ -4098,10 +4065,10 @@
         <v>26</v>
       </c>
       <c r="J25" s="43" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="L25" s="43" t="s">
         <v>476</v>
@@ -4159,7 +4126,7 @@
       </c>
       <c r="K26" s="39"/>
       <c r="L26" s="43" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
@@ -4210,7 +4177,7 @@
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
@@ -4265,11 +4232,11 @@
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -4320,7 +4287,7 @@
         <v>531</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="K29" s="39"/>
       <c r="L29" s="43" t="s">
@@ -4428,7 +4395,7 @@
         <v>81</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="K31" s="39"/>
       <c r="L31" s="43" t="s">
@@ -4530,10 +4497,10 @@
         <v>496</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="K33" s="39"/>
       <c r="L33" s="43" t="s">
@@ -4638,7 +4605,7 @@
         <v>26</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="K35" s="39"/>
       <c r="L35" s="43" t="s">
@@ -4685,10 +4652,10 @@
         <v>505</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="K36" s="39"/>
       <c r="L36" s="43" t="s">
@@ -4743,11 +4710,11 @@
         <v>26</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="K37" s="39"/>
       <c r="L37" s="43" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="19"/>
@@ -4771,13 +4738,13 @@
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
@@ -4798,7 +4765,7 @@
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="43" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="19"/>
@@ -4870,7 +4837,7 @@
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B40" s="30" t="s">
         <v>307</v>
@@ -4944,7 +4911,7 @@
         <v>548</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="3" t="s">
@@ -5027,13 +4994,13 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>617</v>
+        <v>725</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>326</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
@@ -5050,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="L43" s="43" t="s">
         <v>398</v>
@@ -5238,7 +5205,7 @@
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>43</v>
@@ -5255,14 +5222,14 @@
         <v>46</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
@@ -5281,7 +5248,7 @@
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>43</v>
@@ -5305,7 +5272,7 @@
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
@@ -5379,7 +5346,7 @@
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B50" s="29" t="s">
         <v>43</v>
@@ -5403,10 +5370,10 @@
         <v>53</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="19"/>
@@ -5432,7 +5399,7 @@
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="B51" s="29" t="s">
         <v>43</v>
@@ -5455,7 +5422,7 @@
         <v>48</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="43" t="s">
@@ -5480,7 +5447,7 @@
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B52" s="29" t="s">
         <v>43</v>
@@ -5507,7 +5474,7 @@
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="43" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5533,7 +5500,7 @@
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="B53" s="29" t="s">
         <v>43</v>
@@ -5637,7 +5604,7 @@
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>218</v>
@@ -5657,12 +5624,12 @@
         <v>1600</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
       <c r="L55" s="44" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
@@ -5688,13 +5655,13 @@
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="B56" s="31" t="s">
         <v>145</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
@@ -5713,7 +5680,7 @@
       <c r="J56" s="44"/>
       <c r="K56" s="40"/>
       <c r="L56" s="44" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
@@ -5794,7 +5761,7 @@
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="B58" s="31" t="s">
         <v>332</v>
@@ -5847,7 +5814,7 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="B59" s="31" t="s">
         <v>332</v>
@@ -5870,11 +5837,11 @@
         <v>553</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="44" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
@@ -5883,7 +5850,7 @@
       </c>
       <c r="P59" s="36"/>
       <c r="Q59" s="4" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="R59" s="11"/>
       <c r="S59" s="12"/>
@@ -5896,7 +5863,7 @@
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="B60" s="31" t="s">
         <v>332</v>
@@ -5919,11 +5886,11 @@
         <v>550</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="44" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -5971,7 +5938,7 @@
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
@@ -6050,7 +6017,7 @@
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>294</v>
@@ -6077,7 +6044,7 @@
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="44" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -6152,7 +6119,7 @@
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="B65" s="33" t="s">
         <v>125</v>
@@ -6200,7 +6167,7 @@
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1">
       <c r="A66" s="52" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>125</v>
@@ -6223,11 +6190,11 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="44" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
@@ -6251,13 +6218,13 @@
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -6268,15 +6235,15 @@
         <v>24</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="44" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
@@ -6297,13 +6264,13 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
@@ -6317,14 +6284,14 @@
         <v>538</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="J68" s="50" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="48" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19"/>
@@ -6345,18 +6312,18 @@
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="31" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G69" s="31" t="s">
         <v>298</v>
@@ -6374,7 +6341,7 @@
         <v>406</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
@@ -6395,13 +6362,13 @@
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
@@ -6418,11 +6385,11 @@
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="44" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -6519,7 +6486,7 @@
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
@@ -6539,7 +6506,7 @@
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1">
       <c r="A73" s="49" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>275</v>
@@ -6562,11 +6529,11 @@
         <v>280</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="44" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="11"/>
@@ -6644,7 +6611,7 @@
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1">
       <c r="A75" s="49" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>188</v>
@@ -6697,7 +6664,7 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B76" s="31" t="s">
         <v>188</v>
@@ -6720,7 +6687,7 @@
         <v>546</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="44" t="s">
@@ -6817,7 +6784,7 @@
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="44" t="s">
@@ -6891,7 +6858,7 @@
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="B80" s="31" t="s">
         <v>180</v>
@@ -6914,7 +6881,7 @@
         <v>531</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="44" t="s">
@@ -6939,13 +6906,13 @@
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -6953,22 +6920,22 @@
         <v>286</v>
       </c>
       <c r="G81" s="31" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="I81" s="31" t="s">
         <v>531</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="L81" s="44" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="11"/>
@@ -6976,7 +6943,7 @@
         <v>27</v>
       </c>
       <c r="P81" s="36" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="R81" s="11"/>
       <c r="S81" s="12"/>
@@ -6989,7 +6956,7 @@
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="B82" s="31" t="s">
         <v>197</v>
@@ -7012,11 +6979,11 @@
         <v>81</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="44" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="11"/>
@@ -7136,7 +7103,7 @@
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="B85" s="31" t="s">
         <v>125</v>
@@ -7159,7 +7126,7 @@
         <v>458</v>
       </c>
       <c r="J85" s="44" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="K85" s="40"/>
       <c r="L85" s="44" t="s">
@@ -7257,10 +7224,10 @@
         <v>53</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="L87" s="44" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="11"/>
@@ -7286,7 +7253,7 @@
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>98</v>
@@ -7337,7 +7304,7 @@
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B89" s="31" t="s">
         <v>98</v>
@@ -7360,11 +7327,11 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="44" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
@@ -7481,13 +7448,13 @@
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
@@ -7495,20 +7462,20 @@
         <v>156</v>
       </c>
       <c r="G92" s="31" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="I92" s="31" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="J92" s="51" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="44" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -7552,7 +7519,7 @@
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
@@ -7574,13 +7541,13 @@
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
@@ -7597,11 +7564,11 @@
         <v>81</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="44" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
@@ -7667,7 +7634,7 @@
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="B96" s="31" t="s">
         <v>234</v>
@@ -7764,13 +7731,13 @@
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1">
       <c r="A98" s="49" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="B98" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
@@ -7787,11 +7754,11 @@
         <v>26</v>
       </c>
       <c r="J98" s="44" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="K98" s="40"/>
       <c r="L98" s="44" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="M98" s="11"/>
       <c r="N98" s="11"/>
@@ -7858,182 +7825,186 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1">
-      <c r="A100" s="46" t="s">
-        <v>720</v>
-      </c>
-      <c r="B100" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G100" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="H100" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="I100" s="31"/>
+      <c r="A100" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="G100" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="H100" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="I100" s="32"/>
       <c r="J100" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="K100" s="40"/>
-      <c r="L100" s="44" t="s">
-        <v>666</v>
-      </c>
-      <c r="M100" s="11"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="P100" s="36">
-        <v>300</v>
-      </c>
-      <c r="R100" s="11"/>
-      <c r="S100" s="12"/>
-      <c r="T100" s="4">
-        <v>1</v>
-      </c>
-      <c r="U100" s="5">
-        <v>130</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="K100" s="20"/>
+      <c r="L100" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="M100" s="22"/>
+      <c r="N100" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="O100" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P100" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="20"/>
+      <c r="S100" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="T100" s="2">
+        <v>3</v>
+      </c>
+      <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1">
-      <c r="A101" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="B101" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="C101" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="G101" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="H101" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="I101" s="32"/>
-      <c r="J101" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="K101" s="20"/>
-      <c r="L101" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="M101" s="22"/>
-      <c r="N101" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="O101" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="P101" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" s="20"/>
-      <c r="S101" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T101" s="2">
+      <c r="A101" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="B101" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C101" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G101" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="I101" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+      <c r="L101" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="M101" s="21"/>
+      <c r="N101" s="21"/>
+      <c r="O101" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P101" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="R101" s="21"/>
+      <c r="S101" s="26"/>
+      <c r="T101" s="4">
         <v>3</v>
       </c>
-      <c r="U101" s="14"/>
+      <c r="U101" s="5">
+        <v>107</v>
+      </c>
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1">
-      <c r="A102" s="17" t="s">
-        <v>703</v>
-      </c>
-      <c r="B102" s="33" t="s">
+      <c r="A102" s="46" t="s">
+        <v>693</v>
+      </c>
+      <c r="B102" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C102" s="38" t="s">
+      <c r="C102" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="33" t="s">
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="G102" s="33" t="s">
+      <c r="G102" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="H102" s="33" t="s">
-        <v>426</v>
-      </c>
-      <c r="I102" s="33" t="s">
-        <v>427</v>
-      </c>
-      <c r="J102" s="23"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="M102" s="21"/>
-      <c r="N102" s="21"/>
-      <c r="O102" s="38" t="s">
+      <c r="H102" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="I102" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="K102" s="40"/>
+      <c r="L102" s="44" t="s">
+        <v>568</v>
+      </c>
+      <c r="M102" s="11"/>
+      <c r="N102" s="11"/>
+      <c r="O102" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P102" s="21" t="s">
-        <v>429</v>
-      </c>
-      <c r="R102" s="21"/>
-      <c r="S102" s="26"/>
+      <c r="P102" s="36">
+        <v>500</v>
+      </c>
+      <c r="R102" s="11"/>
+      <c r="S102" s="12"/>
       <c r="T102" s="4">
         <v>3</v>
       </c>
       <c r="U102" s="5">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>121</v>
+        <v>657</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>122</v>
+        <v>677</v>
       </c>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
       <c r="F103" s="31" t="s">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="G103" s="31" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="H103" s="31" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="I103" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="J103" s="44"/>
+        <v>548</v>
+      </c>
+      <c r="J103" s="44" t="s">
+        <v>656</v>
+      </c>
       <c r="K103" s="40"/>
       <c r="L103" s="44" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="M103" s="11"/>
       <c r="N103" s="11"/>
       <c r="O103" s="31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P103" s="36">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="R103" s="11"/>
       <c r="S103" s="12"/>
@@ -8041,590 +8012,587 @@
         <v>3</v>
       </c>
       <c r="U103" s="5">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1">
-      <c r="A104" s="46" t="s">
-        <v>702</v>
-      </c>
-      <c r="B104" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C104" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G104" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H104" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="I104" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="J104" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="K104" s="40"/>
-      <c r="L104" s="44" t="s">
-        <v>571</v>
-      </c>
-      <c r="M104" s="11"/>
-      <c r="N104" s="11"/>
-      <c r="O104" s="31" t="s">
+      <c r="A104" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B104" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C104" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D104" s="20"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G104" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H104" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I104" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="J104" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="K104" s="20"/>
+      <c r="L104" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="M104" s="22"/>
+      <c r="N104" s="22"/>
+      <c r="O104" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="P104" s="20"/>
+      <c r="Q104" s="2"/>
+      <c r="R104" s="20"/>
+      <c r="S104" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="T104" s="2">
+        <v>3</v>
+      </c>
+      <c r="U104" s="14"/>
+    </row>
+    <row r="105" spans="1:21" ht="15" customHeight="1">
+      <c r="A105" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="G105" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="H105" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="I105" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="J105" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="K105" s="20"/>
+      <c r="L105" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="M105" s="22"/>
+      <c r="N105" s="22"/>
+      <c r="O105" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="P104" s="36">
-        <v>500</v>
-      </c>
-      <c r="R104" s="11"/>
-      <c r="S104" s="12"/>
-      <c r="T104" s="4">
+      <c r="P105" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" s="20"/>
+      <c r="S105" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="T105" s="2">
         <v>3</v>
       </c>
-      <c r="U104" s="5">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" ht="15" customHeight="1">
-      <c r="A105" s="46" t="s">
-        <v>736</v>
-      </c>
-      <c r="B105" s="31" t="s">
-        <v>580</v>
-      </c>
-      <c r="C105" s="47" t="s">
-        <v>686</v>
-      </c>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="G105" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="H105" s="31" t="s">
-        <v>581</v>
-      </c>
-      <c r="I105" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="J105" s="44" t="s">
-        <v>663</v>
-      </c>
-      <c r="K105" s="40"/>
-      <c r="L105" s="44" t="s">
-        <v>582</v>
-      </c>
-      <c r="M105" s="11"/>
-      <c r="N105" s="11"/>
-      <c r="O105" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="P105" s="36" t="s">
-        <v>665</v>
-      </c>
-      <c r="R105" s="11"/>
-      <c r="S105" s="12"/>
-      <c r="T105" s="4">
+      <c r="U105" s="14"/>
+    </row>
+    <row r="106" spans="1:21" ht="15" customHeight="1">
+      <c r="A106" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C106" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="G106" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="H106" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I106" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="J106" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="K106" s="20"/>
+      <c r="L106" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="M106" s="22"/>
+      <c r="N106" s="22"/>
+      <c r="O106" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="P106" s="20"/>
+      <c r="Q106" s="2"/>
+      <c r="R106" s="20"/>
+      <c r="S106" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="T106" s="2">
         <v>3</v>
       </c>
-      <c r="U105" s="5">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" ht="15" customHeight="1">
-      <c r="A106" s="46" t="s">
-        <v>730</v>
-      </c>
-      <c r="B106" s="31" t="s">
-        <v>664</v>
-      </c>
-      <c r="C106" s="47" t="s">
-        <v>686</v>
-      </c>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="G106" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="H106" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="I106" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="J106" s="44" t="s">
-        <v>663</v>
-      </c>
-      <c r="K106" s="40"/>
-      <c r="L106" s="44" t="s">
-        <v>551</v>
-      </c>
-      <c r="M106" s="11"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="P106" s="36">
-        <v>50</v>
-      </c>
-      <c r="R106" s="11"/>
-      <c r="S106" s="12"/>
-      <c r="T106" s="4">
-        <v>3</v>
-      </c>
-      <c r="U106" s="5">
-        <v>152</v>
-      </c>
+      <c r="U106" s="14"/>
     </row>
     <row r="107" spans="1:21" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B107" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="C107" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="D107" s="20"/>
-      <c r="E107" s="20"/>
-      <c r="F107" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="G107" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C107" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="H107" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="I107" s="32" t="s">
-        <v>74</v>
+      <c r="G107" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H107" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="I107" s="33" t="s">
+        <v>410</v>
       </c>
       <c r="J107" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="K107" s="20"/>
-      <c r="L107" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="M107" s="22"/>
-      <c r="N107" s="22"/>
-      <c r="O107" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="P107" s="20"/>
-      <c r="Q107" s="2"/>
-      <c r="R107" s="20"/>
-      <c r="S107" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="T107" s="2">
-        <v>3</v>
-      </c>
-      <c r="U107" s="14"/>
+        <v>49</v>
+      </c>
+      <c r="K107" s="23"/>
+      <c r="L107" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21"/>
+      <c r="O107" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P107" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q107" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="R107" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="S107" s="26"/>
+      <c r="T107" s="4">
+        <v>1</v>
+      </c>
+      <c r="U107" s="5">
+        <v>40</v>
+      </c>
     </row>
     <row r="108" spans="1:21" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B108" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C108" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G108" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="H108" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="I108" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="J108" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K108" s="23"/>
+      <c r="L108" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="M108" s="21"/>
+      <c r="N108" s="21"/>
+      <c r="O108" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="P108" s="21">
+        <v>320</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>106</v>
+      </c>
+      <c r="R108" s="21">
         <v>114</v>
       </c>
-      <c r="B108" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C108" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D108" s="20"/>
-      <c r="E108" s="20"/>
-      <c r="F108" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="G108" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="H108" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="I108" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="J108" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="K108" s="20"/>
-      <c r="L108" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="M108" s="22"/>
-      <c r="N108" s="22"/>
-      <c r="O108" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P108" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" s="20"/>
-      <c r="S108" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="T108" s="2">
-        <v>3</v>
-      </c>
-      <c r="U108" s="14"/>
+      <c r="S108" s="26"/>
+      <c r="T108" s="4">
+        <v>1</v>
+      </c>
+      <c r="U108" s="5">
+        <v>41</v>
+      </c>
     </row>
     <row r="109" spans="1:21" ht="15" customHeight="1">
-      <c r="A109" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B109" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C109" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="D109" s="20"/>
-      <c r="E109" s="20"/>
-      <c r="F109" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="G109" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="H109" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="I109" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="J109" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="K109" s="20"/>
-      <c r="L109" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="M109" s="22"/>
-      <c r="N109" s="22"/>
-      <c r="O109" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="P109" s="20"/>
-      <c r="Q109" s="2"/>
-      <c r="R109" s="20"/>
-      <c r="S109" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T109" s="2">
-        <v>3</v>
-      </c>
-      <c r="U109" s="14"/>
+      <c r="A109" s="46" t="s">
+        <v>704</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="C109" s="47" t="s">
+        <v>355</v>
+      </c>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="H109" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="I109" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="J109" s="44" t="s">
+        <v>650</v>
+      </c>
+      <c r="K109" s="40"/>
+      <c r="L109" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="M109" s="11"/>
+      <c r="N109" s="11"/>
+      <c r="O109" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="P109" s="36"/>
+      <c r="R109" s="11"/>
+      <c r="S109" s="12"/>
+      <c r="T109" s="4">
+        <v>1</v>
+      </c>
+      <c r="U109" s="5">
+        <v>42</v>
+      </c>
     </row>
     <row r="110" spans="1:21" ht="15" customHeight="1">
-      <c r="A110" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="B110" s="33" t="s">
+      <c r="A110" s="46" t="s">
+        <v>706</v>
+      </c>
+      <c r="B110" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="C110" s="38" t="s">
+      <c r="C110" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21"/>
-      <c r="F110" s="33" t="s">
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="G110" s="33" t="s">
+      <c r="G110" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="H110" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="I110" s="33" t="s">
-        <v>410</v>
+      <c r="H110" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="I110" s="31" t="s">
+        <v>48</v>
       </c>
       <c r="J110" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="K110" s="23"/>
-      <c r="L110" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="M110" s="21"/>
-      <c r="N110" s="21"/>
-      <c r="O110" s="38" t="s">
+      <c r="K110" s="40"/>
+      <c r="L110" t="s">
+        <v>707</v>
+      </c>
+      <c r="M110" s="11"/>
+      <c r="N110" s="11"/>
+      <c r="O110" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P110" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q110" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="R110" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="S110" s="26"/>
+      <c r="P110" s="36">
+        <v>332</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>296</v>
+      </c>
+      <c r="R110" s="11">
+        <v>44</v>
+      </c>
+      <c r="S110" s="12"/>
       <c r="T110" s="4">
         <v>1</v>
       </c>
       <c r="U110" s="5">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:21" ht="15" customHeight="1">
-      <c r="A111" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="B111" s="33" t="s">
+      <c r="A111" s="46" t="s">
+        <v>714</v>
+      </c>
+      <c r="B111" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="C111" s="38" t="s">
+      <c r="C111" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="33" t="s">
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="G111" s="33" t="s">
+      <c r="G111" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="H111" s="33" t="s">
-        <v>415</v>
-      </c>
-      <c r="I111" s="33" t="s">
-        <v>416</v>
-      </c>
-      <c r="J111" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="K111" s="23"/>
-      <c r="L111" s="23" t="s">
-        <v>417</v>
-      </c>
-      <c r="M111" s="21"/>
-      <c r="N111" s="21"/>
-      <c r="O111" s="38" t="s">
+      <c r="H111" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="I111" s="31" t="s">
+        <v>652</v>
+      </c>
+      <c r="J111" s="44" t="s">
+        <v>653</v>
+      </c>
+      <c r="K111" s="40"/>
+      <c r="L111" s="44" t="s">
+        <v>713</v>
+      </c>
+      <c r="M111" s="11"/>
+      <c r="N111" s="11"/>
+      <c r="O111" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P111" s="21">
-        <v>320</v>
-      </c>
-      <c r="Q111" s="4">
-        <v>106</v>
-      </c>
-      <c r="R111" s="21">
-        <v>114</v>
-      </c>
-      <c r="S111" s="26"/>
+      <c r="P111" s="36">
+        <v>66</v>
+      </c>
+      <c r="R111" s="11"/>
+      <c r="S111" s="12"/>
       <c r="T111" s="4">
         <v>1</v>
       </c>
       <c r="U111" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="15" customHeight="1">
+      <c r="A112" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C112" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G112" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="H112" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="I112" s="32"/>
+      <c r="J112" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K112" s="20"/>
+      <c r="L112" s="22" t="s">
+        <v>689</v>
+      </c>
+      <c r="M112" s="22"/>
+      <c r="N112" s="22"/>
+      <c r="O112" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P112" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="20"/>
+      <c r="S112" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="T112" s="2">
+        <v>3</v>
+      </c>
+      <c r="U112" s="14"/>
+    </row>
+    <row r="113" spans="1:21" ht="15" customHeight="1">
+      <c r="A113" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B113" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G113" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H113" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="I113" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J113" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="K113" s="20"/>
+      <c r="L113" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M113" s="22"/>
+      <c r="N113" s="22"/>
+      <c r="O113" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P113" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" s="20"/>
+      <c r="S113" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="T113" s="2">
+        <v>3</v>
+      </c>
+      <c r="U113" s="14"/>
+    </row>
+    <row r="114" spans="1:21" ht="15" customHeight="1">
+      <c r="A114" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="C114" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="D114" s="20"/>
+      <c r="E114" s="20"/>
+      <c r="F114" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="G114" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H114" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="I114" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="J114" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="K114" s="20"/>
+      <c r="L114" s="22" t="s">
+        <v>688</v>
+      </c>
+      <c r="M114" s="22"/>
+      <c r="N114" s="22"/>
+      <c r="O114" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P114" s="20"/>
+      <c r="Q114" s="2"/>
+      <c r="R114" s="20"/>
+      <c r="S114" s="25" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" ht="15" customHeight="1">
-      <c r="A112" s="46" t="s">
-        <v>713</v>
-      </c>
-      <c r="B112" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="C112" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="G112" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="H112" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="I112" s="31" t="s">
-        <v>410</v>
-      </c>
-      <c r="J112" s="44" t="s">
-        <v>657</v>
-      </c>
-      <c r="K112" s="40"/>
-      <c r="L112" s="44" t="s">
-        <v>658</v>
-      </c>
-      <c r="M112" s="11"/>
-      <c r="N112" s="11"/>
-      <c r="O112" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="P112" s="36"/>
-      <c r="R112" s="11"/>
-      <c r="S112" s="12"/>
-      <c r="T112" s="4">
-        <v>1</v>
-      </c>
-      <c r="U112" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" ht="15" customHeight="1">
-      <c r="A113" s="46" t="s">
-        <v>715</v>
-      </c>
-      <c r="B113" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="C113" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="G113" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="H113" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="I113" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="J113" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="K113" s="40"/>
-      <c r="L113" t="s">
-        <v>716</v>
-      </c>
-      <c r="M113" s="11"/>
-      <c r="N113" s="11"/>
-      <c r="O113" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P113" s="36">
-        <v>332</v>
-      </c>
-      <c r="Q113" s="4">
-        <v>296</v>
-      </c>
-      <c r="R113" s="11">
-        <v>44</v>
-      </c>
-      <c r="S113" s="12"/>
-      <c r="T113" s="4">
-        <v>1</v>
-      </c>
-      <c r="U113" s="5">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" ht="15" customHeight="1">
-      <c r="A114" s="46" t="s">
-        <v>724</v>
-      </c>
-      <c r="B114" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="C114" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="G114" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="H114" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="I114" s="31" t="s">
-        <v>659</v>
-      </c>
-      <c r="J114" s="44" t="s">
-        <v>660</v>
-      </c>
-      <c r="K114" s="40"/>
-      <c r="L114" s="44" t="s">
-        <v>723</v>
-      </c>
-      <c r="M114" s="11"/>
-      <c r="N114" s="11"/>
-      <c r="O114" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P114" s="36">
-        <v>66</v>
-      </c>
-      <c r="R114" s="11"/>
-      <c r="S114" s="12"/>
-      <c r="T114" s="4">
-        <v>1</v>
-      </c>
-      <c r="U114" s="5">
-        <v>44</v>
-      </c>
+      <c r="T114" s="2">
+        <v>3</v>
+      </c>
+      <c r="U114" s="14"/>
     </row>
     <row r="115" spans="1:21" ht="15" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>64</v>
+        <v>382</v>
       </c>
       <c r="B115" s="32" t="s">
-        <v>65</v>
+        <v>383</v>
       </c>
       <c r="C115" s="32" t="s">
-        <v>66</v>
+        <v>384</v>
       </c>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
       <c r="F115" s="32" t="s">
-        <v>67</v>
+        <v>385</v>
       </c>
       <c r="G115" s="32" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="H115" s="32" t="s">
-        <v>69</v>
+        <v>386</v>
       </c>
       <c r="I115" s="32"/>
       <c r="J115" s="23" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="22" t="s">
-        <v>698</v>
+        <v>387</v>
       </c>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
       <c r="O115" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P115" s="20" t="s">
-        <v>71</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="P115" s="20"/>
       <c r="Q115" s="2"/>
       <c r="R115" s="20"/>
       <c r="S115" s="25" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="T115" s="2">
         <v>3</v>
@@ -8633,638 +8601,561 @@
     </row>
     <row r="116" spans="1:21" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>55</v>
+        <v>210</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
       <c r="F116" s="32" t="s">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="G116" s="32" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="H116" s="32" t="s">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="I116" s="32" t="s">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="J116" s="23" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
       <c r="O116" s="32" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="P116" s="20" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" s="20"/>
       <c r="S116" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="T116" s="2">
+        <v>41</v>
+      </c>
+      <c r="T116" s="4">
         <v>3</v>
       </c>
       <c r="U116" s="14"/>
     </row>
     <row r="117" spans="1:21" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B117" s="32" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C117" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
+        <v>284</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>285</v>
+      </c>
       <c r="F117" s="32" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="G117" s="32" t="s">
-        <v>59</v>
+        <v>287</v>
       </c>
       <c r="H117" s="32" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="I117" s="32" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="K117" s="20"/>
       <c r="L117" s="22" t="s">
-        <v>697</v>
+        <v>291</v>
       </c>
       <c r="M117" s="22"/>
       <c r="N117" s="22"/>
       <c r="O117" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P117" s="20"/>
+        <v>36</v>
+      </c>
+      <c r="P117" s="20" t="s">
+        <v>292</v>
+      </c>
       <c r="Q117" s="2"/>
       <c r="R117" s="20"/>
       <c r="S117" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T117" s="2">
+        <v>38</v>
+      </c>
+      <c r="T117" s="4">
         <v>3</v>
       </c>
       <c r="U117" s="14"/>
     </row>
     <row r="118" spans="1:21" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
       <c r="F118" s="32" t="s">
-        <v>385</v>
+        <v>58</v>
       </c>
       <c r="G118" s="32" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="I118" s="32"/>
+        <v>339</v>
+      </c>
+      <c r="I118" s="32" t="s">
+        <v>340</v>
+      </c>
       <c r="J118" s="23" t="s">
-        <v>53</v>
+        <v>341</v>
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
       <c r="O118" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="P118" s="20"/>
+        <v>36</v>
+      </c>
+      <c r="P118" s="20" t="s">
+        <v>196</v>
+      </c>
       <c r="Q118" s="2"/>
       <c r="R118" s="20"/>
       <c r="S118" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T118" s="2">
+        <v>38</v>
+      </c>
+      <c r="T118" s="4">
         <v>3</v>
       </c>
       <c r="U118" s="14"/>
     </row>
     <row r="119" spans="1:21" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="32" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="G119" s="32" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="I119" s="32" t="s">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="J119" s="23" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="22" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="P119" s="20" t="s">
-        <v>71</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="P119" s="20"/>
       <c r="Q119" s="2"/>
       <c r="R119" s="20"/>
       <c r="S119" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T119" s="4">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="T119" s="2">
+        <v>2</v>
       </c>
       <c r="U119" s="14"/>
     </row>
     <row r="120" spans="1:21" ht="15" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>282</v>
+        <v>389</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>283</v>
+        <v>390</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="D120" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E120" s="20" t="s">
-        <v>285</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="D120" s="20"/>
+      <c r="E120" s="20"/>
       <c r="F120" s="32" t="s">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="H120" s="32" t="s">
-        <v>288</v>
+        <v>392</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>289</v>
+        <v>393</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>290</v>
+        <v>394</v>
       </c>
       <c r="K120" s="20"/>
       <c r="L120" s="22" t="s">
-        <v>291</v>
+        <v>621</v>
       </c>
       <c r="M120" s="22"/>
       <c r="N120" s="22"/>
       <c r="O120" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="P120" s="20" t="s">
-        <v>292</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="P120" s="20"/>
       <c r="Q120" s="2"/>
       <c r="R120" s="20"/>
       <c r="S120" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T120" s="4">
+        <v>28</v>
+      </c>
+      <c r="T120" s="2">
         <v>3</v>
       </c>
-      <c r="U120" s="14"/>
+      <c r="U120" s="5">
+        <v>162</v>
+      </c>
     </row>
     <row r="121" spans="1:21" ht="15" customHeight="1">
-      <c r="A121" s="15" t="s">
-        <v>337</v>
+      <c r="A121" s="17" t="s">
+        <v>696</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="C121" s="32" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="D121" s="20"/>
       <c r="E121" s="20"/>
       <c r="F121" s="32" t="s">
-        <v>58</v>
+        <v>319</v>
       </c>
       <c r="G121" s="32" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="H121" s="32" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="J121" s="23" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="K121" s="20"/>
       <c r="L121" s="22" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="M121" s="22"/>
       <c r="N121" s="22"/>
       <c r="O121" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="P121" s="20" t="s">
-        <v>196</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="P121" s="20"/>
       <c r="Q121" s="2"/>
       <c r="R121" s="20"/>
       <c r="S121" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T121" s="4">
+        <v>201</v>
+      </c>
+      <c r="T121" s="2">
         <v>3</v>
       </c>
       <c r="U121" s="14"/>
     </row>
     <row r="122" spans="1:21" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="C122" s="32" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
       <c r="F122" s="32" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G122" s="32" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="I122" s="32" t="s">
-        <v>48</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="I122" s="32"/>
       <c r="J122" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="K122" s="20"/>
+        <v>53</v>
+      </c>
+      <c r="K122" s="20" t="s">
+        <v>449</v>
+      </c>
       <c r="L122" s="22" t="s">
-        <v>233</v>
+        <v>450</v>
       </c>
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
       <c r="O122" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="P122" s="20"/>
-      <c r="Q122" s="2"/>
-      <c r="R122" s="20"/>
+        <v>50</v>
+      </c>
+      <c r="P122" s="20">
+        <v>240</v>
+      </c>
+      <c r="Q122" s="2">
+        <v>1350</v>
+      </c>
+      <c r="R122" s="20">
+        <v>1370</v>
+      </c>
       <c r="S122" s="25" t="s">
         <v>51</v>
       </c>
       <c r="T122" s="2">
-        <v>2</v>
-      </c>
-      <c r="U122" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="U122" s="5">
+        <v>129</v>
+      </c>
     </row>
     <row r="123" spans="1:21" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
       <c r="F123" s="32" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G123" s="32" t="s">
-        <v>73</v>
+        <v>367</v>
       </c>
       <c r="H123" s="32" t="s">
-        <v>392</v>
+        <v>147</v>
       </c>
       <c r="I123" s="32" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="J123" s="23" t="s">
-        <v>394</v>
+        <v>223</v>
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>628</v>
+        <v>369</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="32" t="s">
-        <v>395</v>
+        <v>27</v>
       </c>
       <c r="P123" s="20"/>
       <c r="Q123" s="2"/>
       <c r="R123" s="20"/>
       <c r="S123" s="25" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="T123" s="2">
         <v>3</v>
       </c>
       <c r="U123" s="5">
-        <v>162</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:21" ht="15" customHeight="1">
-      <c r="A124" s="17" t="s">
-        <v>705</v>
+      <c r="A124" s="15" t="s">
+        <v>235</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="D124" s="20"/>
       <c r="E124" s="20"/>
       <c r="F124" s="32" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
       <c r="H124" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="I124" s="32" t="s">
-        <v>322</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="I124" s="32"/>
       <c r="J124" s="23" t="s">
-        <v>323</v>
+        <v>53</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="22" t="s">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="32" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="P124" s="20"/>
       <c r="Q124" s="2"/>
       <c r="R124" s="20"/>
       <c r="S124" s="25" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="T124" s="2">
         <v>3</v>
       </c>
-      <c r="U124" s="14"/>
+      <c r="U124" s="5">
+        <v>136</v>
+      </c>
     </row>
     <row r="125" spans="1:21" ht="15" customHeight="1">
       <c r="A125" s="15" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C125" s="32" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D125" s="20"/>
       <c r="E125" s="20"/>
       <c r="F125" s="32" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="G125" s="32" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="H125" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="I125" s="32"/>
+        <v>271</v>
+      </c>
+      <c r="I125" s="31" t="s">
+        <v>575</v>
+      </c>
       <c r="J125" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="K125" s="20" t="s">
-        <v>449</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="K125" s="20"/>
       <c r="L125" s="22" t="s">
-        <v>450</v>
+        <v>272</v>
       </c>
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
       <c r="O125" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="P125" s="20">
-        <v>240</v>
-      </c>
-      <c r="Q125" s="2">
-        <v>1350</v>
-      </c>
-      <c r="R125" s="20">
-        <v>1370</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="P125" s="20"/>
+      <c r="Q125" s="2"/>
+      <c r="R125" s="20"/>
       <c r="S125" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T125" s="2">
+        <v>41</v>
+      </c>
+      <c r="T125" s="4">
         <v>3</v>
       </c>
       <c r="U125" s="5">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:21" ht="15" customHeight="1">
-      <c r="A126" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="B126" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="C126" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G126" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="H126" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="I126" s="32" t="s">
-        <v>368</v>
-      </c>
-      <c r="J126" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="K126" s="20"/>
-      <c r="L126" s="22" t="s">
-        <v>369</v>
-      </c>
-      <c r="M126" s="22"/>
-      <c r="N126" s="22"/>
-      <c r="O126" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="P126" s="20"/>
-      <c r="Q126" s="2"/>
-      <c r="R126" s="20"/>
-      <c r="S126" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="T126" s="2">
-        <v>3</v>
-      </c>
-      <c r="U126" s="5">
-        <v>181</v>
-      </c>
+      <c r="A126" s="15"/>
+      <c r="B126" s="33"/>
+      <c r="C126" s="38"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="33"/>
+      <c r="G126" s="33"/>
+      <c r="H126" s="33"/>
+      <c r="I126" s="33"/>
+      <c r="J126" s="23"/>
+      <c r="K126" s="24"/>
+      <c r="L126" s="23"/>
+      <c r="M126" s="15"/>
+      <c r="N126" s="15"/>
+      <c r="O126" s="38"/>
+      <c r="P126" s="21"/>
+      <c r="R126" s="21"/>
+      <c r="S126" s="26"/>
+      <c r="U126" s="14"/>
     </row>
     <row r="127" spans="1:21" ht="15" customHeight="1">
-      <c r="A127" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B127" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="C127" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="G127" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="H127" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="I127" s="32"/>
-      <c r="J127" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="K127" s="20"/>
-      <c r="L127" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="M127" s="22"/>
-      <c r="N127" s="22"/>
-      <c r="O127" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="P127" s="20"/>
-      <c r="Q127" s="2"/>
-      <c r="R127" s="20"/>
-      <c r="S127" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="T127" s="2">
-        <v>3</v>
-      </c>
-      <c r="U127" s="5">
-        <v>136</v>
-      </c>
+      <c r="A127" s="15"/>
+      <c r="B127" s="33"/>
+      <c r="C127" s="38"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="33"/>
+      <c r="G127" s="33"/>
+      <c r="H127" s="33"/>
+      <c r="I127" s="33"/>
+      <c r="J127" s="23"/>
+      <c r="K127" s="24"/>
+      <c r="L127" s="23"/>
+      <c r="M127" s="15"/>
+      <c r="N127" s="15"/>
+      <c r="O127" s="38"/>
+      <c r="P127" s="21"/>
+      <c r="R127" s="21"/>
+      <c r="S127" s="26"/>
+      <c r="U127" s="14"/>
     </row>
     <row r="128" spans="1:21" ht="15" customHeight="1">
-      <c r="A128" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B128" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="C128" s="32" t="s">
-        <v>268</v>
-      </c>
+      <c r="A128" s="15"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="38"/>
       <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="G128" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="H128" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="I128" s="31" t="s">
-        <v>578</v>
-      </c>
-      <c r="J128" s="23" t="s">
-        <v>627</v>
-      </c>
-      <c r="K128" s="20"/>
-      <c r="L128" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="M128" s="22"/>
-      <c r="N128" s="22"/>
-      <c r="O128" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="P128" s="20"/>
-      <c r="Q128" s="2"/>
-      <c r="R128" s="20"/>
-      <c r="S128" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T128" s="4">
-        <v>3</v>
-      </c>
-      <c r="U128" s="5">
-        <v>121</v>
-      </c>
+      <c r="E128" s="21"/>
+      <c r="F128" s="33"/>
+      <c r="G128" s="33"/>
+      <c r="H128" s="33"/>
+      <c r="I128" s="33"/>
+      <c r="J128" s="23"/>
+      <c r="K128" s="23"/>
+      <c r="L128" s="23"/>
+      <c r="M128" s="21"/>
+      <c r="N128" s="21"/>
+      <c r="O128" s="38"/>
+      <c r="P128" s="21"/>
+      <c r="R128" s="21"/>
+      <c r="S128" s="25"/>
+      <c r="T128" s="2"/>
+      <c r="U128" s="14"/>
     </row>
     <row r="129" spans="1:21" ht="15" customHeight="1">
       <c r="A129" s="15"/>
@@ -9312,22 +9203,21 @@
       <c r="A131" s="15"/>
       <c r="B131" s="33"/>
       <c r="C131" s="38"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="21"/>
+      <c r="D131" s="15"/>
+      <c r="E131" s="15"/>
       <c r="F131" s="33"/>
       <c r="G131" s="33"/>
       <c r="H131" s="33"/>
       <c r="I131" s="33"/>
       <c r="J131" s="23"/>
-      <c r="K131" s="23"/>
+      <c r="K131" s="24"/>
       <c r="L131" s="23"/>
-      <c r="M131" s="21"/>
-      <c r="N131" s="21"/>
+      <c r="M131" s="15"/>
+      <c r="N131" s="15"/>
       <c r="O131" s="38"/>
       <c r="P131" s="21"/>
       <c r="R131" s="21"/>
-      <c r="S131" s="25"/>
-      <c r="T131" s="2"/>
+      <c r="S131" s="26"/>
       <c r="U131" s="14"/>
     </row>
     <row r="132" spans="1:21" ht="15" customHeight="1">
@@ -9352,66 +9242,12 @@
       <c r="U132" s="14"/>
     </row>
     <row r="133" spans="1:21" ht="15" customHeight="1">
-      <c r="A133" s="15"/>
-      <c r="B133" s="33"/>
-      <c r="C133" s="38"/>
-      <c r="D133" s="15"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="33"/>
-      <c r="G133" s="33"/>
-      <c r="H133" s="33"/>
-      <c r="I133" s="33"/>
-      <c r="J133" s="23"/>
-      <c r="K133" s="24"/>
-      <c r="L133" s="23"/>
-      <c r="M133" s="15"/>
-      <c r="N133" s="15"/>
-      <c r="O133" s="38"/>
-      <c r="P133" s="21"/>
-      <c r="R133" s="21"/>
-      <c r="S133" s="26"/>
       <c r="U133" s="14"/>
     </row>
     <row r="134" spans="1:21" ht="15" customHeight="1">
-      <c r="A134" s="15"/>
-      <c r="B134" s="33"/>
-      <c r="C134" s="38"/>
-      <c r="D134" s="15"/>
-      <c r="E134" s="15"/>
-      <c r="F134" s="33"/>
-      <c r="G134" s="33"/>
-      <c r="H134" s="33"/>
-      <c r="I134" s="33"/>
-      <c r="J134" s="23"/>
-      <c r="K134" s="24"/>
-      <c r="L134" s="23"/>
-      <c r="M134" s="15"/>
-      <c r="N134" s="15"/>
-      <c r="O134" s="38"/>
-      <c r="P134" s="21"/>
-      <c r="R134" s="21"/>
-      <c r="S134" s="26"/>
       <c r="U134" s="14"/>
     </row>
     <row r="135" spans="1:21" ht="15" customHeight="1">
-      <c r="A135" s="15"/>
-      <c r="B135" s="33"/>
-      <c r="C135" s="38"/>
-      <c r="D135" s="15"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="33"/>
-      <c r="G135" s="33"/>
-      <c r="H135" s="33"/>
-      <c r="I135" s="33"/>
-      <c r="J135" s="23"/>
-      <c r="K135" s="24"/>
-      <c r="L135" s="23"/>
-      <c r="M135" s="15"/>
-      <c r="N135" s="15"/>
-      <c r="O135" s="38"/>
-      <c r="P135" s="21"/>
-      <c r="R135" s="21"/>
-      <c r="S135" s="26"/>
       <c r="U135" s="14"/>
     </row>
     <row r="136" spans="1:21" ht="15" customHeight="1">
@@ -10950,18 +10786,9 @@
     <row r="647" spans="21:21" ht="15" customHeight="1">
       <c r="U647" s="14"/>
     </row>
-    <row r="648" spans="21:21" ht="15" customHeight="1">
-      <c r="U648" s="14"/>
-    </row>
-    <row r="649" spans="21:21" ht="15" customHeight="1">
-      <c r="U649" s="14"/>
-    </row>
-    <row r="650" spans="21:21" ht="15" customHeight="1">
-      <c r="U650" s="14"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U135">
-    <sortCondition ref="C2:C135"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U132">
+    <sortCondition ref="C2:C132"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
@@ -11008,60 +10835,57 @@
     <hyperlink ref="A9" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{36A963F9-1859-4BB5-AF7B-1749A3316556}"/>
     <hyperlink ref="A10" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{5D5A21F2-A411-44D1-BB9B-2C0C70D5524C}"/>
     <hyperlink ref="A41" r:id="rId43" xr:uid="{84757824-8795-4EBE-A874-F5BC69EB8814}"/>
-    <hyperlink ref="A43" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/5/59/David_SM_Maggiore.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{51CD1CC3-C936-4141-955A-A648504FA975}"/>
-    <hyperlink ref="A54" r:id="rId45" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
-    <hyperlink ref="A72" r:id="rId46" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
-    <hyperlink ref="A73" r:id="rId47" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
-    <hyperlink ref="A75" r:id="rId48" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
-    <hyperlink ref="A74" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
-    <hyperlink ref="A83" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
-    <hyperlink ref="A95" r:id="rId51" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
-    <hyperlink ref="A88" r:id="rId52" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
-    <hyperlink ref="A20" r:id="rId53" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
-    <hyperlink ref="A70" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
-    <hyperlink ref="A98" r:id="rId55" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
-    <hyperlink ref="A82" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
-    <hyperlink ref="A40" r:id="rId57" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
-    <hyperlink ref="A48" r:id="rId58" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
-    <hyperlink ref="A53" r:id="rId59" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
-    <hyperlink ref="A59" r:id="rId60" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
-    <hyperlink ref="A52" r:id="rId61" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
-    <hyperlink ref="A50" r:id="rId62" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
-    <hyperlink ref="A85" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
-    <hyperlink ref="A104" r:id="rId64" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
-    <hyperlink ref="A102" r:id="rId65" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
-    <hyperlink ref="A58" r:id="rId66" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
-    <hyperlink ref="A124" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
-    <hyperlink ref="A56" r:id="rId68" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
-    <hyperlink ref="A76" r:id="rId69" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
-    <hyperlink ref="A67" r:id="rId70" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
-    <hyperlink ref="A64" r:id="rId71" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
-    <hyperlink ref="A65" r:id="rId72" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
-    <hyperlink ref="A112" r:id="rId73" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
-    <hyperlink ref="A89" r:id="rId74" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
-    <hyperlink ref="A113" r:id="rId75" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
-    <hyperlink ref="A55" r:id="rId76" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
-    <hyperlink ref="A92" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
-    <hyperlink ref="A94" r:id="rId78" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
-    <hyperlink ref="A100" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg/1280px-Apollon_et_ses_chevaux%2C_Bassin_du_char_d%27Apollon%2C_Ch%C3%A2teau_de_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C4641D42-22D7-4C83-8C18-F83A1C9DF567}"/>
-    <hyperlink ref="A78" r:id="rId80" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
-    <hyperlink ref="A68" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
-    <hyperlink ref="A66" r:id="rId82" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
-    <hyperlink ref="A61" r:id="rId83" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{7CC81E97-336C-4BE3-9FAB-830B94A1ED65}"/>
-    <hyperlink ref="A114" r:id="rId84" xr:uid="{4AB8AFAA-AC83-45E2-9518-E2D11E6D96B0}"/>
-    <hyperlink ref="A47" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{26C53F9C-E257-4CAE-A946-AC2781FD39DA}"/>
-    <hyperlink ref="A38" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F20C007B-8F5D-4991-B161-59964EC6A904}"/>
-    <hyperlink ref="A81" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E845835-848D-41BC-990F-0451F6EDC6B6}"/>
-    <hyperlink ref="A69" r:id="rId88" xr:uid="{100C0767-B909-4784-8140-124E31407B35}"/>
-    <hyperlink ref="A62" r:id="rId89" xr:uid="{EBB6B418-7671-46B4-8264-66B320EA6644}"/>
-    <hyperlink ref="A63" r:id="rId90" xr:uid="{4531BD62-CB46-48D7-A458-DCEED66905FA}"/>
-    <hyperlink ref="A106" r:id="rId91" xr:uid="{D187F26A-6548-4108-847B-E7C9C32C11E1}"/>
-    <hyperlink ref="A60" r:id="rId92" xr:uid="{0FA07B7D-6A05-40FA-BD8E-65ED21205D3E}"/>
-    <hyperlink ref="A51" r:id="rId93" xr:uid="{1572CB3F-0825-489E-930B-D185D839CFAB}"/>
-    <hyperlink ref="A96" r:id="rId94" xr:uid="{2C8E7F40-8076-41F1-8377-4886D132DE7E}"/>
-    <hyperlink ref="A103" r:id="rId95" xr:uid="{8EB233D0-BBB2-4751-B077-47308791807E}"/>
-    <hyperlink ref="A80" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D67D790E-4D8C-4BD3-9449-D7EE995AFD7D}"/>
-    <hyperlink ref="A105" r:id="rId97" xr:uid="{74E6E34E-22EC-41F4-BAC4-E3036D82A01C}"/>
+    <hyperlink ref="A54" r:id="rId44" display="https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg/960px-Delft_Nieuwe_Kerk_Innen_Grabmal_f%C3%BCr_Willem_van_Oranje_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{41FB2EBC-18B0-4E72-8E17-12026E2B1B61}"/>
+    <hyperlink ref="A72" r:id="rId45" xr:uid="{2377818E-AC7E-412A-BE19-65059C011658}"/>
+    <hyperlink ref="A73" r:id="rId46" xr:uid="{D2EB520A-41B6-4050-9BA7-A2F9E90128BA}"/>
+    <hyperlink ref="A75" r:id="rId47" xr:uid="{D31F16EE-899F-4E6F-A6C0-1DF12552C7AE}"/>
+    <hyperlink ref="A74" r:id="rId48" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{D7099026-06C0-4E8C-A5AD-1DAE9B3A11C0}"/>
+    <hyperlink ref="A83" r:id="rId49" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{67D1B1BB-597D-4023-A8CA-AAF78A01D53A}"/>
+    <hyperlink ref="A95" r:id="rId50" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/00/Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg/1280px-Statue_-_Pandore_-_%281685-1686%29_-_MR_2018_-_Pierre_Legros_-_%281629-1714%29_-_Parterre_de_Latone_-_Versailles_-_P1610943.jpg" xr:uid="{5D8D11BB-6611-4C47-A8DF-783BE7726359}"/>
+    <hyperlink ref="A88" r:id="rId51" xr:uid="{B1599CA8-63DF-4BEC-8F09-D4C45C5D45FE}"/>
+    <hyperlink ref="A20" r:id="rId52" xr:uid="{56598E81-E882-4593-9AB0-74EC7B800DCE}"/>
+    <hyperlink ref="A70" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CCCDEFB6-C808-4E74-A9C5-5BC09C29CE46}"/>
+    <hyperlink ref="A98" r:id="rId54" xr:uid="{C0BDED27-92AA-46E1-9B68-2A486CB8F7D7}"/>
+    <hyperlink ref="A82" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg/1920px-St_Paul%27s_Cathedral_Choir_looking_east%2C_London%2C_UK_-_Diliff.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E073FFDC-29C3-42A1-880A-380D978686D8}"/>
+    <hyperlink ref="A40" r:id="rId56" xr:uid="{130B22D3-5782-4F0D-B7C8-D3BF002E75FD}"/>
+    <hyperlink ref="A48" r:id="rId57" xr:uid="{4C8ED76E-7B25-4E08-9DBD-20F3D8A26B7E}"/>
+    <hyperlink ref="A53" r:id="rId58" xr:uid="{4DBB1DAB-6B3B-4D97-8928-1E16F166947B}"/>
+    <hyperlink ref="A59" r:id="rId59" xr:uid="{D0D77010-664F-4F2D-AD56-25ECDF509320}"/>
+    <hyperlink ref="A52" r:id="rId60" xr:uid="{352FED50-3DF8-4AAF-BCE0-EC8587E6B779}"/>
+    <hyperlink ref="A50" r:id="rId61" xr:uid="{551771DB-AAB5-471C-97F1-82CD209D69CF}"/>
+    <hyperlink ref="A85" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG/960px-Enl%C3%A8vement_de_Proserpine_par_Pluton%2C_Girardon%2C_original_-_DSC_0872.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B6F2CEFB-2709-4120-AF27-D78960901EBA}"/>
+    <hyperlink ref="A102" r:id="rId63" xr:uid="{53862230-EA81-4ADF-84D7-FD0021C6356E}"/>
+    <hyperlink ref="A101" r:id="rId64" xr:uid="{546A282D-0C7C-4FCD-9E42-9077E76DEF2E}"/>
+    <hyperlink ref="A58" r:id="rId65" xr:uid="{33170364-5FA0-4BBD-8BA5-BE2B68C53775}"/>
+    <hyperlink ref="A121" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg/960px-Tomb_of_Sir_Charles_Morrison_the_younger%2C_Watford_St_Mary.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{2D9F1EE9-3CBA-461D-8A38-1BAED25F8D28}"/>
+    <hyperlink ref="A56" r:id="rId67" display="https://upload.wikimedia.org/wikipedia/commons/f/f3/Gaspard_Marsy%2C_Fontaine_de_l%E2%80%99Encelade%2C_Mus%C3%A9e_national_des_ch%C3%A2teaux_de_Versailles_et_de_Trianon%2C_Versailles%2C_France_%281675%E2%80%931676%29_-_20050429.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" xr:uid="{5E0D5918-66F3-4E12-AFA1-16E14BCC8184}"/>
+    <hyperlink ref="A76" r:id="rId68" xr:uid="{3F4281FE-FDB5-4873-9F97-710BAF681054}"/>
+    <hyperlink ref="A67" r:id="rId69" xr:uid="{8E8F765D-C5E2-47AF-BC7E-45F2FDE98214}"/>
+    <hyperlink ref="A64" r:id="rId70" xr:uid="{21FF6A36-A7E1-4888-9CE8-3FD5FD46700C}"/>
+    <hyperlink ref="A65" r:id="rId71" xr:uid="{8AE029F1-554D-4286-9FDA-82330EEC6FB3}"/>
+    <hyperlink ref="A109" r:id="rId72" xr:uid="{A587986D-44C6-4208-A922-ABCF8FB01161}"/>
+    <hyperlink ref="A89" r:id="rId73" xr:uid="{9E40D529-6CC5-4F9D-A4E6-415A94874B05}"/>
+    <hyperlink ref="A110" r:id="rId74" xr:uid="{56DE9D51-6003-41EB-AAB7-2EB81338797F}"/>
+    <hyperlink ref="A55" r:id="rId75" xr:uid="{4E51EF88-0776-4969-A6A0-811BC545C220}"/>
+    <hyperlink ref="A92" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg/1280px-Santa_Maria_della_Salute_%28Venice%29_-_Main_altar_-_Sculptures_by_Giusto_Le_Court.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{76BABBDA-9AAB-4181-8A67-237D9FDBBFA5}"/>
+    <hyperlink ref="A94" r:id="rId77" xr:uid="{168ED901-08FA-45FA-ABC6-3F8A49DF4EA4}"/>
+    <hyperlink ref="A78" r:id="rId78" xr:uid="{490235A8-C24C-4C1F-A9E3-16CEDB63570C}"/>
+    <hyperlink ref="A68" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg/960px-Den_Haag_Grote_Kerk_Sint_Jacob_Innen_Grabmal_Jacob_van_Wassenaer_Obdam_7.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{42AB930F-CB8E-434A-82F4-1FA8B5696992}"/>
+    <hyperlink ref="A66" r:id="rId80" xr:uid="{09B52CE9-3ECC-49E8-9624-7B0722683A08}"/>
+    <hyperlink ref="A61" r:id="rId81" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/8c/Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg/1280px-Jos%C3%A9_de_Mora_-_Virgin_of_Sorrows_-_Museo_Nacional_de_Escultura_Valladolid.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{7CC81E97-336C-4BE3-9FAB-830B94A1ED65}"/>
+    <hyperlink ref="A111" r:id="rId82" xr:uid="{4AB8AFAA-AC83-45E2-9518-E2D11E6D96B0}"/>
+    <hyperlink ref="A47" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg/960px-Vase_de_la_guerre_au_Ch%C3%A2teau_de_Versailles_le_9_d%C3%A9cembre_2014_-_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{26C53F9C-E257-4CAE-A946-AC2781FD39DA}"/>
+    <hyperlink ref="A38" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG/960px-0_Statue_de_Sainte_H%C3%A9l%C3%A8ne_par_Andrea_Bolgi_-_Basilique_St-Pierre_-_Vatican.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F20C007B-8F5D-4991-B161-59964EC6A904}"/>
+    <hyperlink ref="A81" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG/960px-S.m._del_carmine%2C_int.%2C_cappella_corsini%2C_g.b._foggini%2C_apparizione_di_maria_a_s.andrea_corsini%2C_1683-91_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E845835-848D-41BC-990F-0451F6EDC6B6}"/>
+    <hyperlink ref="A69" r:id="rId86" xr:uid="{100C0767-B909-4784-8140-124E31407B35}"/>
+    <hyperlink ref="A62" r:id="rId87" xr:uid="{EBB6B418-7671-46B4-8264-66B320EA6644}"/>
+    <hyperlink ref="A63" r:id="rId88" xr:uid="{4531BD62-CB46-48D7-A458-DCEED66905FA}"/>
+    <hyperlink ref="A103" r:id="rId89" xr:uid="{D187F26A-6548-4108-847B-E7C9C32C11E1}"/>
+    <hyperlink ref="A60" r:id="rId90" xr:uid="{0FA07B7D-6A05-40FA-BD8E-65ED21205D3E}"/>
+    <hyperlink ref="A51" r:id="rId91" xr:uid="{1572CB3F-0825-489E-930B-D185D839CFAB}"/>
+    <hyperlink ref="A96" r:id="rId92" xr:uid="{2C8E7F40-8076-41F1-8377-4886D132DE7E}"/>
+    <hyperlink ref="A80" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG/960px-Giuliano_finelli%2C_ritratto_di_michelangelo_il_giovane%2C_1630.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{47D80A35-1E21-4529-A926-92C226793AE1}"/>
+    <hyperlink ref="A43" r:id="rId94" xr:uid="{8270DF4C-5EE2-4815-A631-2529804B465C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0DDBD4-3999-4B68-A366-F1DD54CCF15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C51FCBE-3B61-475B-86CD-E767E9EF6949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="726">
   <si>
     <t>Image</t>
   </si>
@@ -146,9 +146,6 @@
     <t>Bois polychrome</t>
   </si>
   <si>
-    <t>c.175 cm</t>
-  </si>
-  <si>
     <t>espagnole</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
     <t>"Statue du Danube"</t>
   </si>
   <si>
-    <t>c.350 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mercurius.jpg/1280px-Mercurius.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>Palais royal d'Amsterdam (ancien hôtel de ville)</t>
   </si>
   <si>
-    <t>c.200 cm</t>
-  </si>
-  <si>
     <t>belge</t>
   </si>
   <si>
@@ -449,9 +440,6 @@
     <t>"Sainte Suzanne"</t>
   </si>
   <si>
-    <t>c.220 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg/1280px-Apollon_et_5_nymphes%2C_Bosquet_des_bains_d%27Apollon%2C_Versailles.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -590,9 +578,6 @@
     <t>"Buste de Maria Duglioli Barberini"</t>
   </si>
   <si>
-    <t>c.70 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg/1280px-Cristo_yacente%2C_Gregorio_Fern%C3%A1ndez_%28Valladolid%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -620,9 +605,6 @@
     <t>"Cristo yacente"</t>
   </si>
   <si>
-    <t>c.180 cm</t>
-  </si>
-  <si>
     <t>Grinling</t>
   </si>
   <si>
@@ -827,9 +809,6 @@
     <t>"Cristo de la Clemencia"</t>
   </si>
   <si>
-    <t>c.195 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cd/HochaltarUeberlingen.jpg/960px-HochaltarUeberlingen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -908,9 +887,6 @@
     <t>"Saint Michel Archange terrassant le démon"</t>
   </si>
   <si>
-    <t>c.226 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Monument_fun%C3%A9raire_d%27Antoine_d%27Aubray_%28Louvre%2C_LP_543%29.jpg/1280px-Monument_fun%C3%A9raire_d%27Antoine_d%27Aubray_%28Louvre%2C_LP_543%29.jpg</t>
   </si>
   <si>
@@ -1040,9 +1016,6 @@
     <t>"Marie-Madeleine pénitente"</t>
   </si>
   <si>
-    <t>c.165 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/San_Fernando%2C_Pedro_Rold%C3%A1n.jpg/1280px-San_Fernando%2C_Pedro_Rold%C3%A1n.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1175,9 +1148,6 @@
     <t>"Sainte Cécile"</t>
   </si>
   <si>
-    <t>c.145 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Le_chateau_de_versailles_le_jardin_41.JPG/1280px-Le_chateau_de_versailles_le_jardin_41.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1352,9 +1322,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>c,190</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a1/Mercure_chevauchant_P%C3%A9gase_by_Antoine_Coysevox%2C_Paris_18_May_2022.jpg/1280px-Mercure_chevauchant_P%C3%A9gase_by_Antoine_Coysevox%2C_Paris_18_May_2022.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1376,9 +1343,6 @@
     <t>49;5</t>
   </si>
   <si>
-    <t>c,200</t>
-  </si>
-  <si>
     <t>Bassin d'Apollon</t>
   </si>
   <si>
@@ -1907,9 +1871,6 @@
     <t>Stèles du chœur</t>
   </si>
   <si>
-    <t>88 stèles</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saint François d'Assise </t>
   </si>
   <si>
@@ -1967,9 +1928,6 @@
     <t>L'Apparition de la Vierge à saint Andrea Corsini </t>
   </si>
   <si>
-    <t>c,400</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cathédrale Saint-Paul </t>
   </si>
   <si>
@@ -2235,6 +2193,24 @@
   </si>
   <si>
     <t xml:space="preserve">Haut-Reliefs </t>
+  </si>
+  <si>
+    <t>L'Immaculée Conception</t>
+  </si>
+  <si>
+    <t>Haut-relief</t>
+  </si>
+  <si>
+    <t>Marbre et stuc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haut-relief </t>
+  </si>
+  <si>
+    <t>175 cm</t>
+  </si>
+  <si>
+    <t>Néerladais</t>
   </si>
 </sst>
 </file>
@@ -2870,10 +2846,10 @@
     <col min="20" max="20" width="9.140625" style="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="4" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" style="5" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="1"/>
+    <col min="23" max="23" width="12.85546875" style="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" customHeight="1">
+    <row r="1" spans="1:23" ht="15" customHeight="1">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -2917,7 +2893,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="P1" s="34" t="s">
         <v>14</v>
@@ -2938,8 +2914,11 @@
         <v>19</v>
       </c>
       <c r="V1" s="14"/>
-    </row>
-    <row r="2" spans="1:22" ht="15" customHeight="1">
+      <c r="W1" s="34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>20</v>
       </c>
@@ -2964,36 +2943,42 @@
         <v>26</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="53" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="7"/>
       <c r="O2" s="28" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="P2" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="R2" s="4">
         <v>490</v>
       </c>
+      <c r="T2" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U2" s="4">
         <v>1</v>
       </c>
       <c r="V2" s="5">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" ht="15" customHeight="1">
+      <c r="W2" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15" customHeight="1">
       <c r="A3" s="16" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>21</v>
@@ -3010,39 +2995,44 @@
         <v>24</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K3" s="39"/>
       <c r="L3" s="54" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="39"/>
       <c r="O3" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Q3" s="35"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U3" s="4">
         <v>1</v>
       </c>
       <c r="V3" s="5">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1">
+      <c r="W3" s="41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>21</v>
@@ -3059,22 +3049,22 @@
         <v>24</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="54" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="39"/>
       <c r="O4" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P4" s="29" t="s">
         <v>27</v>
@@ -3085,20 +3075,25 @@
       <c r="R4" s="4">
         <v>240</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="35">
         <v>180</v>
       </c>
-      <c r="T4" s="19"/>
+      <c r="T4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U4" s="4">
         <v>1</v>
       </c>
       <c r="V4" s="5">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="14.25" customHeight="1">
+      <c r="W4" s="41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="14.25" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>21</v>
@@ -3115,41 +3110,46 @@
         <v>24</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="I5" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="54" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="39"/>
       <c r="O5" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P5" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="35">
         <v>78</v>
       </c>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U5" s="4">
         <v>1</v>
       </c>
       <c r="V5" s="5">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" ht="15" customHeight="1">
+      <c r="W5" s="41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>21</v>
@@ -3166,22 +3166,22 @@
         <v>24</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="K6" s="39"/>
       <c r="L6" s="54" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="M6" s="19"/>
       <c r="N6" s="39"/>
       <c r="O6" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P6" s="29" t="s">
         <v>27</v>
@@ -3189,50 +3189,55 @@
       <c r="Q6" s="35">
         <v>280</v>
       </c>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U6" s="4">
         <v>1</v>
       </c>
       <c r="V6" s="5">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" ht="15" customHeight="1">
+      <c r="W6" s="41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="30" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="3" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P7" s="30" t="s">
         <v>27</v>
@@ -3243,48 +3248,51 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U7" s="2">
         <v>2</v>
       </c>
       <c r="V7" s="14"/>
-    </row>
-    <row r="8" spans="1:22" ht="15" customHeight="1">
+      <c r="W7" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="30" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I8" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P8" s="30" t="s">
         <v>27</v>
@@ -3299,7 +3307,7 @@
         <v>63</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U8" s="2">
         <v>2</v>
@@ -3307,91 +3315,99 @@
       <c r="V8" s="5">
         <v>89</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" ht="15" customHeight="1">
+      <c r="W8" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="29" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H9" s="29">
         <v>1650</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="K9" s="39"/>
       <c r="L9" s="54" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="M9" s="19"/>
       <c r="N9" s="39"/>
       <c r="O9" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P9" s="29" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Q9" s="35"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U9" s="4">
         <v>2</v>
       </c>
       <c r="V9" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1">
+      <c r="W9" s="41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
       <c r="F10" s="29" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="I10" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K10" s="39"/>
       <c r="L10" s="54" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="39"/>
       <c r="O10" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P10" s="29" t="s">
         <v>27</v>
@@ -3402,54 +3418,59 @@
       <c r="R10" s="4">
         <v>202</v>
       </c>
-      <c r="S10" s="19">
+      <c r="S10" s="35">
         <v>124</v>
       </c>
-      <c r="T10" s="19"/>
+      <c r="T10" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U10" s="4">
         <v>2</v>
       </c>
       <c r="V10" s="5">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" ht="15" customHeight="1">
+      <c r="W10" s="41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="30" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="3" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="28" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="P11" s="30" t="s">
         <v>27</v>
@@ -3466,50 +3487,53 @@
         <v>1</v>
       </c>
       <c r="V11" s="14"/>
-    </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1">
+      <c r="W11" s="30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" s="28" t="s">
         <v>163</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>167</v>
       </c>
       <c r="I12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="53" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M12" s="4"/>
       <c r="N12" s="7"/>
       <c r="O12" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P12" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>28</v>
@@ -3520,50 +3544,53 @@
       <c r="V12" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" ht="15" customHeight="1">
+      <c r="W12" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15" customHeight="1">
       <c r="A13" s="10" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I13" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="53" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="M13" s="4"/>
       <c r="N13" s="7"/>
       <c r="O13" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P13" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>28</v>
@@ -3574,50 +3601,53 @@
       <c r="V13" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="15" customHeight="1">
+      <c r="W13" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="28" t="s">
         <v>163</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>167</v>
       </c>
       <c r="I14" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="53" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="M14" s="4"/>
       <c r="N14" s="7"/>
       <c r="O14" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P14" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="R14" s="4">
         <v>109</v>
@@ -3631,50 +3661,53 @@
       <c r="V14" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" ht="15" customHeight="1">
+      <c r="W14" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I15" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="53" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="M15" s="4"/>
       <c r="N15" s="7"/>
       <c r="O15" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P15" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="R15" s="4">
         <v>279</v>
@@ -3691,50 +3724,53 @@
       <c r="V15" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" ht="15" customHeight="1">
+      <c r="W15" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="I16" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="53" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M16" s="4"/>
       <c r="N16" s="7"/>
       <c r="O16" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>28</v>
@@ -3745,50 +3781,53 @@
       <c r="V16" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="15" customHeight="1">
+      <c r="W16" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="53" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="M17" s="4"/>
       <c r="N17" s="7"/>
       <c r="O17" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P17" s="37" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>28</v>
@@ -3799,97 +3838,105 @@
       <c r="V17" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="15" customHeight="1">
+      <c r="W17" s="37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E18" s="19"/>
       <c r="F18" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="K18" s="39"/>
       <c r="L18" s="54" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="39"/>
       <c r="O18" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P18" s="29" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Q18" s="35">
         <v>470</v>
       </c>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U18" s="4">
         <v>1</v>
       </c>
       <c r="V18" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" ht="15" customHeight="1">
+      <c r="W18" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I19" s="29" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K19" s="39"/>
       <c r="L19" s="54" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="39"/>
       <c r="O19" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P19" s="29" t="s">
         <v>27</v>
@@ -3900,144 +3947,159 @@
       <c r="R19" s="4">
         <v>99</v>
       </c>
-      <c r="S19" s="19">
+      <c r="S19" s="35">
         <v>46</v>
       </c>
-      <c r="T19" s="19"/>
+      <c r="T19" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U19" s="4">
         <v>1</v>
       </c>
       <c r="V19" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" ht="15" customHeight="1">
+      <c r="W19" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15" customHeight="1">
       <c r="A20" s="45" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E20" s="19"/>
       <c r="F20" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K20" s="39"/>
       <c r="L20" s="54" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="M20" s="19"/>
       <c r="N20" s="39" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P20" s="29" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="Q20" s="35">
         <v>900</v>
       </c>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U20" s="4">
         <v>1</v>
       </c>
       <c r="V20" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" ht="15" customHeight="1">
+      <c r="W20" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E21" s="19"/>
       <c r="F21" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K21" s="39"/>
       <c r="L21" s="54" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="39"/>
       <c r="O21" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P21" s="29" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Q21" s="35">
         <v>700</v>
       </c>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U21" s="4">
         <v>1</v>
       </c>
       <c r="V21" s="5">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" ht="15" customHeight="1">
+      <c r="W21" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H22" s="29" t="s">
         <v>33</v>
@@ -4046,69 +4108,74 @@
         <v>26</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="K22" s="39"/>
       <c r="L22" s="54" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="39"/>
       <c r="O22" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P22" s="29" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="Q22" s="35">
         <v>1269</v>
       </c>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U22" s="4">
         <v>1</v>
       </c>
       <c r="V22" s="5">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="15" customHeight="1">
+      <c r="W22" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E23" s="19"/>
       <c r="F23" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K23" s="39"/>
       <c r="L23" s="54" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="39"/>
       <c r="O23" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P23" s="29" t="s">
         <v>27</v>
@@ -4116,52 +4183,57 @@
       <c r="Q23" s="35">
         <v>78</v>
       </c>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U23" s="4">
         <v>1</v>
       </c>
       <c r="V23" s="5">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" ht="15" customHeight="1">
+      <c r="W23" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K24" s="39"/>
       <c r="L24" s="54" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="39"/>
       <c r="O24" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P24" s="29" t="s">
         <v>27</v>
@@ -4169,54 +4241,59 @@
       <c r="Q24" s="35">
         <v>280</v>
       </c>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U24" s="4">
         <v>1</v>
       </c>
       <c r="V24" s="5">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" ht="15" customHeight="1">
+      <c r="W24" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="15" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J25" s="43" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="L25" s="54" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="39"/>
       <c r="O25" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P25" s="29" t="s">
         <v>27</v>
@@ -4227,57 +4304,62 @@
       <c r="R25" s="4">
         <v>210</v>
       </c>
-      <c r="S25" s="19">
+      <c r="S25" s="35">
         <v>90</v>
       </c>
-      <c r="T25" s="19"/>
+      <c r="T25" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U25" s="4">
         <v>1</v>
       </c>
       <c r="V25" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" ht="15" customHeight="1">
+      <c r="W25" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K26" s="39"/>
       <c r="L26" s="54" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="M26" s="19"/>
       <c r="N26" s="39"/>
       <c r="O26" s="19" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="P26" s="29" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Q26" s="35">
         <v>1677</v>
@@ -4285,54 +4367,59 @@
       <c r="R26" s="4">
         <v>2400</v>
       </c>
-      <c r="S26" s="19">
+      <c r="S26" s="35">
         <v>3400</v>
       </c>
-      <c r="T26" s="19"/>
+      <c r="T26" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U26" s="4">
         <v>1</v>
       </c>
       <c r="V26" s="5">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" ht="15" customHeight="1">
+      <c r="W26" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E27" s="19"/>
       <c r="F27" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J27" s="43" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="K27" s="39"/>
       <c r="L27" s="54" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="M27" s="19"/>
       <c r="N27" s="39"/>
       <c r="O27" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P27" s="29" t="s">
         <v>27</v>
@@ -4343,54 +4430,59 @@
       <c r="R27" s="4">
         <v>175</v>
       </c>
-      <c r="S27" s="19">
+      <c r="S27" s="35">
         <v>100</v>
       </c>
-      <c r="T27" s="19"/>
+      <c r="T27" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U27" s="4">
         <v>1</v>
       </c>
       <c r="V27" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" ht="15" customHeight="1">
+      <c r="W27" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="15" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E28" s="19"/>
       <c r="F28" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="K28" s="39"/>
       <c r="L28" s="54" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="M28" s="19"/>
       <c r="N28" s="39"/>
       <c r="O28" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P28" s="29" t="s">
         <v>27</v>
@@ -4401,54 +4493,59 @@
       <c r="R28" s="4">
         <v>175</v>
       </c>
-      <c r="S28" s="19">
+      <c r="S28" s="35">
         <v>100</v>
       </c>
-      <c r="T28" s="19"/>
+      <c r="T28" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U28" s="4">
         <v>1</v>
       </c>
       <c r="V28" s="5">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" ht="15" customHeight="1">
+      <c r="W28" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="15" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="K29" s="39"/>
       <c r="L29" s="54" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="M29" s="19"/>
       <c r="N29" s="39"/>
       <c r="O29" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P29" s="29" t="s">
         <v>27</v>
@@ -4459,57 +4556,62 @@
       <c r="R29" s="4">
         <v>54</v>
       </c>
-      <c r="S29" s="19">
+      <c r="S29" s="35">
         <v>30</v>
       </c>
-      <c r="T29" s="19"/>
+      <c r="T29" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U29" s="4">
         <v>1</v>
       </c>
       <c r="V29" s="5">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" ht="15" customHeight="1">
+      <c r="W29" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="15" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="K30" s="39"/>
       <c r="L30" s="54" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="M30" s="19"/>
       <c r="N30" s="39"/>
       <c r="O30" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P30" s="29" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="Q30" s="35">
         <v>200</v>
@@ -4517,52 +4619,57 @@
       <c r="R30" s="4">
         <v>1000</v>
       </c>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U30" s="4">
         <v>1</v>
       </c>
       <c r="V30" s="5">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" ht="15" customHeight="1">
+      <c r="W30" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E31" s="19"/>
       <c r="F31" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H31" s="29" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="K31" s="39"/>
       <c r="L31" s="54" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="M31" s="19"/>
       <c r="N31" s="39"/>
       <c r="O31" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P31" s="29" t="s">
         <v>27</v>
@@ -4570,52 +4677,57 @@
       <c r="Q31" s="35">
         <v>182</v>
       </c>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U31" s="4">
         <v>1</v>
       </c>
       <c r="V31" s="5">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" ht="15" customHeight="1">
+      <c r="W31" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="I32" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K32" s="39"/>
       <c r="L32" s="54" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="M32" s="19"/>
       <c r="N32" s="39"/>
       <c r="O32" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P32" s="29" t="s">
         <v>27</v>
@@ -4626,54 +4738,59 @@
       <c r="R32" s="4">
         <v>70</v>
       </c>
-      <c r="S32" s="19">
+      <c r="S32" s="35">
         <v>32</v>
       </c>
-      <c r="T32" s="19"/>
+      <c r="T32" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U32" s="4">
         <v>1</v>
       </c>
       <c r="V32" s="5">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" ht="15" customHeight="1">
+      <c r="W32" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="15" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E33" s="19"/>
       <c r="F33" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="J33" s="43" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="K33" s="39"/>
       <c r="L33" s="54" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M33" s="19"/>
       <c r="N33" s="39"/>
       <c r="O33" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P33" s="29" t="s">
         <v>27</v>
@@ -4684,54 +4801,59 @@
       <c r="R33" s="4">
         <v>98</v>
       </c>
-      <c r="S33" s="19">
+      <c r="S33" s="35">
         <v>50</v>
       </c>
-      <c r="T33" s="19"/>
+      <c r="T33" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U33" s="4">
         <v>1</v>
       </c>
       <c r="V33" s="5">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" ht="15" customHeight="1">
+      <c r="W33" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="15" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E34" s="19"/>
       <c r="F34" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K34" s="39"/>
       <c r="L34" s="54" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="39"/>
       <c r="O34" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P34" s="29" t="s">
         <v>27</v>
@@ -4739,52 +4861,57 @@
       <c r="Q34" s="35">
         <v>600</v>
       </c>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U34" s="4">
         <v>1</v>
       </c>
       <c r="V34" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" ht="15" customHeight="1">
+      <c r="W34" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="15" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E35" s="19"/>
       <c r="F35" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J35" s="43" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="K35" s="39"/>
       <c r="L35" s="54" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="M35" s="19"/>
       <c r="N35" s="39"/>
       <c r="O35" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P35" s="29" t="s">
         <v>27</v>
@@ -4792,52 +4919,57 @@
       <c r="Q35" s="35">
         <v>103</v>
       </c>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U35" s="4">
         <v>1</v>
       </c>
       <c r="V35" s="5">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" ht="15" customHeight="1">
+      <c r="W35" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="15" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E36" s="19"/>
       <c r="F36" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="J36" s="43" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="K36" s="39"/>
       <c r="L36" s="54" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M36" s="19"/>
       <c r="N36" s="39"/>
       <c r="O36" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P36" s="29" t="s">
         <v>27</v>
@@ -4848,57 +4980,62 @@
       <c r="R36" s="4">
         <v>73.7</v>
       </c>
-      <c r="S36" s="19">
+      <c r="S36" s="35">
         <v>47.9</v>
       </c>
-      <c r="T36" s="19"/>
+      <c r="T36" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U36" s="4">
         <v>1</v>
       </c>
       <c r="V36" s="5">
         <v>26</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" ht="15" customHeight="1">
+      <c r="W36" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="15" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="29" t="s">
         <v>23</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="K37" s="39"/>
       <c r="L37" s="54" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="M37" s="19"/>
       <c r="N37" s="39"/>
       <c r="O37" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P37" s="29" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Q37" s="35">
         <v>150</v>
@@ -4906,50 +5043,55 @@
       <c r="R37" s="4">
         <v>1500</v>
       </c>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U37" s="4">
         <v>1</v>
       </c>
       <c r="V37" s="5">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" ht="15" customHeight="1">
+      <c r="W37" s="41" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
       <c r="F38" s="29" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="G38" s="29" t="s">
         <v>34</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I38" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K38" s="39"/>
       <c r="L38" s="54" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="M38" s="19"/>
       <c r="N38" s="39"/>
       <c r="O38" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P38" s="29" t="s">
         <v>27</v>
@@ -4957,61 +5099,66 @@
       <c r="Q38" s="35">
         <v>450</v>
       </c>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="U38" s="4">
         <v>3</v>
       </c>
       <c r="V38" s="5">
         <v>110</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" ht="15" customHeight="1">
+      <c r="W38" s="41" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="15" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="30" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I39" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P39" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>439</v>
+        <v>81</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>190</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="U39" s="2">
         <v>3</v>
@@ -5019,21 +5166,24 @@
       <c r="V39" s="5">
         <v>104</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" ht="15" customHeight="1">
+      <c r="W39" s="30" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15" customHeight="1">
       <c r="A40" s="46" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="30" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G40" s="30" t="s">
         <v>33</v>
@@ -5045,27 +5195,27 @@
         <v>26</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="19" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="P40" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>138</v>
+        <v>722</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>220</v>
       </c>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="U40" s="4">
         <v>2</v>
@@ -5073,8 +5223,11 @@
       <c r="V40" s="5">
         <v>54</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" ht="15" customHeight="1">
+      <c r="W40" s="30" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1">
       <c r="A41" s="9" t="s">
         <v>29</v>
       </c>
@@ -5096,30 +5249,32 @@
         <v>34</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="K41" s="2"/>
-      <c r="L41" s="3" t="s">
+      <c r="L41" s="53" t="s">
+        <v>720</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
       <c r="O41" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P41" s="30" t="s">
         <v>36</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>37</v>
+        <v>724</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U41" s="2">
         <v>3</v>
@@ -5127,45 +5282,48 @@
       <c r="V41" s="5">
         <v>149</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" ht="15" customHeight="1">
+      <c r="W41" s="30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="15" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="J42" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="H42" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="I42" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q42" s="2">
         <v>85</v>
@@ -5177,7 +5335,7 @@
         <v>74</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="U42" s="2">
         <v>3</v>
@@ -5185,44 +5343,47 @@
       <c r="V42" s="5">
         <v>103</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" ht="15" customHeight="1">
+      <c r="W42" s="30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="15" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="29" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="H43" s="29" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>26</v>
       </c>
       <c r="J43" s="43" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="L43" s="54" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="M43" s="19"/>
       <c r="N43" s="39"/>
       <c r="O43" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P43" s="29" t="s">
         <v>27</v>
@@ -5230,50 +5391,55 @@
       <c r="Q43" s="35">
         <v>240</v>
       </c>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U43" s="4">
         <v>3</v>
       </c>
       <c r="V43" s="5">
         <v>105</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" ht="15" customHeight="1">
+      <c r="W43" s="41" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="30" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G44" s="30" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H44" s="30" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I44" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P44" s="30" t="s">
         <v>27</v>
@@ -5288,7 +5454,7 @@
         <v>96</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U44" s="2">
         <v>3</v>
@@ -5296,151 +5462,166 @@
       <c r="V44" s="5">
         <v>143</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" ht="15" customHeight="1">
+      <c r="W44" s="30" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="15" customHeight="1">
       <c r="A45" s="10" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B45" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G45" s="28" t="s">
+      <c r="H45" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="H45" s="28" t="s">
+      <c r="I45" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="I45" s="28" t="s">
+      <c r="J45" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J45" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="K45" s="7" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="L45" s="53" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="7"/>
       <c r="O45" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P45" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="S45" s="4">
         <v>128</v>
       </c>
+      <c r="T45" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U45" s="4">
         <v>1</v>
       </c>
       <c r="V45" s="14"/>
-    </row>
-    <row r="46" spans="1:22" ht="15" customHeight="1">
+      <c r="W45" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="15" customHeight="1">
       <c r="A46" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="C46" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G46" s="28" t="s">
+      <c r="H46" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="H46" s="28" t="s">
+      <c r="I46" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="I46" s="28" t="s">
+      <c r="J46" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J46" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="K46" s="7" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="L46" s="53" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="M46" s="4"/>
       <c r="N46" s="7"/>
       <c r="O46" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P46" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="S46" s="4">
         <v>128</v>
       </c>
+      <c r="T46" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U46" s="4">
         <v>1</v>
       </c>
       <c r="V46" s="5">
         <v>84</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" ht="15" customHeight="1">
+      <c r="W46" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="15" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="B47" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G47" s="28" t="s">
-        <v>46</v>
-      </c>
       <c r="H47" s="28" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="53" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="M47" s="4"/>
       <c r="N47" s="7"/>
       <c r="O47" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P47" s="37" t="s">
         <v>27</v>
@@ -5451,42 +5632,48 @@
       <c r="R47" s="4">
         <v>176</v>
       </c>
+      <c r="T47" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U47" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" ht="15" customHeight="1">
+      <c r="W47" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="15" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B48" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G48" s="28" t="s">
-        <v>46</v>
-      </c>
       <c r="H48" s="28" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="53" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="M48" s="4"/>
       <c r="N48" s="7"/>
       <c r="O48" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P48" s="37" t="s">
         <v>27</v>
@@ -5500,53 +5687,59 @@
       <c r="S48" s="4">
         <v>82</v>
       </c>
+      <c r="T48" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U48" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" ht="15" customHeight="1">
+      <c r="W48" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="15" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="28" t="s">
-        <v>46</v>
-      </c>
       <c r="H49" s="28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I49" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="L49" s="53" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="7"/>
       <c r="O49" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P49" s="37" t="s">
         <v>27</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="R49" s="4">
         <v>75</v>
@@ -5554,49 +5747,55 @@
       <c r="S49" s="4">
         <v>35</v>
       </c>
+      <c r="T49" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U49" s="4">
         <v>1</v>
       </c>
       <c r="V49" s="14"/>
-    </row>
-    <row r="50" spans="1:22" ht="15" customHeight="1">
+      <c r="W49" s="37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="15" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B50" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="41" t="s">
         <v>43</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>44</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="19"/>
       <c r="F50" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="29" t="s">
-        <v>46</v>
-      </c>
       <c r="H50" s="29" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="I50" s="29"/>
       <c r="J50" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="L50" s="54" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="M50" s="19"/>
       <c r="N50" s="39"/>
       <c r="O50" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P50" s="29" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Q50" s="35">
         <v>390</v>
@@ -5604,103 +5803,113 @@
       <c r="R50" s="4">
         <v>309</v>
       </c>
-      <c r="S50" s="19">
+      <c r="S50" s="35">
         <v>30</v>
       </c>
-      <c r="T50" s="19"/>
+      <c r="T50" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U50" s="4">
         <v>1</v>
       </c>
       <c r="V50" s="5">
         <v>82</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" ht="15" customHeight="1">
+      <c r="W50" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="15" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B51" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="41" t="s">
         <v>43</v>
-      </c>
-      <c r="C51" s="41" t="s">
-        <v>44</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="19"/>
       <c r="F51" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G51" s="29" t="s">
-        <v>46</v>
-      </c>
       <c r="H51" s="29" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="K51" s="39"/>
       <c r="L51" s="54" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="M51" s="19"/>
       <c r="N51" s="39"/>
       <c r="O51" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P51" s="29" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Q51" s="35">
         <v>400</v>
       </c>
-      <c r="S51" s="19"/>
-      <c r="T51" s="19"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="U51" s="4">
         <v>1</v>
       </c>
       <c r="V51" s="5">
         <v>83</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" ht="15" customHeight="1">
+      <c r="W51" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="15" customHeight="1">
       <c r="A52" s="46" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B52" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="41" t="s">
         <v>43</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>44</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="19"/>
       <c r="F52" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" s="29" t="s">
         <v>45</v>
-      </c>
-      <c r="G52" s="29" t="s">
-        <v>46</v>
       </c>
       <c r="H52" s="29">
         <v>1679</v>
       </c>
       <c r="I52" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J52" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K52" s="39"/>
       <c r="L52" s="54" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="39"/>
       <c r="O52" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P52" s="29" t="s">
         <v>27</v>
@@ -5711,55 +5920,60 @@
       <c r="R52" s="4">
         <v>58</v>
       </c>
-      <c r="S52" s="19">
+      <c r="S52" s="35">
         <v>34</v>
       </c>
-      <c r="T52" s="19"/>
+      <c r="T52" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="U52" s="4">
         <v>1</v>
       </c>
       <c r="V52" s="5">
         <v>85</v>
       </c>
-    </row>
-    <row r="53" spans="1:22" ht="15" customHeight="1">
+      <c r="W52" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="15" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="B53" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="41" t="s">
         <v>43</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>44</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="19"/>
       <c r="F53" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G53" s="29" t="s">
-        <v>46</v>
-      </c>
       <c r="H53" s="29" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="I53" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="J53" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="K53" s="39"/>
       <c r="L53" s="54" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="M53" s="19"/>
       <c r="N53" s="39"/>
       <c r="O53" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P53" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q53" s="35">
         <v>60</v>
@@ -5767,52 +5981,57 @@
       <c r="R53" s="4">
         <v>68</v>
       </c>
-      <c r="S53" s="19">
+      <c r="S53" s="35">
         <v>34</v>
       </c>
-      <c r="T53" s="19"/>
+      <c r="T53" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="U53" s="4">
         <v>1</v>
       </c>
       <c r="V53" s="5">
         <v>87</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" ht="15" customHeight="1">
+      <c r="W53" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="15" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="30" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G54" s="30" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H54" s="30" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P54" s="30" t="s">
         <v>27</v>
@@ -5823,7 +6042,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="U54" s="2">
         <v>3</v>
@@ -5831,43 +6050,46 @@
       <c r="V54" s="5">
         <v>191</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" ht="15" customHeight="1">
+      <c r="W54" s="30" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="15" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
       <c r="F55" s="31" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G55" s="31" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H55" s="31">
         <v>1600</v>
       </c>
       <c r="I55" s="31" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="J55" s="44"/>
       <c r="K55" s="40"/>
       <c r="L55" s="55" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="40"/>
       <c r="O55" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P55" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q55" s="36">
         <v>223</v>
@@ -5875,53 +6097,58 @@
       <c r="R55" s="4">
         <v>110</v>
       </c>
-      <c r="S55" s="11">
+      <c r="S55" s="36">
         <v>150</v>
       </c>
-      <c r="T55" s="12"/>
+      <c r="T55" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="U55" s="4">
         <v>3</v>
       </c>
       <c r="V55" s="5">
         <v>192</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" ht="15" customHeight="1">
+      <c r="W55" s="47" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="15" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="D56" s="11"/>
       <c r="E56" s="11"/>
       <c r="F56" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G56" s="31" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H56" s="31" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="I56" s="31" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="J56" s="44"/>
       <c r="K56" s="40"/>
       <c r="L56" s="55" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="40"/>
       <c r="O56" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P56" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q56" s="36">
         <v>130</v>
@@ -5929,58 +6156,63 @@
       <c r="R56" s="4">
         <v>350</v>
       </c>
-      <c r="S56" s="11">
+      <c r="S56" s="36">
         <v>171</v>
       </c>
-      <c r="T56" s="12"/>
+      <c r="T56" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="U56" s="4">
         <v>3</v>
       </c>
       <c r="V56" s="5">
         <v>135</v>
       </c>
-    </row>
-    <row r="57" spans="1:22" ht="15" customHeight="1">
+      <c r="W56" s="47" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="15" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G57" s="32" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I57" s="32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J57" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K57" s="20"/>
       <c r="L57" s="22" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
       <c r="O57" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P57" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="Q57" s="20" t="s">
-        <v>335</v>
+      <c r="Q57" s="20">
+        <v>165</v>
       </c>
       <c r="R57" s="2">
         <v>55</v>
@@ -5989,7 +6221,7 @@
         <v>97</v>
       </c>
       <c r="T57" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U57" s="2">
         <v>2</v>
@@ -5997,42 +6229,45 @@
       <c r="V57" s="5">
         <v>78</v>
       </c>
-    </row>
-    <row r="58" spans="1:22" ht="15" customHeight="1">
+      <c r="W57" s="32" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="15" customHeight="1">
       <c r="A58" s="46" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
       <c r="F58" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G58" s="31" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H58" s="31" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="I58" s="32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J58" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K58" s="40"/>
       <c r="L58" s="55" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="40"/>
       <c r="O58" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P58" s="31" t="s">
         <v>36</v>
@@ -6043,104 +6278,111 @@
       <c r="R58" s="4">
         <v>38</v>
       </c>
-      <c r="S58" s="11">
+      <c r="S58" s="36">
         <v>35</v>
       </c>
-      <c r="T58" s="12"/>
+      <c r="T58" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="U58" s="4">
         <v>2</v>
       </c>
       <c r="V58" s="5">
         <v>79</v>
       </c>
-    </row>
-    <row r="59" spans="1:22" ht="15" customHeight="1">
+      <c r="W58" s="47" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" ht="15" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
       <c r="F59" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G59" s="31" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H59" s="31" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="I59" s="31" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="J59" s="44" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="K59" s="40"/>
       <c r="L59" s="55" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="40"/>
       <c r="O59" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P59" s="31" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="Q59" s="36"/>
-      <c r="R59" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="S59" s="11"/>
-      <c r="T59" s="12"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="U59" s="4">
         <v>2</v>
       </c>
       <c r="V59" s="5">
         <v>80</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" ht="15" customHeight="1">
+      <c r="W59" s="47" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="15" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C60" s="47" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="11"/>
       <c r="F60" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G60" s="31" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H60" s="31">
         <v>1663</v>
       </c>
       <c r="I60" s="31" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="J60" s="44" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="K60" s="40"/>
       <c r="L60" s="55" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="40"/>
       <c r="O60" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P60" s="31" t="s">
         <v>36</v>
@@ -6148,50 +6390,55 @@
       <c r="Q60" s="36">
         <v>83</v>
       </c>
-      <c r="S60" s="11"/>
-      <c r="T60" s="12"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="U60" s="4">
         <v>2</v>
       </c>
       <c r="V60" s="5">
         <v>81</v>
       </c>
-    </row>
-    <row r="61" spans="1:22" ht="15" customHeight="1">
+      <c r="W60" s="47" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="15" customHeight="1">
       <c r="A61" s="17" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="32" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G61" s="32" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H61" s="32" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I61" s="32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="22" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
       <c r="O61" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P61" s="32" t="s">
         <v>36</v>
@@ -6200,54 +6447,57 @@
         <v>47</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="S61" s="20">
         <v>27.5</v>
       </c>
       <c r="T61" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U61" s="2">
         <v>2</v>
       </c>
       <c r="V61" s="14"/>
-    </row>
-    <row r="62" spans="1:22" ht="15" customHeight="1">
+      <c r="W61" s="32" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="15" customHeight="1">
       <c r="A62" s="17" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="32" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H62" s="32" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="I62" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J62" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="J62" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="K62" s="20"/>
       <c r="L62" s="22" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="M62" s="22"/>
       <c r="N62" s="22"/>
       <c r="O62" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P62" s="32" t="s">
         <v>27</v>
@@ -6262,51 +6512,54 @@
         <v>65</v>
       </c>
       <c r="T62" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U62" s="2">
         <v>2</v>
       </c>
       <c r="V62" s="14"/>
-    </row>
-    <row r="63" spans="1:22" ht="15" customHeight="1">
+      <c r="W62" s="32" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="15" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="31" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="G63" s="31" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H63" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I63" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="J63" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="K63" s="40"/>
       <c r="L63" s="55" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="40"/>
       <c r="O63" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P63" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q63" s="36">
         <v>220</v>
@@ -6314,50 +6567,55 @@
       <c r="R63" s="4">
         <v>200</v>
       </c>
-      <c r="S63" s="11"/>
-      <c r="T63" s="12"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U63" s="4">
         <v>2</v>
       </c>
       <c r="V63" s="5">
         <v>95</v>
       </c>
-    </row>
-    <row r="64" spans="1:22" ht="15" customHeight="1">
+      <c r="W63" s="47" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="15" customHeight="1">
       <c r="A64" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I64" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K64" s="20"/>
       <c r="L64" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M64" s="22"/>
       <c r="N64" s="22"/>
       <c r="O64" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P64" s="32" t="s">
         <v>27</v>
@@ -6368,7 +6626,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="20"/>
       <c r="T64" s="25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U64" s="2">
         <v>1</v>
@@ -6376,42 +6634,45 @@
       <c r="V64" s="5">
         <v>46</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" ht="15" customHeight="1">
+      <c r="W64" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" ht="15" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D65" s="21"/>
       <c r="E65" s="21"/>
       <c r="F65" s="33" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G65" s="33" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="I65" s="33" t="s">
         <v>26</v>
       </c>
       <c r="J65" s="23" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K65" s="23"/>
       <c r="L65" s="56" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="M65" s="21"/>
       <c r="N65" s="23"/>
       <c r="O65" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P65" s="38" t="s">
         <v>27</v>
@@ -6420,31 +6681,36 @@
         <v>468</v>
       </c>
       <c r="S65" s="21"/>
-      <c r="T65" s="26"/>
+      <c r="T65" s="25" t="s">
+        <v>69</v>
+      </c>
       <c r="U65" s="4">
         <v>1</v>
       </c>
       <c r="V65" s="5">
         <v>45</v>
       </c>
-    </row>
-    <row r="66" spans="1:22" ht="15" customHeight="1">
+      <c r="W65" s="38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" ht="15" customHeight="1">
       <c r="A66" s="51" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C66" s="47" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
       <c r="F66" s="31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G66" s="31" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H66" s="31">
         <v>1629</v>
@@ -6453,16 +6719,16 @@
         <v>26</v>
       </c>
       <c r="J66" s="44" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="K66" s="40"/>
       <c r="L66" s="55" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="40"/>
       <c r="O66" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P66" s="31" t="s">
         <v>27</v>
@@ -6473,99 +6739,109 @@
       <c r="R66" s="4">
         <v>105</v>
       </c>
-      <c r="S66" s="11"/>
-      <c r="T66" s="12"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="25" t="s">
+        <v>69</v>
+      </c>
       <c r="U66" s="4">
         <v>1</v>
       </c>
       <c r="V66" s="5">
         <v>47</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" ht="15" customHeight="1">
+      <c r="W66" s="47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="15" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
       <c r="F67" s="31" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G67" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="J67" s="44"/>
       <c r="K67" s="40"/>
       <c r="L67" s="55" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="M67" s="11"/>
       <c r="N67" s="40"/>
       <c r="O67" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P67" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q67" s="36">
         <v>61</v>
       </c>
-      <c r="S67" s="11"/>
-      <c r="T67" s="12"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="25" t="s">
+        <v>69</v>
+      </c>
       <c r="U67" s="4">
         <v>3</v>
       </c>
       <c r="V67" s="5">
         <v>187</v>
       </c>
-    </row>
-    <row r="68" spans="1:22" ht="15" customHeight="1">
+      <c r="W67" s="47" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" ht="15" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="29" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="J68" s="49" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="57" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="39"/>
       <c r="O68" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P68" s="29" t="s">
         <v>27</v>
@@ -6573,103 +6849,113 @@
       <c r="Q68" s="35">
         <v>750</v>
       </c>
-      <c r="S68" s="19"/>
-      <c r="T68" s="19"/>
+      <c r="S68" s="35"/>
+      <c r="T68" s="25" t="s">
+        <v>69</v>
+      </c>
       <c r="U68" s="4">
         <v>3</v>
       </c>
       <c r="V68" s="5">
         <v>194</v>
       </c>
-    </row>
-    <row r="69" spans="1:22" ht="15" customHeight="1">
+      <c r="W68" s="41" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="15" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="D69" s="11"/>
       <c r="E69" s="11"/>
       <c r="F69" s="31" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="G69" s="31" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="H69" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I69" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="L69" s="55" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="40"/>
       <c r="O69" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P69" s="31" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Q69" s="36">
         <v>550</v>
       </c>
-      <c r="S69" s="11"/>
-      <c r="T69" s="12"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U69" s="4">
         <v>3</v>
       </c>
       <c r="V69" s="5">
         <v>111</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" ht="15" customHeight="1">
+      <c r="W69" s="47" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" ht="15" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="31" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="I70" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J70" s="44" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="K70" s="40"/>
       <c r="L70" s="55" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="40"/>
       <c r="O70" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P70" s="31" t="s">
         <v>27</v>
@@ -6677,50 +6963,55 @@
       <c r="Q70" s="36">
         <v>290</v>
       </c>
-      <c r="S70" s="11"/>
-      <c r="T70" s="12"/>
+      <c r="S70" s="36"/>
+      <c r="T70" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U70" s="4">
         <v>3</v>
       </c>
       <c r="V70" s="5">
         <v>114</v>
       </c>
-    </row>
-    <row r="71" spans="1:22" ht="15" customHeight="1">
+      <c r="W70" s="47" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G71" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H71" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="I71" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="G71" s="32" t="s">
+      <c r="J71" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="H71" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="I71" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="J71" s="23" t="s">
-        <v>96</v>
       </c>
       <c r="K71" s="20"/>
       <c r="L71" s="22" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M71" s="22"/>
       <c r="N71" s="22"/>
       <c r="O71" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P71" s="32" t="s">
         <v>27</v>
@@ -6737,145 +7028,156 @@
         <v>3</v>
       </c>
       <c r="V71" s="14"/>
-    </row>
-    <row r="72" spans="1:22" ht="15" customHeight="1">
+      <c r="W71" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" ht="15" customHeight="1">
       <c r="A72" s="17" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="32" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H72" s="32" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I72" s="32" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="22" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="M72" s="22"/>
       <c r="N72" s="22"/>
       <c r="O72" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P72" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Q72" s="20"/>
       <c r="R72" s="2"/>
       <c r="S72" s="20"/>
       <c r="T72" s="25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U72" s="2">
         <v>3</v>
       </c>
       <c r="V72" s="14"/>
-    </row>
-    <row r="73" spans="1:22" ht="15" customHeight="1">
+      <c r="W72" s="32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" ht="15" customHeight="1">
       <c r="A73" s="48" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="31" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H73" s="31">
         <v>1695</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J73" s="44" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="K73" s="40"/>
       <c r="L73" s="55" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="M73" s="11"/>
       <c r="N73" s="40"/>
       <c r="O73" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P73" s="31" t="s">
         <v>27</v>
       </c>
       <c r="Q73" s="36">
-        <v>150</v>
-      </c>
-      <c r="S73" s="11"/>
-      <c r="T73" s="12"/>
+        <v>1500</v>
+      </c>
+      <c r="S73" s="36"/>
+      <c r="T73" s="25" t="s">
+        <v>69</v>
+      </c>
       <c r="U73" s="4">
         <v>3</v>
       </c>
       <c r="V73" s="5">
         <v>186</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" ht="15" customHeight="1">
+      <c r="W73" s="47" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="15" customHeight="1">
       <c r="A74" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="32" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G74" s="32" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H74" s="32" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I74" s="32" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J74" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="53" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="M74" s="22"/>
       <c r="N74" s="22" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O74" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P74" s="32" t="s">
         <v>36</v>
@@ -6890,7 +7192,7 @@
         <v>75.5</v>
       </c>
       <c r="T74" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U74" s="2">
         <v>2</v>
@@ -6898,42 +7200,45 @@
       <c r="V74" s="5">
         <v>74</v>
       </c>
-    </row>
-    <row r="75" spans="1:22" ht="15" customHeight="1">
+      <c r="W74" s="32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" ht="15" customHeight="1">
       <c r="A75" s="48" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="31" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K75" s="40"/>
       <c r="L75" s="55" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="M75" s="11"/>
       <c r="N75" s="40"/>
       <c r="O75" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P75" s="31" t="s">
         <v>36</v>
@@ -6944,52 +7249,57 @@
       <c r="R75" s="4">
         <v>218</v>
       </c>
-      <c r="S75" s="11">
+      <c r="S75" s="36">
         <v>140</v>
       </c>
-      <c r="T75" s="12"/>
+      <c r="T75" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="U75" s="4">
         <v>2</v>
       </c>
       <c r="V75" s="5">
         <v>75</v>
       </c>
-    </row>
-    <row r="76" spans="1:22" ht="15" customHeight="1">
+      <c r="W75" s="47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="15" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="31" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="K76" s="40"/>
       <c r="L76" s="55" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="M76" s="11"/>
       <c r="N76" s="40"/>
       <c r="O76" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P76" s="31" t="s">
         <v>36</v>
@@ -7000,37 +7310,42 @@
       <c r="R76" s="4">
         <v>191</v>
       </c>
-      <c r="S76" s="11">
+      <c r="S76" s="36">
         <v>75</v>
       </c>
-      <c r="T76" s="12"/>
+      <c r="T76" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="U76" s="4">
         <v>2</v>
       </c>
       <c r="V76" s="5">
         <v>76</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" ht="15" customHeight="1">
+      <c r="W76" s="47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" ht="15" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G77" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I77" s="31" t="s">
         <v>26</v>
@@ -7038,61 +7353,66 @@
       <c r="J77" s="44"/>
       <c r="K77" s="40"/>
       <c r="L77" s="55" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="M77" s="11"/>
       <c r="N77" s="40"/>
       <c r="O77" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P77" s="31" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="Q77" s="36"/>
-      <c r="S77" s="11"/>
-      <c r="T77" s="12"/>
+      <c r="S77" s="36"/>
+      <c r="T77" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U77" s="4">
         <v>2</v>
       </c>
       <c r="V77" s="5">
         <v>57</v>
       </c>
-    </row>
-    <row r="78" spans="1:22" ht="15" customHeight="1">
+      <c r="W77" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" ht="15" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G78" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H78" s="31" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I78" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="K78" s="40"/>
       <c r="L78" s="55" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="M78" s="11"/>
       <c r="N78" s="40"/>
       <c r="O78" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P78" s="31" t="s">
         <v>27</v>
@@ -7100,56 +7420,61 @@
       <c r="Q78" s="36">
         <v>310</v>
       </c>
-      <c r="S78" s="11"/>
-      <c r="T78" s="12"/>
+      <c r="S78" s="36"/>
+      <c r="T78" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U78" s="4">
         <v>2</v>
       </c>
       <c r="V78" s="5">
         <v>58</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" ht="15" customHeight="1">
+      <c r="W78" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" ht="15" customHeight="1">
       <c r="A79" s="15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="32" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G79" s="32" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I79" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J79" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="J79" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="K79" s="20"/>
       <c r="L79" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M79" s="22"/>
       <c r="N79" s="22"/>
       <c r="O79" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P79" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q79" s="20" t="s">
-        <v>185</v>
+      <c r="Q79" s="20">
+        <v>70</v>
       </c>
       <c r="R79" s="2"/>
       <c r="S79" s="20"/>
@@ -7160,16 +7485,19 @@
         <v>2</v>
       </c>
       <c r="V79" s="14"/>
-    </row>
-    <row r="80" spans="1:22" ht="15" customHeight="1">
+      <c r="W79" s="32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="15" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
@@ -7177,25 +7505,25 @@
         <v>32</v>
       </c>
       <c r="G80" s="31" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H80" s="31">
         <v>1630</v>
       </c>
       <c r="I80" s="31" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="K80" s="40"/>
       <c r="L80" s="55" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="M80" s="11"/>
       <c r="N80" s="40"/>
       <c r="O80" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P80" s="31" t="s">
         <v>27</v>
@@ -7203,201 +7531,221 @@
       <c r="Q80" s="36">
         <v>87</v>
       </c>
-      <c r="S80" s="11"/>
-      <c r="T80" s="12"/>
+      <c r="S80" s="36"/>
+      <c r="T80" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U80" s="4">
         <v>2</v>
       </c>
       <c r="V80" s="5">
         <v>65</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" ht="15" customHeight="1">
+      <c r="W80" s="47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" ht="15" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
       <c r="F81" s="31" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G81" s="31" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="I81" s="31" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="K81" s="40" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="L81" s="55" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="M81" s="11"/>
       <c r="N81" s="40"/>
       <c r="O81" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P81" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q81" s="36" t="s">
-        <v>644</v>
-      </c>
-      <c r="S81" s="11"/>
-      <c r="T81" s="12"/>
+      <c r="Q81" s="36">
+        <v>400</v>
+      </c>
+      <c r="S81" s="36"/>
+      <c r="T81" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U81" s="4">
         <v>3</v>
       </c>
       <c r="V81" s="5">
         <v>116</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" ht="15" customHeight="1">
+      <c r="W81" s="47" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" ht="15" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
       <c r="F82" s="31" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G82" s="31" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="I82" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J82" s="44" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="K82" s="40"/>
       <c r="L82" s="55" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="M82" s="11"/>
       <c r="N82" s="40"/>
       <c r="O82" s="11" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="P82" s="31" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="Q82" s="36"/>
-      <c r="S82" s="11"/>
-      <c r="T82" s="12"/>
+      <c r="S82" s="36"/>
+      <c r="T82" s="12" t="s">
+        <v>725</v>
+      </c>
       <c r="U82" s="4">
         <v>3</v>
       </c>
       <c r="V82" s="5">
         <v>102</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" ht="15" customHeight="1">
+      <c r="W82" s="47" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" ht="15" customHeight="1">
       <c r="A83" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D83" s="21"/>
       <c r="E83" s="21"/>
       <c r="F83" s="33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G83" s="33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H83" s="33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I83" s="33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J83" s="23"/>
       <c r="K83" s="23"/>
       <c r="L83" s="56" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="M83" s="21"/>
       <c r="N83" s="23"/>
       <c r="O83" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P83" s="38" t="s">
         <v>27</v>
       </c>
       <c r="Q83" s="21" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="S83" s="21"/>
-      <c r="T83" s="26"/>
+      <c r="T83" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U83" s="4">
         <v>1</v>
       </c>
       <c r="V83" s="5">
         <v>34</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" ht="15" customHeight="1">
+      <c r="W83" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" ht="15" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
       <c r="F84" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G84" s="31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I84" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K84" s="40"/>
       <c r="L84" s="55" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M84" s="11"/>
       <c r="N84" s="40"/>
       <c r="O84" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P84" s="31" t="s">
         <v>27</v>
@@ -7412,7 +7760,7 @@
         <v>170</v>
       </c>
       <c r="T84" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U84" s="4">
         <v>1</v>
@@ -7420,42 +7768,45 @@
       <c r="V84" s="5">
         <v>35</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" ht="15" customHeight="1">
+      <c r="W84" s="47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" ht="15" customHeight="1">
       <c r="A85" s="46" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
       <c r="F85" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G85" s="31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="I85" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="J85" s="44" t="s">
-        <v>647</v>
-      </c>
-      <c r="K85" s="40"/>
+        <v>511</v>
+      </c>
+      <c r="I85" s="31"/>
+      <c r="J85" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" s="44" t="s">
+        <v>633</v>
+      </c>
       <c r="L85" s="55" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="M85" s="11"/>
       <c r="N85" s="40"/>
       <c r="O85" s="19" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="P85" s="31" t="s">
         <v>27</v>
@@ -7466,102 +7817,112 @@
       <c r="R85" s="4">
         <v>138</v>
       </c>
-      <c r="S85" s="11">
+      <c r="S85" s="36">
         <v>146</v>
       </c>
-      <c r="T85" s="12"/>
+      <c r="T85" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U85" s="4">
         <v>1</v>
       </c>
       <c r="V85" s="5">
         <v>37</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" ht="15" customHeight="1">
+      <c r="W85" s="47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" ht="15" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
       <c r="F86" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G86" s="31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H86" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="I86" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="J86" s="44"/>
+        <v>144</v>
+      </c>
+      <c r="I86" s="31"/>
+      <c r="J86" s="23" t="s">
+        <v>52</v>
+      </c>
       <c r="K86" s="40"/>
       <c r="L86" s="55" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="M86" s="11"/>
       <c r="N86" s="40"/>
       <c r="O86" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P86" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q86" s="36"/>
+      <c r="S86" s="36"/>
+      <c r="T86" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="Q86" s="36"/>
-      <c r="S86" s="11"/>
-      <c r="T86" s="12"/>
       <c r="U86" s="4">
         <v>1</v>
       </c>
       <c r="V86" s="5">
         <v>38</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" ht="15" customHeight="1">
+      <c r="W86" s="47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" ht="15" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D87" s="11"/>
       <c r="E87" s="11"/>
       <c r="F87" s="31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G87" s="31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H87" s="31" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="I87" s="31"/>
       <c r="J87" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K87" s="40" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="L87" s="55" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="M87" s="11"/>
       <c r="N87" s="40"/>
       <c r="O87" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P87" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q87" s="36">
         <v>228</v>
@@ -7569,50 +7930,55 @@
       <c r="R87" s="4">
         <v>98</v>
       </c>
-      <c r="S87" s="11">
+      <c r="S87" s="36">
         <v>83</v>
       </c>
-      <c r="T87" s="12"/>
+      <c r="T87" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U87" s="4">
         <v>1</v>
       </c>
       <c r="V87" s="5">
         <v>39</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" ht="15" customHeight="1">
+      <c r="W87" s="47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" ht="15" customHeight="1">
       <c r="A88" s="17" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C88" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="32" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G88" s="32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H88" s="32">
         <v>1677</v>
       </c>
       <c r="I88" s="32"/>
       <c r="J88" s="23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K88" s="20"/>
       <c r="L88" s="22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M88" s="22"/>
       <c r="N88" s="22"/>
       <c r="O88" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P88" s="32" t="s">
         <v>27</v>
@@ -7633,24 +7999,27 @@
         <v>3</v>
       </c>
       <c r="V88" s="14"/>
-    </row>
-    <row r="89" spans="1:22" ht="15" customHeight="1">
+      <c r="W88" s="32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" ht="15" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C89" s="47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
       <c r="F89" s="31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G89" s="31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H89" s="31">
         <v>1670</v>
@@ -7659,76 +8028,81 @@
         <v>26</v>
       </c>
       <c r="J89" s="44" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="K89" s="40"/>
       <c r="L89" s="55" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="40"/>
       <c r="O89" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P89" s="31" t="s">
         <v>27</v>
       </c>
       <c r="Q89" s="36"/>
-      <c r="S89" s="11"/>
-      <c r="T89" s="12"/>
+      <c r="S89" s="36"/>
+      <c r="T89" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U89" s="4">
         <v>2</v>
       </c>
       <c r="V89" s="5">
         <v>63</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" ht="15" customHeight="1">
+      <c r="W89" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" ht="15" customHeight="1">
       <c r="A90" s="17" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="32" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G90" s="32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I90" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="J90" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="J90" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="K90" s="20"/>
       <c r="L90" s="22" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="M90" s="22"/>
       <c r="N90" s="22"/>
       <c r="O90" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P90" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q90" s="20" t="s">
-        <v>447</v>
+        <v>39</v>
+      </c>
+      <c r="Q90" s="20">
+        <v>200</v>
       </c>
       <c r="R90" s="2"/>
       <c r="S90" s="20"/>
       <c r="T90" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U90" s="2">
         <v>3</v>
@@ -7736,345 +8110,372 @@
       <c r="V90" s="5">
         <v>133</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" ht="15" customHeight="1">
+      <c r="W90" s="32" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" ht="15" customHeight="1">
       <c r="A91" s="15" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="32" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G91" s="32" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H91" s="32" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I91" s="32"/>
       <c r="J91" s="23" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K91" s="20"/>
       <c r="L91" s="22" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="M91" s="22"/>
       <c r="N91" s="22"/>
       <c r="O91" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P91" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q91" s="20" t="s">
-        <v>71</v>
+        <v>202</v>
+      </c>
+      <c r="Q91" s="20">
+        <v>200</v>
       </c>
       <c r="R91" s="2"/>
       <c r="S91" s="20"/>
       <c r="T91" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U91" s="2">
         <v>3</v>
       </c>
       <c r="V91" s="14"/>
-    </row>
-    <row r="92" spans="1:22" ht="15" customHeight="1">
+      <c r="W91" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" ht="15" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C92" s="47" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
       <c r="F92" s="31" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G92" s="31" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="I92" s="31" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="J92" s="50" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="K92" s="40"/>
       <c r="L92" s="55" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="40"/>
       <c r="O92" s="19" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="P92" s="31" t="s">
         <v>27</v>
       </c>
       <c r="Q92" s="36"/>
-      <c r="S92" s="11"/>
-      <c r="T92" s="12"/>
+      <c r="S92" s="36"/>
+      <c r="T92" s="12" t="s">
+        <v>218</v>
+      </c>
       <c r="U92" s="4">
         <v>3</v>
       </c>
       <c r="V92" s="5">
         <v>171</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" ht="15" customHeight="1">
+      <c r="W92" s="47" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" ht="15" customHeight="1">
       <c r="A93" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G93" s="32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H93" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I93" s="32"/>
       <c r="J93" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K93" s="20"/>
       <c r="L93" s="22" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="M93" s="22"/>
       <c r="N93" s="22"/>
       <c r="O93" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P93" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q93" s="20" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="Q93" s="20">
+        <v>200</v>
       </c>
       <c r="R93" s="2"/>
       <c r="S93" s="20"/>
       <c r="T93" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U93" s="2">
         <v>3</v>
       </c>
       <c r="V93" s="14"/>
-    </row>
-    <row r="94" spans="1:22" ht="15" customHeight="1">
+      <c r="W93" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" ht="15" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="C94" s="47" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
       <c r="F94" s="31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G94" s="31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H94" s="31" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="I94" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="K94" s="40"/>
       <c r="L94" s="55" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="40"/>
       <c r="O94" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P94" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q94" s="36"/>
-      <c r="S94" s="11"/>
-      <c r="T94" s="12"/>
+      <c r="S94" s="36"/>
+      <c r="T94" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U94" s="4">
         <v>3</v>
       </c>
       <c r="V94" s="5">
         <v>176</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" ht="15" customHeight="1">
+      <c r="W94" s="47" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" ht="15" customHeight="1">
       <c r="A95" s="17" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="32" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="G95" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H95" s="32" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="I95" s="32"/>
       <c r="J95" s="23" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="K95" s="20"/>
       <c r="L95" s="22" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="M95" s="22"/>
       <c r="N95" s="22"/>
       <c r="O95" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P95" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q95" s="20" t="s">
-        <v>138</v>
+      <c r="Q95" s="20">
+        <v>220</v>
       </c>
       <c r="R95" s="2"/>
       <c r="S95" s="20"/>
       <c r="T95" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U95" s="2">
         <v>3</v>
       </c>
       <c r="V95" s="14"/>
-    </row>
-    <row r="96" spans="1:22" ht="15" customHeight="1">
+      <c r="W95" s="32" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" ht="15" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C96" s="47" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D96" s="11"/>
       <c r="E96" s="11"/>
       <c r="F96" s="31" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="G96" s="31" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="H96" s="31" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="I96" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J96" s="23" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="K96" s="40"/>
       <c r="L96" s="55" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="M96" s="11"/>
       <c r="N96" s="40"/>
       <c r="O96" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P96" s="31" t="s">
         <v>27</v>
       </c>
       <c r="Q96" s="36"/>
-      <c r="S96" s="11"/>
-      <c r="T96" s="12"/>
+      <c r="S96" s="36"/>
+      <c r="T96" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U96" s="4">
         <v>2</v>
       </c>
       <c r="V96" s="5">
         <v>97</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" ht="15" customHeight="1">
+      <c r="W96" s="47" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" ht="15" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="32" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G97" s="32" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I97" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J97" s="23" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="K97" s="20"/>
       <c r="L97" s="22" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M97" s="22"/>
       <c r="N97" s="22"/>
       <c r="O97" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P97" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q97" s="20" t="s">
-        <v>380</v>
+      <c r="Q97" s="20">
+        <v>145</v>
       </c>
       <c r="R97" s="2"/>
       <c r="S97" s="20"/>
@@ -8087,94 +8488,102 @@
       <c r="V97" s="5">
         <v>53</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" ht="15" customHeight="1">
+      <c r="W97" s="32" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" ht="15" customHeight="1">
       <c r="A98" s="48" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="D98" s="11"/>
       <c r="E98" s="11"/>
       <c r="F98" s="31" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="H98" s="31" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I98" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J98" s="44" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="K98" s="40"/>
       <c r="L98" s="55" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="M98" s="11"/>
       <c r="N98" s="40"/>
       <c r="O98" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P98" s="31" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Q98" s="36">
         <v>350</v>
       </c>
-      <c r="S98" s="11"/>
-      <c r="T98" s="12"/>
+      <c r="S98" s="36"/>
+      <c r="T98" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U98" s="4">
         <v>3</v>
       </c>
       <c r="V98" s="5">
         <v>106</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" ht="15" customHeight="1">
+      <c r="W98" s="47" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" ht="15" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
       <c r="F99" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G99" s="32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H99" s="32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I99" s="32"/>
       <c r="J99" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K99" s="20"/>
       <c r="L99" s="22" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M99" s="22"/>
       <c r="N99" s="22"/>
       <c r="O99" s="19" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="P99" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Q99" s="20">
         <v>204</v>
@@ -8182,149 +8591,160 @@
       <c r="R99" s="2"/>
       <c r="S99" s="20"/>
       <c r="T99" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U99" s="2">
         <v>1</v>
       </c>
       <c r="V99" s="14"/>
-    </row>
-    <row r="100" spans="1:22" ht="15" customHeight="1">
+      <c r="W99" s="32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" ht="15" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
       <c r="F100" s="32" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G100" s="32" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H100" s="32" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="I100" s="32"/>
       <c r="J100" s="23" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="K100" s="20"/>
       <c r="L100" s="53" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="M100" s="22"/>
       <c r="N100" s="22" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="O100" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P100" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="Q100" s="20" t="s">
-        <v>264</v>
+      <c r="Q100" s="20">
+        <v>195</v>
       </c>
       <c r="R100" s="2"/>
       <c r="S100" s="20"/>
       <c r="T100" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U100" s="2">
         <v>3</v>
       </c>
       <c r="V100" s="14"/>
-    </row>
-    <row r="101" spans="1:22" ht="15" customHeight="1">
+      <c r="W100" s="32" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" ht="15" customHeight="1">
       <c r="A101" s="17" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="21"/>
       <c r="F101" s="33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G101" s="33" t="s">
         <v>24</v>
       </c>
       <c r="H101" s="33" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="I101" s="33" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="J101" s="23"/>
       <c r="K101" s="23"/>
       <c r="L101" s="56" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="M101" s="21"/>
       <c r="N101" s="23"/>
       <c r="O101" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P101" s="38" t="s">
         <v>27</v>
       </c>
       <c r="Q101" s="21" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="S101" s="21"/>
-      <c r="T101" s="26"/>
+      <c r="T101" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U101" s="4">
         <v>3</v>
       </c>
       <c r="V101" s="5">
         <v>107</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" ht="15" customHeight="1">
+      <c r="W101" s="38" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" ht="15" customHeight="1">
       <c r="A102" s="46" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
       <c r="F102" s="31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G102" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H102" s="31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I102" s="31" t="s">
         <v>26</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="K102" s="40"/>
       <c r="L102" s="55" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="M102" s="11"/>
       <c r="N102" s="40"/>
       <c r="O102" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P102" s="31" t="s">
         <v>27</v>
@@ -8332,50 +8752,55 @@
       <c r="Q102" s="36">
         <v>500</v>
       </c>
-      <c r="S102" s="11"/>
-      <c r="T102" s="12"/>
+      <c r="S102" s="36"/>
+      <c r="T102" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U102" s="4">
         <v>3</v>
       </c>
       <c r="V102" s="5">
         <v>109</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" ht="15" customHeight="1">
+      <c r="W102" s="47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" ht="15" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
       <c r="F103" s="31" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G103" s="31" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H103" s="31" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="I103" s="31" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="J103" s="44" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="K103" s="40"/>
       <c r="L103" s="55" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="M103" s="11"/>
       <c r="N103" s="40"/>
       <c r="O103" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P103" s="31" t="s">
         <v>36</v>
@@ -8383,56 +8808,60 @@
       <c r="Q103" s="36">
         <v>50</v>
       </c>
-      <c r="S103" s="11"/>
-      <c r="T103" s="12"/>
+      <c r="S103" s="36"/>
+      <c r="T103" s="25" t="s">
+        <v>28</v>
+      </c>
       <c r="U103" s="4">
         <v>3</v>
       </c>
       <c r="V103" s="5">
         <v>152</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" ht="15" customHeight="1">
+      <c r="W103" s="47" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" ht="15" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C104" s="32" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="32" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G104" s="32" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H104" s="32" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I104" s="32" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J104" s="23" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="K104" s="20"/>
       <c r="L104" s="22" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M104" s="22"/>
       <c r="N104" s="22"/>
       <c r="O104" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P104" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q104" s="20"/>
-      <c r="R104" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="R104" s="20"/>
       <c r="S104" s="20"/>
       <c r="T104" s="25" t="s">
         <v>28</v>
@@ -8441,48 +8870,51 @@
         <v>3</v>
       </c>
       <c r="V104" s="14"/>
-    </row>
-    <row r="105" spans="1:22" ht="15" customHeight="1">
+      <c r="W104" s="32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" ht="15" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B105" s="32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C105" s="32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G105" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H105" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I105" s="32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J105" s="23" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K105" s="20"/>
       <c r="L105" s="22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M105" s="22"/>
       <c r="N105" s="22"/>
       <c r="O105" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P105" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q105" s="20" t="s">
-        <v>71</v>
+      <c r="Q105" s="20">
+        <v>200</v>
       </c>
       <c r="R105" s="2"/>
       <c r="S105" s="20"/>
@@ -8493,148 +8925,159 @@
         <v>3</v>
       </c>
       <c r="V105" s="14"/>
-    </row>
-    <row r="106" spans="1:22" ht="15" customHeight="1">
+      <c r="W105" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" ht="15" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C106" s="32" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="G106" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H106" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="I106" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="J106" s="23" t="s">
         <v>154</v>
-      </c>
-      <c r="G106" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="H106" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="I106" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="J106" s="23" t="s">
-        <v>158</v>
       </c>
       <c r="K106" s="20"/>
       <c r="L106" s="22" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="M106" s="22"/>
       <c r="N106" s="22"/>
       <c r="O106" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P106" s="32" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="Q106" s="20"/>
       <c r="R106" s="2"/>
       <c r="S106" s="20"/>
       <c r="T106" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U106" s="2">
         <v>3</v>
       </c>
       <c r="V106" s="14"/>
-    </row>
-    <row r="107" spans="1:22" ht="15" customHeight="1">
+      <c r="W106" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" ht="15" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D107" s="21"/>
       <c r="E107" s="21"/>
       <c r="F107" s="33" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G107" s="33" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H107" s="33" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J107" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K107" s="23"/>
       <c r="L107" s="56" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="M107" s="21"/>
       <c r="N107" s="23"/>
       <c r="O107" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P107" s="38" t="s">
         <v>27</v>
       </c>
       <c r="Q107" s="21" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="R107" s="4" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="S107" s="21" t="s">
-        <v>413</v>
-      </c>
-      <c r="T107" s="26"/>
+        <v>403</v>
+      </c>
+      <c r="T107" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U107" s="4">
         <v>1</v>
       </c>
       <c r="V107" s="5">
         <v>40</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" ht="15" customHeight="1">
+      <c r="W107" s="38" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" ht="15" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B108" s="33" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D108" s="21"/>
       <c r="E108" s="21"/>
       <c r="F108" s="33" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G108" s="33" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H108" s="33" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="J108" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K108" s="23"/>
       <c r="L108" s="56" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="M108" s="21"/>
       <c r="N108" s="23"/>
       <c r="O108" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P108" s="38" t="s">
         <v>27</v>
@@ -8648,98 +9091,108 @@
       <c r="S108" s="21">
         <v>114</v>
       </c>
-      <c r="T108" s="26"/>
+      <c r="T108" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U108" s="4">
         <v>1</v>
       </c>
       <c r="V108" s="5">
         <v>41</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" ht="15" customHeight="1">
+      <c r="W108" s="38" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" ht="15" customHeight="1">
       <c r="A109" s="46" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D109" s="11"/>
       <c r="E109" s="11"/>
       <c r="F109" s="31" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G109" s="31" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H109" s="31" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="I109" s="31" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="J109" s="44" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="K109" s="40"/>
       <c r="L109" s="55" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="M109" s="11"/>
       <c r="N109" s="40"/>
       <c r="O109" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P109" s="31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Q109" s="36"/>
-      <c r="S109" s="11"/>
-      <c r="T109" s="12"/>
+      <c r="S109" s="36"/>
+      <c r="T109" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U109" s="4">
         <v>1</v>
       </c>
       <c r="V109" s="5">
         <v>42</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" ht="15" customHeight="1">
+      <c r="W109" s="47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" ht="15" customHeight="1">
       <c r="A110" s="46" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D110" s="11"/>
       <c r="E110" s="11"/>
       <c r="F110" s="31" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G110" s="31" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H110" s="31" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="I110" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J110" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="J110" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="K110" s="40"/>
       <c r="L110" s="58" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="M110" s="11"/>
       <c r="N110" s="40"/>
       <c r="O110" s="19" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="P110" s="31" t="s">
         <v>27</v>
@@ -8750,157 +9203,172 @@
       <c r="R110" s="4">
         <v>296</v>
       </c>
-      <c r="S110" s="11">
+      <c r="S110" s="36">
         <v>44</v>
       </c>
-      <c r="T110" s="12"/>
+      <c r="T110" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U110" s="4">
         <v>1</v>
       </c>
       <c r="V110" s="5">
         <v>43</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" ht="15" customHeight="1">
+      <c r="W110" s="47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" ht="15" customHeight="1">
       <c r="A111" s="46" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D111" s="11"/>
       <c r="E111" s="11"/>
       <c r="F111" s="31" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G111" s="31" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H111" s="31" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="I111" s="31" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="J111" s="44" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="K111" s="40"/>
       <c r="L111" s="55" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="M111" s="11"/>
       <c r="N111" s="40"/>
-      <c r="O111" s="11"/>
+      <c r="O111" s="11" t="s">
+        <v>712</v>
+      </c>
       <c r="P111" s="31" t="s">
         <v>27</v>
       </c>
       <c r="Q111" s="36">
         <v>66</v>
       </c>
-      <c r="S111" s="11"/>
-      <c r="T111" s="12"/>
+      <c r="S111" s="36"/>
+      <c r="T111" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="U111" s="4">
         <v>1</v>
       </c>
       <c r="V111" s="5">
         <v>44</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" ht="15" customHeight="1">
+      <c r="W111" s="47" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" ht="15" customHeight="1">
       <c r="A112" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C112" s="32" t="s">
         <v>64</v>
-      </c>
-      <c r="B112" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C112" s="32" t="s">
-        <v>66</v>
       </c>
       <c r="D112" s="20"/>
       <c r="E112" s="20"/>
       <c r="F112" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G112" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H112" s="32" t="s">
         <v>67</v>
-      </c>
-      <c r="G112" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="H112" s="32" t="s">
-        <v>69</v>
       </c>
       <c r="I112" s="32"/>
       <c r="J112" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K112" s="20"/>
       <c r="L112" s="22" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="M112" s="22"/>
       <c r="N112" s="22"/>
       <c r="O112" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P112" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q112" s="20" t="s">
-        <v>71</v>
+      <c r="Q112" s="20">
+        <v>200</v>
       </c>
       <c r="R112" s="2"/>
       <c r="S112" s="20"/>
       <c r="T112" s="25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U112" s="2">
         <v>3</v>
       </c>
       <c r="V112" s="14"/>
-    </row>
-    <row r="113" spans="1:22" ht="15" customHeight="1">
+      <c r="W112" s="32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="15" customHeight="1">
       <c r="A113" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B113" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="B113" s="32" t="s">
+      <c r="C113" s="32" t="s">
         <v>56</v>
-      </c>
-      <c r="C113" s="32" t="s">
-        <v>57</v>
       </c>
       <c r="D113" s="20"/>
       <c r="E113" s="20"/>
       <c r="F113" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G113" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G113" s="32" t="s">
+      <c r="H113" s="32" t="s">
         <v>59</v>
-      </c>
-      <c r="H113" s="32" t="s">
-        <v>60</v>
       </c>
       <c r="I113" s="32" t="s">
         <v>26</v>
       </c>
       <c r="J113" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K113" s="20"/>
       <c r="L113" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M113" s="22"/>
       <c r="N113" s="22"/>
       <c r="O113" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P113" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="Q113" s="20" t="s">
-        <v>63</v>
+      <c r="Q113" s="20">
+        <v>350</v>
       </c>
       <c r="R113" s="2"/>
       <c r="S113" s="20"/>
@@ -8911,42 +9379,45 @@
         <v>3</v>
       </c>
       <c r="V113" s="14"/>
-    </row>
-    <row r="114" spans="1:22" ht="15" customHeight="1">
+      <c r="W113" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="15" customHeight="1">
       <c r="A114" s="15" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B114" s="32" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C114" s="32" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
       <c r="F114" s="32" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="G114" s="32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H114" s="32" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I114" s="32" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="J114" s="23" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="K114" s="20"/>
       <c r="L114" s="22" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="M114" s="22"/>
       <c r="N114" s="22"/>
       <c r="O114" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P114" s="32" t="s">
         <v>27</v>
@@ -8955,280 +9426,298 @@
       <c r="R114" s="2"/>
       <c r="S114" s="20"/>
       <c r="T114" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U114" s="2">
         <v>3</v>
       </c>
       <c r="V114" s="14"/>
-    </row>
-    <row r="115" spans="1:22" ht="15" customHeight="1">
+      <c r="W114" s="32" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" ht="15" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B115" s="32" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C115" s="32" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D115" s="20"/>
       <c r="E115" s="20"/>
       <c r="F115" s="32" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="G115" s="32" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="H115" s="32" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="I115" s="32"/>
       <c r="J115" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="22" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
       <c r="O115" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P115" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Q115" s="20"/>
       <c r="R115" s="2"/>
       <c r="S115" s="20"/>
       <c r="T115" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U115" s="2">
         <v>3</v>
       </c>
       <c r="V115" s="14"/>
-    </row>
-    <row r="116" spans="1:22" ht="15" customHeight="1">
+      <c r="W115" s="32" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="15" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D116" s="20"/>
       <c r="E116" s="20"/>
       <c r="F116" s="32" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G116" s="32" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H116" s="32" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I116" s="32" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J116" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="K116" s="20"/>
       <c r="L116" s="22" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="M116" s="22"/>
       <c r="N116" s="22"/>
       <c r="O116" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P116" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q116" s="20" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="Q116" s="20">
+        <v>200</v>
       </c>
       <c r="R116" s="2"/>
       <c r="S116" s="20"/>
       <c r="T116" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U116" s="4">
         <v>3</v>
       </c>
       <c r="V116" s="14"/>
-    </row>
-    <row r="117" spans="1:22" ht="15" customHeight="1">
+      <c r="W116" s="32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" ht="15" customHeight="1">
       <c r="A117" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B117" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="C117" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F117" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="G117" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="H117" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="I117" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="B117" s="32" t="s">
+      <c r="J117" s="23" t="s">
         <v>282</v>
-      </c>
-      <c r="C117" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="D117" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E117" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="F117" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="G117" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="H117" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="I117" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="J117" s="23" t="s">
-        <v>289</v>
       </c>
       <c r="K117" s="20"/>
       <c r="L117" s="22" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="M117" s="22"/>
       <c r="N117" s="22"/>
       <c r="O117" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P117" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="Q117" s="20" t="s">
-        <v>291</v>
+      <c r="Q117" s="20">
+        <v>226</v>
       </c>
       <c r="R117" s="2"/>
       <c r="S117" s="20"/>
       <c r="T117" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U117" s="4">
         <v>3</v>
       </c>
       <c r="V117" s="14"/>
-    </row>
-    <row r="118" spans="1:22" ht="15" customHeight="1">
+      <c r="W117" s="32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" ht="15" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D118" s="20"/>
       <c r="E118" s="20"/>
       <c r="F118" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G118" s="32" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I118" s="32" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="J118" s="23" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="K118" s="20"/>
       <c r="L118" s="22" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
       <c r="O118" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P118" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="Q118" s="20" t="s">
-        <v>195</v>
+      <c r="Q118" s="20">
+        <v>180</v>
       </c>
       <c r="R118" s="2"/>
       <c r="S118" s="20"/>
       <c r="T118" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U118" s="4">
         <v>3</v>
       </c>
       <c r="V118" s="14"/>
-    </row>
-    <row r="119" spans="1:22" ht="15" customHeight="1">
+      <c r="W118" s="32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" ht="15" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D119" s="20"/>
       <c r="E119" s="20"/>
       <c r="F119" s="32" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G119" s="32" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="I119" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J119" s="23" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="22" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P119" s="32" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Q119" s="20"/>
       <c r="R119" s="2"/>
       <c r="S119" s="20"/>
       <c r="T119" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U119" s="2">
         <v>2</v>
       </c>
       <c r="V119" s="14"/>
-    </row>
-    <row r="120" spans="1:22" ht="15" customHeight="1">
+      <c r="W119" s="32" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" ht="15" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D120" s="20"/>
       <c r="E120" s="20"/>
@@ -9236,28 +9725,28 @@
         <v>34</v>
       </c>
       <c r="G120" s="32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H120" s="32" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="K120" s="20"/>
       <c r="L120" s="22" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="M120" s="22"/>
       <c r="N120" s="22"/>
       <c r="O120" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P120" s="32" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Q120" s="20"/>
       <c r="R120" s="2"/>
@@ -9271,42 +9760,45 @@
       <c r="V120" s="5">
         <v>162</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" ht="15" customHeight="1">
+      <c r="W120" s="32" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" ht="15" customHeight="1">
       <c r="A121" s="17" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C121" s="32" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D121" s="20"/>
       <c r="E121" s="20"/>
       <c r="F121" s="32" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="G121" s="32" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H121" s="32" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J121" s="23" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="K121" s="20"/>
       <c r="L121" s="22" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="M121" s="22"/>
       <c r="N121" s="22"/>
       <c r="O121" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P121" s="32" t="s">
         <v>27</v>
@@ -9315,51 +9807,54 @@
       <c r="R121" s="2"/>
       <c r="S121" s="20"/>
       <c r="T121" s="25" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="U121" s="2">
         <v>3</v>
       </c>
       <c r="V121" s="14"/>
-    </row>
-    <row r="122" spans="1:22" ht="15" customHeight="1">
+      <c r="W121" s="32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" ht="15" customHeight="1">
       <c r="A122" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C122" s="32" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D122" s="20"/>
       <c r="E122" s="20"/>
       <c r="F122" s="32" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G122" s="32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I122" s="32"/>
       <c r="J122" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K122" s="20" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="L122" s="22" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
       <c r="O122" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P122" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q122" s="20">
         <v>240</v>
@@ -9371,7 +9866,7 @@
         <v>1370</v>
       </c>
       <c r="T122" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U122" s="2">
         <v>3</v>
@@ -9379,42 +9874,45 @@
       <c r="V122" s="5">
         <v>129</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" ht="15" customHeight="1">
+      <c r="W122" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" ht="15" customHeight="1">
       <c r="A123" s="15" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="D123" s="20"/>
       <c r="E123" s="20"/>
       <c r="F123" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G123" s="32" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H123" s="32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I123" s="32" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="J123" s="23" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="22" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="19" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="P123" s="32" t="s">
         <v>27</v>
@@ -9423,7 +9921,7 @@
       <c r="R123" s="2"/>
       <c r="S123" s="20"/>
       <c r="T123" s="25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U123" s="2">
         <v>3</v>
@@ -9431,49 +9929,58 @@
       <c r="V123" s="5">
         <v>181</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" ht="15" customHeight="1">
+      <c r="W123" s="32" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" ht="15" customHeight="1">
       <c r="A124" s="15" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D124" s="20"/>
       <c r="E124" s="20"/>
       <c r="F124" s="32" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H124" s="32" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="I124" s="32"/>
       <c r="J124" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K124" s="20"/>
       <c r="L124" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="19" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="P124" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q124" s="20"/>
-      <c r="R124" s="2"/>
-      <c r="S124" s="20"/>
+        <v>27</v>
+      </c>
+      <c r="Q124" s="20">
+        <v>106</v>
+      </c>
+      <c r="R124" s="2">
+        <v>85</v>
+      </c>
+      <c r="S124" s="20">
+        <v>50</v>
+      </c>
       <c r="T124" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U124" s="2">
         <v>3</v>
@@ -9481,51 +9988,58 @@
       <c r="V124" s="5">
         <v>136</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" ht="15" customHeight="1">
+      <c r="W124" s="32" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" ht="15" customHeight="1">
       <c r="A125" s="15" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C125" s="32" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D125" s="20"/>
       <c r="E125" s="20"/>
       <c r="F125" s="32" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G125" s="32" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H125" s="32" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="I125" s="31" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="J125" s="23" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="K125" s="20"/>
       <c r="L125" s="22" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
       <c r="O125" s="19" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="P125" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q125" s="20"/>
-      <c r="R125" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="Q125" s="20">
+        <v>1000</v>
+      </c>
+      <c r="R125" s="2">
+        <v>500</v>
+      </c>
       <c r="S125" s="20"/>
       <c r="T125" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U125" s="4">
         <v>3</v>
@@ -9533,8 +10047,11 @@
       <c r="V125" s="5">
         <v>121</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" ht="15" customHeight="1">
+      <c r="W125" s="32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" ht="15" customHeight="1">
       <c r="A126" s="15"/>
       <c r="B126" s="33"/>
       <c r="C126" s="38"/>
@@ -9555,8 +10072,9 @@
       <c r="S126" s="21"/>
       <c r="T126" s="26"/>
       <c r="V126" s="14"/>
-    </row>
-    <row r="127" spans="1:22" ht="15" customHeight="1">
+      <c r="W126" s="38"/>
+    </row>
+    <row r="127" spans="1:23" ht="15" customHeight="1">
       <c r="A127" s="15"/>
       <c r="B127" s="33"/>
       <c r="C127" s="38"/>
@@ -9577,8 +10095,9 @@
       <c r="S127" s="21"/>
       <c r="T127" s="26"/>
       <c r="V127" s="14"/>
-    </row>
-    <row r="128" spans="1:22" ht="15" customHeight="1">
+      <c r="W127" s="38"/>
+    </row>
+    <row r="128" spans="1:23" ht="15" customHeight="1">
       <c r="A128" s="15"/>
       <c r="B128" s="33"/>
       <c r="C128" s="38"/>
@@ -9600,8 +10119,9 @@
       <c r="T128" s="25"/>
       <c r="U128" s="2"/>
       <c r="V128" s="14"/>
-    </row>
-    <row r="129" spans="1:22" ht="15" customHeight="1">
+      <c r="W128" s="38"/>
+    </row>
+    <row r="129" spans="1:23" ht="15" customHeight="1">
       <c r="A129" s="15"/>
       <c r="B129" s="33"/>
       <c r="C129" s="38"/>
@@ -9622,8 +10142,9 @@
       <c r="S129" s="21"/>
       <c r="T129" s="26"/>
       <c r="V129" s="14"/>
-    </row>
-    <row r="130" spans="1:22" ht="15" customHeight="1">
+      <c r="W129" s="38"/>
+    </row>
+    <row r="130" spans="1:23" ht="15" customHeight="1">
       <c r="A130" s="15"/>
       <c r="B130" s="33"/>
       <c r="C130" s="38"/>
@@ -9644,8 +10165,9 @@
       <c r="S130" s="21"/>
       <c r="T130" s="26"/>
       <c r="V130" s="14"/>
-    </row>
-    <row r="131" spans="1:22" ht="15" customHeight="1">
+      <c r="W130" s="38"/>
+    </row>
+    <row r="131" spans="1:23" ht="15" customHeight="1">
       <c r="A131" s="15"/>
       <c r="B131" s="33"/>
       <c r="C131" s="38"/>
@@ -9666,8 +10188,9 @@
       <c r="S131" s="21"/>
       <c r="T131" s="26"/>
       <c r="V131" s="14"/>
-    </row>
-    <row r="132" spans="1:22" ht="15" customHeight="1">
+      <c r="W131" s="38"/>
+    </row>
+    <row r="132" spans="1:23" ht="15" customHeight="1">
       <c r="A132" s="15"/>
       <c r="B132" s="33"/>
       <c r="C132" s="38"/>
@@ -9688,41 +10211,42 @@
       <c r="S132" s="21"/>
       <c r="T132" s="26"/>
       <c r="V132" s="14"/>
-    </row>
-    <row r="133" spans="1:22" ht="15" customHeight="1">
+      <c r="W132" s="38"/>
+    </row>
+    <row r="133" spans="1:23" ht="15" customHeight="1">
       <c r="V133" s="14"/>
     </row>
-    <row r="134" spans="1:22" ht="15" customHeight="1">
+    <row r="134" spans="1:23" ht="15" customHeight="1">
       <c r="V134" s="14"/>
     </row>
-    <row r="135" spans="1:22" ht="15" customHeight="1">
+    <row r="135" spans="1:23" ht="15" customHeight="1">
       <c r="V135" s="14"/>
     </row>
-    <row r="136" spans="1:22" ht="15" customHeight="1">
+    <row r="136" spans="1:23" ht="15" customHeight="1">
       <c r="V136" s="14"/>
     </row>
-    <row r="137" spans="1:22" ht="15" customHeight="1">
+    <row r="137" spans="1:23" ht="15" customHeight="1">
       <c r="V137" s="14"/>
     </row>
-    <row r="138" spans="1:22" ht="15" customHeight="1">
+    <row r="138" spans="1:23" ht="15" customHeight="1">
       <c r="V138" s="14"/>
     </row>
-    <row r="139" spans="1:22" ht="15" customHeight="1">
+    <row r="139" spans="1:23" ht="15" customHeight="1">
       <c r="V139" s="14"/>
     </row>
-    <row r="140" spans="1:22" ht="15" customHeight="1">
+    <row r="140" spans="1:23" ht="15" customHeight="1">
       <c r="V140" s="14"/>
     </row>
-    <row r="141" spans="1:22" ht="15" customHeight="1">
+    <row r="141" spans="1:23" ht="15" customHeight="1">
       <c r="V141" s="14"/>
     </row>
-    <row r="142" spans="1:22" ht="15" customHeight="1">
+    <row r="142" spans="1:23" ht="15" customHeight="1">
       <c r="V142" s="14"/>
     </row>
-    <row r="143" spans="1:22" ht="15" customHeight="1">
+    <row r="143" spans="1:23" ht="15" customHeight="1">
       <c r="V143" s="14"/>
     </row>
-    <row r="144" spans="1:22" ht="15" customHeight="1">
+    <row r="144" spans="1:23" ht="15" customHeight="1">
       <c r="V144" s="14"/>
     </row>
     <row r="145" spans="22:22" ht="15" customHeight="1">

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C51FCBE-3B61-475B-86CD-E767E9EF6949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECFD08F-61D6-41BC-9C32-8812F593E630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="729">
   <si>
     <t>Image</t>
   </si>
@@ -2211,6 +2211,15 @@
   </si>
   <si>
     <t>Néerladais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour l'ensemble eniron 600 </t>
+  </si>
+  <si>
+    <t>environ 300</t>
+  </si>
+  <si>
+    <t>Monument funéraire avec ronde-bosse</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2383,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2518,6 +2527,33 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{6AA84E56-6885-4D6A-8954-39C99888AB8D}"/>
@@ -2841,7 +2877,8 @@
     <col min="14" max="14" width="9" style="8" customWidth="1"/>
     <col min="15" max="15" width="46.85546875" style="1" customWidth="1"/>
     <col min="16" max="16" width="18.85546875" style="37" customWidth="1"/>
-    <col min="17" max="18" width="10" style="4" customWidth="1"/>
+    <col min="17" max="17" width="10" style="7" customWidth="1"/>
+    <col min="18" max="18" width="10" style="4" customWidth="1"/>
     <col min="19" max="19" width="7.7109375" style="4" customWidth="1"/>
     <col min="20" max="20" width="9.140625" style="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="4" customWidth="1"/>
@@ -2957,7 +2994,7 @@
       <c r="P2" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="7" t="s">
         <v>398</v>
       </c>
       <c r="R2" s="4">
@@ -3015,7 +3052,7 @@
       <c r="P3" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="Q3" s="35"/>
+      <c r="Q3" s="43"/>
       <c r="S3" s="35"/>
       <c r="T3" s="2" t="s">
         <v>28</v>
@@ -3069,7 +3106,7 @@
       <c r="P4" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="43">
         <v>286</v>
       </c>
       <c r="R4" s="4">
@@ -3130,7 +3167,7 @@
       <c r="P5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="Q5" s="35">
+      <c r="Q5" s="43">
         <v>78</v>
       </c>
       <c r="S5" s="35"/>
@@ -3186,7 +3223,7 @@
       <c r="P6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="43">
         <v>280</v>
       </c>
       <c r="S6" s="35"/>
@@ -3358,7 +3395,7 @@
       <c r="P9" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="Q9" s="35"/>
+      <c r="Q9" s="43"/>
       <c r="S9" s="35"/>
       <c r="T9" s="2" t="s">
         <v>50</v>
@@ -3412,7 +3449,7 @@
       <c r="P10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q10" s="35">
+      <c r="Q10" s="43">
         <v>700</v>
       </c>
       <c r="R10" s="4">
@@ -3532,7 +3569,7 @@
       <c r="P12" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="7" t="s">
         <v>390</v>
       </c>
       <c r="T12" s="2" t="s">
@@ -3589,7 +3626,7 @@
       <c r="P13" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="7" t="s">
         <v>388</v>
       </c>
       <c r="T13" s="2" t="s">
@@ -3646,7 +3683,7 @@
       <c r="P14" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="7" t="s">
         <v>386</v>
       </c>
       <c r="R14" s="4">
@@ -3706,7 +3743,7 @@
       <c r="P15" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="7" t="s">
         <v>392</v>
       </c>
       <c r="R15" s="4">
@@ -3769,7 +3806,7 @@
       <c r="P16" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="Q16" s="7" t="s">
         <v>394</v>
       </c>
       <c r="T16" s="2" t="s">
@@ -3826,7 +3863,7 @@
       <c r="P17" s="37" t="s">
         <v>396</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="Q17" s="7" t="s">
         <v>397</v>
       </c>
       <c r="T17" s="2" t="s">
@@ -3883,7 +3920,7 @@
       <c r="P18" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="Q18" s="35">
+      <c r="Q18" s="43">
         <v>470</v>
       </c>
       <c r="S18" s="35"/>
@@ -3941,7 +3978,7 @@
       <c r="P19" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q19" s="35">
+      <c r="Q19" s="43">
         <v>105</v>
       </c>
       <c r="R19" s="4">
@@ -4006,7 +4043,7 @@
       <c r="P20" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="Q20" s="35">
+      <c r="Q20" s="43">
         <v>900</v>
       </c>
       <c r="S20" s="35"/>
@@ -4064,7 +4101,7 @@
       <c r="P21" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="Q21" s="35">
+      <c r="Q21" s="43">
         <v>700</v>
       </c>
       <c r="S21" s="35"/>
@@ -4122,7 +4159,7 @@
       <c r="P22" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="43">
         <v>1269</v>
       </c>
       <c r="S22" s="35"/>
@@ -4180,7 +4217,7 @@
       <c r="P23" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="43">
         <v>78</v>
       </c>
       <c r="S23" s="35"/>
@@ -4238,7 +4275,7 @@
       <c r="P24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="43">
         <v>280</v>
       </c>
       <c r="S24" s="35"/>
@@ -4298,7 +4335,7 @@
       <c r="P25" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="43">
         <v>188</v>
       </c>
       <c r="R25" s="4">
@@ -4361,7 +4398,7 @@
       <c r="P26" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="43">
         <v>1677</v>
       </c>
       <c r="R26" s="4">
@@ -4424,7 +4461,7 @@
       <c r="P27" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="43">
         <v>330</v>
       </c>
       <c r="R27" s="4">
@@ -4487,7 +4524,7 @@
       <c r="P28" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="43">
         <v>330</v>
       </c>
       <c r="R28" s="4">
@@ -4550,7 +4587,7 @@
       <c r="P29" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q29" s="43">
         <v>72</v>
       </c>
       <c r="R29" s="4">
@@ -4613,7 +4650,7 @@
       <c r="P30" s="29" t="s">
         <v>439</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="43">
         <v>200</v>
       </c>
       <c r="R30" s="4">
@@ -4674,7 +4711,7 @@
       <c r="P31" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="43">
         <v>182</v>
       </c>
       <c r="S31" s="35"/>
@@ -4732,7 +4769,7 @@
       <c r="P32" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="43">
         <v>83</v>
       </c>
       <c r="R32" s="4">
@@ -4795,7 +4832,7 @@
       <c r="P33" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="43">
         <v>106</v>
       </c>
       <c r="R33" s="4">
@@ -4817,61 +4854,64 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="15" customHeight="1">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:23" s="68" customFormat="1" ht="15" customHeight="1">
+      <c r="A34" s="59" t="s">
         <v>485</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="29" t="s">
+      <c r="E34" s="63"/>
+      <c r="F34" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="H34" s="29" t="s">
+      <c r="H34" s="60" t="s">
         <v>486</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="64" t="s">
         <v>422</v>
       </c>
-      <c r="K34" s="39"/>
-      <c r="L34" s="54" t="s">
+      <c r="K34" s="65"/>
+      <c r="L34" s="66" t="s">
         <v>487</v>
       </c>
-      <c r="M34" s="19"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="19" t="s">
-        <v>714</v>
-      </c>
-      <c r="P34" s="29" t="s">
+      <c r="M34" s="63"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="63" t="s">
+        <v>728</v>
+      </c>
+      <c r="P34" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="Q34" s="35">
-        <v>600</v>
-      </c>
-      <c r="S34" s="35"/>
-      <c r="T34" s="2" t="s">
+      <c r="Q34" s="69" t="s">
+        <v>726</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="S34" s="67"/>
+      <c r="T34" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="U34" s="4">
+      <c r="U34" s="5">
         <v>1</v>
       </c>
       <c r="V34" s="5">
         <v>24</v>
       </c>
-      <c r="W34" s="41" t="s">
+      <c r="W34" s="61" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4916,7 +4956,7 @@
       <c r="P35" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="43">
         <v>103</v>
       </c>
       <c r="S35" s="35"/>
@@ -4974,7 +5014,7 @@
       <c r="P36" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="43">
         <v>132.4</v>
       </c>
       <c r="R36" s="4">
@@ -5037,7 +5077,7 @@
       <c r="P37" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="Q37" s="35">
+      <c r="Q37" s="43">
         <v>150</v>
       </c>
       <c r="R37" s="4">
@@ -5096,7 +5136,7 @@
       <c r="P38" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="43">
         <v>450</v>
       </c>
       <c r="S38" s="35"/>
@@ -5388,7 +5428,7 @@
       <c r="P43" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q43" s="35">
+      <c r="Q43" s="43">
         <v>240</v>
       </c>
       <c r="S43" s="35"/>
@@ -5507,7 +5547,7 @@
       <c r="P45" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q45" s="4" t="s">
+      <c r="Q45" s="7" t="s">
         <v>407</v>
       </c>
       <c r="R45" s="4" t="s">
@@ -5568,7 +5608,7 @@
       <c r="P46" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q46" s="4" t="s">
+      <c r="Q46" s="7" t="s">
         <v>407</v>
       </c>
       <c r="R46" s="4" t="s">
@@ -5626,7 +5666,7 @@
       <c r="P47" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q47" s="4">
+      <c r="Q47" s="7">
         <v>233</v>
       </c>
       <c r="R47" s="4">
@@ -5678,7 +5718,7 @@
       <c r="P48" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="4">
+      <c r="Q48" s="7">
         <v>104</v>
       </c>
       <c r="R48" s="4">
@@ -5738,7 +5778,7 @@
       <c r="P49" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="Q49" s="4" t="s">
+      <c r="Q49" s="7" t="s">
         <v>414</v>
       </c>
       <c r="R49" s="4">
@@ -5797,7 +5837,7 @@
       <c r="P50" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="43">
         <v>390</v>
       </c>
       <c r="R50" s="4">
@@ -5858,7 +5898,7 @@
       <c r="P51" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="43">
         <v>400</v>
       </c>
       <c r="S51" s="35"/>
@@ -5914,7 +5954,7 @@
       <c r="P52" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q52" s="35">
+      <c r="Q52" s="43">
         <v>62</v>
       </c>
       <c r="R52" s="4">
@@ -5975,7 +6015,7 @@
       <c r="P53" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="43">
         <v>60</v>
       </c>
       <c r="R53" s="4">
@@ -6091,7 +6131,7 @@
       <c r="P55" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="Q55" s="36">
+      <c r="Q55" s="44">
         <v>223</v>
       </c>
       <c r="R55" s="4">
@@ -6150,7 +6190,7 @@
       <c r="P56" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q56" s="36">
+      <c r="Q56" s="44">
         <v>130</v>
       </c>
       <c r="R56" s="4">
@@ -6272,7 +6312,7 @@
       <c r="P58" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Q58" s="36">
+      <c r="Q58" s="44">
         <v>65</v>
       </c>
       <c r="R58" s="4">
@@ -6333,7 +6373,7 @@
       <c r="P59" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="Q59" s="36"/>
+      <c r="Q59" s="44"/>
       <c r="S59" s="36"/>
       <c r="T59" s="25" t="s">
         <v>37</v>
@@ -6387,7 +6427,7 @@
       <c r="P60" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Q60" s="36">
+      <c r="Q60" s="44">
         <v>83</v>
       </c>
       <c r="S60" s="36"/>
@@ -6561,7 +6601,7 @@
       <c r="P63" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="Q63" s="36">
+      <c r="Q63" s="44">
         <v>220</v>
       </c>
       <c r="R63" s="4">
@@ -6677,7 +6717,7 @@
       <c r="P65" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q65" s="21">
+      <c r="Q65" s="23">
         <v>468</v>
       </c>
       <c r="S65" s="21"/>
@@ -6733,7 +6773,7 @@
       <c r="P66" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q66" s="36">
+      <c r="Q66" s="44">
         <v>175</v>
       </c>
       <c r="R66" s="4">
@@ -6790,7 +6830,7 @@
       <c r="P67" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="Q67" s="36">
+      <c r="Q67" s="44">
         <v>61</v>
       </c>
       <c r="S67" s="36"/>
@@ -6846,7 +6886,7 @@
       <c r="P68" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="Q68" s="35">
+      <c r="Q68" s="43">
         <v>750</v>
       </c>
       <c r="S68" s="35"/>
@@ -6904,7 +6944,7 @@
       <c r="P69" s="31" t="s">
         <v>443</v>
       </c>
-      <c r="Q69" s="36">
+      <c r="Q69" s="44">
         <v>550</v>
       </c>
       <c r="S69" s="36"/>
@@ -6960,7 +7000,7 @@
       <c r="P70" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q70" s="36">
+      <c r="Q70" s="44">
         <v>290</v>
       </c>
       <c r="S70" s="36"/>
@@ -7124,7 +7164,7 @@
       <c r="P73" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q73" s="36">
+      <c r="Q73" s="44">
         <v>1500</v>
       </c>
       <c r="S73" s="36"/>
@@ -7243,7 +7283,7 @@
       <c r="P75" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Q75" s="36">
+      <c r="Q75" s="44">
         <v>175</v>
       </c>
       <c r="R75" s="4">
@@ -7304,7 +7344,7 @@
       <c r="P76" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Q76" s="36">
+      <c r="Q76" s="44">
         <v>40</v>
       </c>
       <c r="R76" s="4">
@@ -7363,7 +7403,7 @@
       <c r="P77" s="31" t="s">
         <v>520</v>
       </c>
-      <c r="Q77" s="36"/>
+      <c r="Q77" s="44"/>
       <c r="S77" s="36"/>
       <c r="T77" s="25" t="s">
         <v>28</v>
@@ -7417,7 +7457,7 @@
       <c r="P78" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q78" s="36">
+      <c r="Q78" s="44">
         <v>310</v>
       </c>
       <c r="S78" s="36"/>
@@ -7528,7 +7568,7 @@
       <c r="P80" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q80" s="36">
+      <c r="Q80" s="44">
         <v>87</v>
       </c>
       <c r="S80" s="36"/>
@@ -7586,7 +7626,7 @@
       <c r="P81" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q81" s="36">
+      <c r="Q81" s="44">
         <v>400</v>
       </c>
       <c r="S81" s="36"/>
@@ -7642,7 +7682,7 @@
       <c r="P82" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="Q82" s="36"/>
+      <c r="Q82" s="44"/>
       <c r="S82" s="36"/>
       <c r="T82" s="12" t="s">
         <v>725</v>
@@ -7694,7 +7734,7 @@
       <c r="P83" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q83" s="21" t="s">
+      <c r="Q83" s="23" t="s">
         <v>409</v>
       </c>
       <c r="S83" s="21"/>
@@ -7811,7 +7851,7 @@
       <c r="P85" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q85" s="36">
+      <c r="Q85" s="44">
         <v>287.5</v>
       </c>
       <c r="R85" s="4">
@@ -7870,7 +7910,7 @@
       <c r="P86" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q86" s="36"/>
+      <c r="Q86" s="44"/>
       <c r="S86" s="36"/>
       <c r="T86" s="25" t="s">
         <v>50</v>
@@ -7924,7 +7964,7 @@
       <c r="P87" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Q87" s="36">
+      <c r="Q87" s="44">
         <v>228</v>
       </c>
       <c r="R87" s="4">
@@ -8042,7 +8082,7 @@
       <c r="P89" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q89" s="36"/>
+      <c r="Q89" s="44"/>
       <c r="S89" s="36"/>
       <c r="T89" s="25" t="s">
         <v>28</v>
@@ -8206,7 +8246,7 @@
       <c r="P92" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q92" s="36"/>
+      <c r="Q92" s="44"/>
       <c r="S92" s="36"/>
       <c r="T92" s="12" t="s">
         <v>218</v>
@@ -8313,7 +8353,7 @@
       <c r="P94" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="Q94" s="36"/>
+      <c r="Q94" s="44"/>
       <c r="S94" s="36"/>
       <c r="T94" s="25" t="s">
         <v>50</v>
@@ -8420,7 +8460,7 @@
       <c r="P96" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q96" s="36"/>
+      <c r="Q96" s="44"/>
       <c r="S96" s="36"/>
       <c r="T96" s="25" t="s">
         <v>50</v>
@@ -8531,7 +8571,7 @@
       <c r="P98" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="Q98" s="36">
+      <c r="Q98" s="44">
         <v>350</v>
       </c>
       <c r="S98" s="36"/>
@@ -8693,7 +8733,7 @@
       <c r="P101" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q101" s="21" t="s">
+      <c r="Q101" s="23" t="s">
         <v>418</v>
       </c>
       <c r="S101" s="21"/>
@@ -8749,7 +8789,7 @@
       <c r="P102" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q102" s="36">
+      <c r="Q102" s="44">
         <v>500</v>
       </c>
       <c r="S102" s="36"/>
@@ -8805,7 +8845,7 @@
       <c r="P103" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Q103" s="36">
+      <c r="Q103" s="44">
         <v>50</v>
       </c>
       <c r="S103" s="36"/>
@@ -9021,7 +9061,7 @@
       <c r="P107" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q107" s="21" t="s">
+      <c r="Q107" s="23" t="s">
         <v>401</v>
       </c>
       <c r="R107" s="4" t="s">
@@ -9082,7 +9122,7 @@
       <c r="P108" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="Q108" s="21">
+      <c r="Q108" s="23">
         <v>320</v>
       </c>
       <c r="R108" s="4">
@@ -9143,7 +9183,7 @@
       <c r="P109" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="Q109" s="36"/>
+      <c r="Q109" s="44"/>
       <c r="S109" s="36"/>
       <c r="T109" s="25" t="s">
         <v>50</v>
@@ -9197,7 +9237,7 @@
       <c r="P110" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q110" s="36">
+      <c r="Q110" s="44">
         <v>332</v>
       </c>
       <c r="R110" s="4">
@@ -9258,7 +9298,7 @@
       <c r="P111" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Q111" s="36">
+      <c r="Q111" s="44">
         <v>66</v>
       </c>
       <c r="S111" s="36"/>
@@ -10068,7 +10108,7 @@
       <c r="N126" s="24"/>
       <c r="O126" s="15"/>
       <c r="P126" s="38"/>
-      <c r="Q126" s="21"/>
+      <c r="Q126" s="23"/>
       <c r="S126" s="21"/>
       <c r="T126" s="26"/>
       <c r="V126" s="14"/>
@@ -10091,7 +10131,7 @@
       <c r="N127" s="24"/>
       <c r="O127" s="15"/>
       <c r="P127" s="38"/>
-      <c r="Q127" s="21"/>
+      <c r="Q127" s="23"/>
       <c r="S127" s="21"/>
       <c r="T127" s="26"/>
       <c r="V127" s="14"/>
@@ -10114,7 +10154,7 @@
       <c r="N128" s="23"/>
       <c r="O128" s="21"/>
       <c r="P128" s="38"/>
-      <c r="Q128" s="21"/>
+      <c r="Q128" s="23"/>
       <c r="S128" s="21"/>
       <c r="T128" s="25"/>
       <c r="U128" s="2"/>
@@ -10138,7 +10178,7 @@
       <c r="N129" s="24"/>
       <c r="O129" s="15"/>
       <c r="P129" s="38"/>
-      <c r="Q129" s="21"/>
+      <c r="Q129" s="23"/>
       <c r="S129" s="21"/>
       <c r="T129" s="26"/>
       <c r="V129" s="14"/>
@@ -10161,7 +10201,7 @@
       <c r="N130" s="24"/>
       <c r="O130" s="15"/>
       <c r="P130" s="38"/>
-      <c r="Q130" s="21"/>
+      <c r="Q130" s="23"/>
       <c r="S130" s="21"/>
       <c r="T130" s="26"/>
       <c r="V130" s="14"/>
@@ -10184,7 +10224,7 @@
       <c r="N131" s="24"/>
       <c r="O131" s="15"/>
       <c r="P131" s="38"/>
-      <c r="Q131" s="21"/>
+      <c r="Q131" s="23"/>
       <c r="S131" s="21"/>
       <c r="T131" s="26"/>
       <c r="V131" s="14"/>
@@ -10207,7 +10247,7 @@
       <c r="N132" s="24"/>
       <c r="O132" s="15"/>
       <c r="P132" s="38"/>
-      <c r="Q132" s="21"/>
+      <c r="Q132" s="23"/>
       <c r="S132" s="21"/>
       <c r="T132" s="26"/>
       <c r="V132" s="14"/>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECFD08F-61D6-41BC-9C32-8812F593E630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DD6668-C1D9-4862-94B1-D307BB9B6146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2213,13 +2213,13 @@
     <t>Néerladais</t>
   </si>
   <si>
-    <t xml:space="preserve">Pour l'ensemble eniron 600 </t>
-  </si>
-  <si>
-    <t>environ 300</t>
-  </si>
-  <si>
     <t>Monument funéraire avec ronde-bosse</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 600 (environ et  pour l'ensemble)</t>
+  </si>
+  <si>
+    <t>300 (environ)</t>
   </si>
 </sst>
 </file>
@@ -4890,16 +4890,16 @@
       <c r="M34" s="63"/>
       <c r="N34" s="65"/>
       <c r="O34" s="63" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="P34" s="60" t="s">
         <v>27</v>
       </c>
       <c r="Q34" s="69" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="S34" s="67"/>
       <c r="T34" s="62" t="s">

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DD6668-C1D9-4862-94B1-D307BB9B6146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F33D7F-1CF2-41B9-B559-72C8FD605590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2216,10 +2216,10 @@
     <t>Monument funéraire avec ronde-bosse</t>
   </si>
   <si>
-    <t xml:space="preserve"> 600 (environ et  pour l'ensemble)</t>
-  </si>
-  <si>
-    <t>300 (environ)</t>
+    <t xml:space="preserve"> 600 cm (environ et  pour l'ensemble)</t>
+  </si>
+  <si>
+    <t>300 cm (environ)</t>
   </si>
 </sst>
 </file>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -957,7 +957,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>c.1604</t>
+          <t>environ 1604</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>c.1636</t>
+          <t>environ 1636</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>c.1670-1690</t>
+          <t>environ 1670-1690</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>c.1576</t>
+          <t>environ 1576</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>c.1570</t>
+          <t>environ 1570</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>c.1616-1620</t>
+          <t>environ 1616-1620</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>c.1576</t>
+          <t>environ 1576</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>c.1601</t>
+          <t>environ 1601</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>c.1570</t>
+          <t>environ 1570</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>c.1583</t>
+          <t>environ 1583</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -874,12 +874,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/P1000460_Paris_Ier_Eglise_Saint-Roch_Nativit%C3%A9_Val-de-Grace_reductwk.JPG/1280px-P1000460_Paris_Ier_Eglise_Saint-Roch_Nativit%C3%A9_Val-de-Grace_reductwk.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f8/Monument_fun%C3%A9raire_de_Jacques_Auguste_de_Thou_%28Louvre%2C_N_15270%29_1.jpg/1280px-Monument_fun%C3%A9raire_de_Jacques_Auguste_de_Thou_%28Louvre%2C_N_15270%29_1.jpg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Michel</t>
+          <t>François</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,17 +889,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>environ 1604</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1644-1645</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Église Saint-Roch</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"La Nativité "</t>
+          <t>"Monument funéraire de Jacques-Auguste de Thou"</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -928,7 +928,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>160</v>
+        <v>146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>126</v>
+      </c>
+      <c r="S7" t="n">
+        <v>63</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -942,7 +948,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f8/Monument_fun%C3%A9raire_de_Jacques_Auguste_de_Thou_%28Louvre%2C_N_15270%29_1.jpg/1280px-Monument_fun%C3%A9raire_de_Jacques_Auguste_de_Thou_%28Louvre%2C_N_15270%29_1.jpg</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -957,7 +963,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>environ 1604</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -967,7 +973,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1644-1645</t>
+          <t>1642-1663</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -982,7 +988,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"Monument funéraire de Jacques-Auguste de Thou"</t>
+          <t>Tombeau du duc de Longueville</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -996,13 +1002,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>146</v>
+        <v>700</v>
       </c>
       <c r="R8" t="n">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="S8" t="n">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1016,7 +1022,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/P1000460_Paris_Ier_Eglise_Saint-Roch_Nativit%C3%A9_Val-de-Grace_reductwk.JPG/1280px-P1000460_Paris_Ier_Eglise_Saint-Roch_Nativit%C3%A9_Val-de-Grace_reductwk.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1039,8 +1045,10 @@
           <t>1686</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>1650</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1665</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1049,23 +1057,26 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Porte Saint-Denis </t>
+          <t>Église Saint-Roch</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haut-Reliefs </t>
+          <t>"La Nativité "</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pierre</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>160</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1079,12 +1090,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg/960px-Monument_du_coeur_du_duc_Henri_Ier_de_Longueville_%28Louvre%2C_MR_3099%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg/1280px-Porte_Saint_Denis_-_Paris_X_%28FR75%29_-_2023-06-14_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Michel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1094,18 +1105,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1669</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1642-1663</t>
-        </is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1650</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1114,32 +1123,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t xml:space="preserve">Porte Saint-Denis </t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Tombeau du duc de Longueville</t>
+          <t xml:space="preserve">Haut-Reliefs </t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>700</v>
-      </c>
-      <c r="R10" t="n">
-        <v>202</v>
-      </c>
-      <c r="S10" t="n">
-        <v>124</v>
+          <t>Pierre</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0c/Napoli_s_Martino_Pietro_Bernini_Carit%C3%A0_di_s_Martino_1050007.JPG/960px-Napoli_s_Martino_Pietro_Bernini_Carit%C3%A0_di_s_Martino_1050007.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Apollo_and_Daphne_by_Bernini_-_Galleria_Borghese_-_Rome%2C_Italy_-_DSC04587.jpg/1280px-Apollo_and_Daphne_by_Bernini_-_Galleria_Borghese_-_Rome%2C_Italy_-_DSC04587.jpg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Gian Lorenzo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1173,37 +1173,37 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1585-1587</t>
+          <t>1622-1625</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Certosa di San Martino</t>
+          <t>Galleria Borghese</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>"Saint Martin et le mendiant"</t>
+          <t>Apollon et Daphné</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1211,8 +1211,10 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q11" t="n">
-        <v>138</v>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1226,7 +1228,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/36/Apollo_and_Daphne_by_Bernini_-_Galleria_Borghese_-_Rome%2C_Italy_-_DSC04587.jpg/1280px-Apollo_and_Daphne_by_Bernini_-_Galleria_Borghese_-_Rome%2C_Italy_-_DSC04587.jpg</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Bernini%27s_David_02.jpg/960px-Bernini%27s_David_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1256,7 +1258,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1622-1625</t>
+          <t>1623-1624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1271,7 +1273,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Apollon et Daphné</t>
+          <t>David</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1286,7 +1288,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1301,7 +1303,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Bernini%27s_David_02.jpg/960px-Bernini%27s_David_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/The_Rape_of_Proserpina_%28Rome%29.jpg/960px-The_Rape_of_Proserpina_%28Rome%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1331,7 +1333,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1623-1624</t>
+          <t>1622-1625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1346,7 +1348,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Le Rapt de Proserpine</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1361,8 +1363,11 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>170</t>
-        </is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>109</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1376,7 +1381,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/The_Rape_of_Proserpina_%28Rome%29.jpg/960px-The_Rape_of_Proserpina_%28Rome%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1406,7 +1411,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1622-1625</t>
+          <t>1647-1652</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1416,12 +1421,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Galleria Borghese</t>
+          <t>Santa Maria della Vittoria</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Le Rapt de Proserpine</t>
+          <t>L'Extase de sainte Thérèse</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1436,11 +1441,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>350</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>109</v>
+        <v>279</v>
+      </c>
+      <c r="S14" t="n">
+        <v>206</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1454,7 +1462,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baldaquin_Bernin_Saint-Pierre_Vatican.jpg/960px-Baldaquin_Bernin_Saint-Pierre_Vatican.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1484,7 +1492,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1647-1652</t>
+          <t>1624-1633</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1494,34 +1502,28 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Santa Maria della Vittoria</t>
+          <t>Basilique Saint-Pierre</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>L'Extase de sainte Thérèse</t>
+          <t>Baldaquin</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element architectural liturgique</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>279</v>
-      </c>
-      <c r="S15" t="n">
-        <v>206</v>
+          <t>2900</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1535,7 +1537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baldaquin_Bernin_Saint-Pierre_Vatican.jpg/960px-Baldaquin_Bernin_Saint-Pierre_Vatican.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1565,7 +1567,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1624-1633</t>
+          <t>1648-1651</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1575,27 +1577,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Basilique Saint-Pierre</t>
+          <t>Piazza Navona</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Baldaquin</t>
+          <t>Fontaine des Quatre-Fleuves</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Element architectural liturgique</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre et Travertin</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1610,7 +1612,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bernini%2C_fontana_del_tritone_by_night.JPG/960px-Bernini%2C_fontana_del_tritone_by_night.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1640,7 +1642,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1648-1651</t>
+          <t>1642-1643</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1650,12 +1652,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Piazza Navona</t>
+          <t>Piazza Barberini</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Fontaine des Quatre-Fleuves</t>
+          <t>Fontaine du Triton</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1665,13 +1667,11 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Marbre et Travertin</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
+          <t>Travertin</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bernini%2C_fontana_del_tritone_by_night.JPG/960px-Bernini%2C_fontana_del_tritone_by_night.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/2/29/Busto_luigi_xiv.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1715,36 +1715,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1642-1643</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Piazza Barberini</t>
+          <t>Château de Versailles</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Fontaine du Triton</t>
+          <t>Buste de Louis XIV</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Travertin</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470</v>
+        <v>105</v>
+      </c>
+      <c r="R18" t="n">
+        <v>99</v>
+      </c>
+      <c r="S18" t="n">
+        <v>46</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1758,7 +1764,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/2/29/Busto_luigi_xiv.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/00120_Vatican_City_-_panoramio_%2842%29.jpg/960px-00120_Vatican_City_-_panoramio_%2842%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1788,42 +1794,41 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1657-1666</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Château de Versailles</t>
+          <t>Basilique Saint-Pierre</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Buste de Louis XIV</t>
+          <t>Chaire</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Cathedra Petri</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element architectural liturgique</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze, stuc, marbre</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>105</v>
-      </c>
-      <c r="R19" t="n">
-        <v>99</v>
-      </c>
-      <c r="S19" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1837,7 +1842,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/00120_Vatican_City_-_panoramio_%2842%29.jpg/960px-00120_Vatican_City_-_panoramio_%2842%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d1/0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg/960px-0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1867,7 +1872,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1657-1666</t>
+          <t>1671-1678</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1882,26 +1887,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Chaire</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Cathedra Petri</t>
+          <t>Tombeau du pape Alexandre VII</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Element architectural liturgique</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bronze, stuc, marbre</t>
+          <t>Marbre, bronze</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d1/0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg/960px-0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a3/Elephant_and_Obelisk_-_Bernini.jpg/960px-Elephant_and_Obelisk_-_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1671-1678</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1955,26 +1955,26 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Basilique Saint-Pierre</t>
+          <t>Piazza della Minerva</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Tombeau du pape Alexandre VII</t>
+          <t>L'Éléphant à l'obélisque</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marbre, bronze</t>
+          <t>Marbre, pierre</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700</v>
+        <v>1269</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a3/Elephant_and_Obelisk_-_Bernini.jpg/960px-Elephant_and_Obelisk_-_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Gian_lorenzo_bernini%2C_ritratto_del_cardinale_scipione_borghese%2C_1632_ca%2C_CCLXV_01.JPG/960px-Gian_lorenzo_bernini%2C_ritratto_del_cardinale_scipione_borghese%2C_1632_ca%2C_CCLXV_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2028,26 +2028,26 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Piazza della Minerva</t>
+          <t>Galleria Borghese</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>L'Éléphant à l'obélisque</t>
+          <t>Buste de Scipione Borghese</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marbre, pierre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1269</v>
+        <v>78</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Gian_lorenzo_bernini%2C_ritratto_del_cardinale_scipione_borghese%2C_1632_ca%2C_CCLXV_01.JPG/960px-Gian_lorenzo_bernini%2C_ritratto_del_cardinale_scipione_borghese%2C_1632_ca%2C_CCLXV_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/Museo_borghese%2C_sala_del_gladiatore%2C_g.l._bernini%2C_verit%C3%A0_svelata%2C_1645-52%2C_02.JPG/960px-Museo_borghese%2C_sala_del_gladiatore%2C_g.l._bernini%2C_verit%C3%A0_svelata%2C_1645-52%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1645-1652</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Buste de Scipione Borghese</t>
+          <t>La Vérité dévoilée par le Temps</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/Museo_borghese%2C_sala_del_gladiatore%2C_g.l._bernini%2C_verit%C3%A0_svelata%2C_1645-52%2C_02.JPG/960px-Museo_borghese%2C_sala_del_gladiatore%2C_g.l._bernini%2C_verit%C3%A0_svelata%2C_1645-52%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Giovanni_Lorenzo_Bernini-Blessed_Ludovica_Albertoni-Basilica_of_San_Francesco_a_Ripa.jpg/1280px-Giovanni_Lorenzo_Bernini-Blessed_Ludovica_Albertoni-Basilica_of_San_Francesco_a_Ripa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1645-1652</t>
+          <t>1671-1674</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2174,12 +2174,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Galleria Borghese</t>
+          <t>San Francesco a Ripa</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Chapelle Altieri</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>La Vérité dévoilée par le Temps</t>
+          <t>La Bienheureuse Ludovica Albertoni</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2193,7 +2198,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>280</v>
+        <v>188</v>
+      </c>
+      <c r="R24" t="n">
+        <v>210</v>
+      </c>
+      <c r="S24" t="n">
+        <v>90</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2207,7 +2218,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Giovanni_Lorenzo_Bernini-Blessed_Ludovica_Albertoni-Basilica_of_San_Francesco_a_Ripa.jpg/1280px-Giovanni_Lorenzo_Bernini-Blessed_Ludovica_Albertoni-Basilica_of_San_Francesco_a_Ripa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Arches_at_the_vatican_%285200698505%29.jpg/1280px-Arches_at_the_vatican_%285200698505%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2237,7 +2248,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1671-1674</t>
+          <t>1656-1667</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2247,37 +2258,32 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>San Francesco a Ripa</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Chapelle Altieri</t>
+          <t>Basilique Saint-Pierre</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>La Bienheureuse Ludovica Albertoni</t>
+          <t xml:space="preserve">Colonnade </t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element architectural</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Travertin</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>188</v>
+        <v>1677</v>
       </c>
       <c r="R25" t="n">
-        <v>210</v>
+        <v>2400</v>
       </c>
       <c r="S25" t="n">
-        <v>90</v>
+        <v>3400</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2291,7 +2297,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Arches_at_the_vatican_%285200698505%29.jpg/1280px-Arches_at_the_vatican_%285200698505%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Angel_with_the_Crown_of_Thorns_by_Bernini.jpg/960px-Angel_with_the_Crown_of_Thorns_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2321,7 +2327,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1656-1667</t>
+          <t>1668-1669</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2331,32 +2337,32 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Basilique Saint-Pierre</t>
+          <t>Basilique San Andrea delle Fratte</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colonnade </t>
+          <t>Ange à la couronne d'épines</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Element architectural</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Travertin</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>1677</v>
+        <v>330</v>
       </c>
       <c r="R26" t="n">
-        <v>2400</v>
+        <v>175</v>
       </c>
       <c r="S26" t="n">
-        <v>3400</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2370,7 +2376,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Angel_with_the_Crown_of_Thorns_by_Bernini.jpg/960px-Angel_with_the_Crown_of_Thorns_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Angel_with_the_Superscription_by_Bernini.jpg/960px-Angel_with_the_Superscription_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2415,7 +2421,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ange à la couronne d'épines</t>
+          <t xml:space="preserve">Ange au cartouche </t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2449,7 +2455,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Angel_with_the_Superscription_by_Bernini.jpg/960px-Angel_with_the_Superscription_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg/960px-Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2479,22 +2485,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1668-1669</t>
+          <t>1636-1638</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Basilique San Andrea delle Fratte</t>
+          <t>Musée du Bargello</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ange au cartouche </t>
+          <t>Buste de Costanza Bonarelli</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2508,13 +2514,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>330</v>
+        <v>72</v>
       </c>
       <c r="R28" t="n">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2528,7 +2534,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg/960px-Gianlorenzo_bernini%2C_ritratto_di_costanza_bonarelli%2C_1637-38%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/14_514_Piazza_Navona%2C_Fontana_del_Moro.jpg/1280px-14_514_Piazza_Navona%2C_Fontana_del_Moro.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2558,42 +2564,39 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1636-1638</t>
+          <t>1653-1655</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Musée du Bargello</t>
+          <t>Piazza Navona</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Buste de Costanza Bonarelli</t>
+          <t>Fontaine du Maure</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Travertin, marbre</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="R29" t="n">
-        <v>54</v>
-      </c>
-      <c r="S29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2607,7 +2610,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0f/14_514_Piazza_Navona%2C_Fontana_del_Moro.jpg/1280px-14_514_Piazza_Navona%2C_Fontana_del_Moro.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Giovanni_Lorenzo_Bernini-Neptune_and_Triton-Victoria_and_Albert_Museum.jpg/960px-Giovanni_Lorenzo_Bernini-Neptune_and_Triton-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2637,39 +2640,36 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1653-1655</t>
+          <t>1622-1623</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Piazza Navona</t>
+          <t>Victoria and Albert Museum</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Fontaine du Maure</t>
+          <t>Neptune et Triton</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Travertin, marbre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>200</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1000</v>
+        <v>182</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Giovanni_Lorenzo_Bernini-Neptune_and_Triton-Victoria_and_Albert_Museum.jpg/960px-Giovanni_Lorenzo_Bernini-Neptune_and_Triton-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Gian_lorenzo_bernini%2C_ritratto_del_cardinale_richelieu%2C_1641.JPG/960px-Gian_lorenzo_bernini%2C_ritratto_del_cardinale_richelieu%2C_1641.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2713,22 +2713,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1622-1623</t>
+          <t>1640-1641</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Victoria and Albert Museum</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Neptune et Triton</t>
+          <t>Buste du cardinal de Richelieu</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2742,7 +2742,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>182</v>
+        <v>83</v>
+      </c>
+      <c r="R31" t="n">
+        <v>70</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2756,7 +2762,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Gian_lorenzo_bernini%2C_ritratto_del_cardinale_richelieu%2C_1641.JPG/960px-Gian_lorenzo_bernini%2C_ritratto_del_cardinale_richelieu%2C_1641.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Gian_Lorenzo_Bernini%2C_busto_di_Francesco_I_d%27Este%2C_1650-51%2C_02.jpg/960px-Gian_Lorenzo_Bernini%2C_busto_di_Francesco_I_d%27Este%2C_1650-51%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2786,22 +2792,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1640-1641</t>
+          <t>1650-1651</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t xml:space="preserve">Modène </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Galleria Estense</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Buste du cardinal de Richelieu</t>
+          <t>Buste de Francesco Ier d'Este</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2815,13 +2821,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="R32" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="S32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2835,7 +2841,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Gian_Lorenzo_Bernini%2C_busto_di_Francesco_I_d%27Este%2C_1650-51%2C_02.jpg/960px-Gian_Lorenzo_Bernini%2C_busto_di_Francesco_I_d%27Este%2C_1650-51%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Petersdom_Mathilde_von_Toskana.jpg/960px-Petersdom_Mathilde_von_Toskana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2865,27 +2871,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1650-1651</t>
+          <t>1633-1637</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modène </t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Galleria Estense</t>
+          <t>Basilique Saint-Pierre</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Buste de Francesco Ier d'Este</t>
+          <t>Monument funéraire de la comtesse Mathilde de Toscane</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2893,14 +2899,15 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q33" t="n">
-        <v>106</v>
-      </c>
-      <c r="R33" t="n">
-        <v>98</v>
-      </c>
-      <c r="S33" t="n">
-        <v>50</v>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 600 cm (environ et  pour l'ensemble)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>300 cm (environ)</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2914,7 +2921,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Petersdom_Mathilde_von_Toskana.jpg/960px-Petersdom_Mathilde_von_Toskana.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Bust_of_Jesus_Christ_by_Gianlorenzo_Bernini.jpg/1280px-Bust_of_Jesus_Christ_by_Gianlorenzo_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2944,7 +2951,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1633-1637</t>
+          <t>1674-1677</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2954,17 +2961,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Basilique Saint-Pierre</t>
+          <t>Basilique Saint Sébastien hors-les-Murs</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Monument funéraire de la comtesse Mathilde de Toscane</t>
+          <t>Buste du Sauveur</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2972,15 +2979,8 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 600 cm (environ et  pour l'ensemble)</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>300 cm (environ)</t>
-        </is>
+      <c r="Q34" t="n">
+        <v>103</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Bust_of_Jesus_Christ_by_Gianlorenzo_Bernini.jpg/1280px-Bust_of_Jesus_Christ_by_Gianlorenzo_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ab/A_Faun_Teased_by_Children_by_Bernini.jpg/960px-A_Faun_Teased_by_Children_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1674-1677</t>
+          <t>1618-1619</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Basilique Saint Sébastien hors-les-Murs</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Buste du Sauveur</t>
+          <t>Le Faune poursuivi par des amours</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3053,7 +3053,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>103</v>
+        <v>132.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>47.9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3067,7 +3073,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ab/A_Faun_Teased_by_Children_by_Bernini.jpg/960px-A_Faun_Teased_by_Children_by_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3097,42 +3103,39 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1618-1619</t>
+          <t>1652-1653</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Piazza di Spagna</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Le Faune poursuivi par des amours</t>
+          <t xml:space="preserve">Fontaine de la Barcaccia </t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Travertin</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>132.4</v>
+        <v>150</v>
       </c>
       <c r="R36" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="S36" t="n">
-        <v>47.9</v>
+        <v>1500</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3146,12 +3149,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0c/Napoli_s_Martino_Pietro_Bernini_Carit%C3%A0_di_s_Martino_1050007.JPG/960px-Napoli_s_Martino_Pietro_Bernini_Carit%C3%A0_di_s_Martino_1050007.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gian Lorenzo</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3166,49 +3169,46 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1652-1653</t>
+          <t>1585-1587</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Piazza di Spagna</t>
+          <t>Certosa di San Martino</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fontaine de la Barcaccia </t>
+          <t>"Saint Martin et le mendiant"</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Travertin</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>150</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1500</v>
+        <v>138</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5432,12 +5432,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Giacomo Antonio</t>
+          <t>Cosimo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5447,17 +5447,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1648-1651</t>
+          <t>1660s</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5467,31 +5467,26 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Piazza Navona</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Fontaine des Quatre-Fleuves</t>
+          <t>Pont Saint Ange</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Le Nil</t>
+          <t>Ange portant le voile de Sainte Véronique</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Element d'architecture urbaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Travertin</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550</v>
+        <v>290</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5505,12 +5500,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg/960px-Ange_portant_le_voile_de_sainte_V%C3%A9ronique_de_Cosimo_Fancelli%2C_Pont_Saint-Ange%2C_Rome%2C_Italie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/e/e1/Fontana_dei_fiumi_%28Rome%29_-_Nile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cosimo</t>
+          <t>Giacomo Antonio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5520,17 +5515,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1660s</t>
+          <t>1648-1651</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5540,26 +5535,31 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pont Saint Ange</t>
+          <t>Piazza Navona</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Fontaine des Quatre-Fleuves</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Ange portant le voile de Sainte Véronique</t>
+          <t>Le Nil</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Element d'architecture urbaine</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Travertin</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>290</v>
+        <v>550</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>environ 1604</t>
+          <t>1604 environ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>environ 1636</t>
+          <t>1636 environ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>environ 1670-1690</t>
+          <t>1670-1690 environ</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>environ 1576</t>
+          <t>1576 environ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>environ 1570</t>
+          <t>1570 environ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>environ 1616-1620</t>
+          <t>1616-1620 environ</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>environ 1576</t>
+          <t>1576 environ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>environ 1601</t>
+          <t>1601 environ</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>environ 1570</t>
+          <t>1570 environ</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>environ 1583</t>
+          <t>1583 environ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
